--- a/balance.xlsx
+++ b/balance.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1113" uniqueCount="898">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1117" uniqueCount="903">
   <si>
     <t>Balance de Junked Metal. Esta planilla se genera desde src/balance.json (npm run balance:xlsx) y vuelve al juego con npm run balance:import.</t>
   </si>
@@ -2120,6 +2120,18 @@
     <t>Un jefe pasa a fase 2 con menos de esta fracción de su vida</t>
   </si>
   <si>
+    <t>segunda_barra_vida</t>
+  </si>
+  <si>
+    <t>Jefe final: al vaciar la primera barra ruge y se llena una segunda con esta fracción de su vida</t>
+  </si>
+  <si>
+    <t>segunda_barra_dano</t>
+  </si>
+  <si>
+    <t>Jefe final en la segunda barra: multiplicador del daño que hace al auto</t>
+  </si>
+  <si>
     <t>fase2_vel</t>
   </si>
   <si>
@@ -2676,6 +2688,9 @@
   </si>
   <si>
     <t>Presencia: fracción del tiempo en que el equipo logra pegarle al jefe (0 a 1)</t>
+  </si>
+  <si>
+    <t>vida (con segunda barra)</t>
   </si>
   <si>
     <t>DPS supuesto del equipo</t>
@@ -4516,7 +4531,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C91"/>
+  <dimension ref="A1:C93"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" style="1" customWidth="1"/>
@@ -4584,7 +4599,7 @@
         <v>698</v>
       </c>
       <c r="B6">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="C6" t="s">
         <v>699</v>
@@ -4595,7 +4610,7 @@
         <v>700</v>
       </c>
       <c r="B7">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="C7" t="s">
         <v>701</v>
@@ -4606,7 +4621,7 @@
         <v>702</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>1.2</v>
       </c>
       <c r="C8" t="s">
         <v>703</v>
@@ -4617,7 +4632,7 @@
         <v>704</v>
       </c>
       <c r="B9">
-        <v>16</v>
+        <v>1.7</v>
       </c>
       <c r="C9" t="s">
         <v>705</v>
@@ -4628,7 +4643,7 @@
         <v>706</v>
       </c>
       <c r="B10">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="C10" t="s">
         <v>707</v>
@@ -4639,7 +4654,7 @@
         <v>708</v>
       </c>
       <c r="B11">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
         <v>709</v>
@@ -4650,7 +4665,7 @@
         <v>710</v>
       </c>
       <c r="B12">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
         <v>711</v>
@@ -4661,7 +4676,7 @@
         <v>712</v>
       </c>
       <c r="B13">
-        <v>1.2</v>
+        <v>11</v>
       </c>
       <c r="C13" t="s">
         <v>713</v>
@@ -4672,7 +4687,7 @@
         <v>714</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C14" t="s">
         <v>715</v>
@@ -4683,7 +4698,7 @@
         <v>716</v>
       </c>
       <c r="B15">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="C15" t="s">
         <v>717</v>
@@ -4694,7 +4709,7 @@
         <v>718</v>
       </c>
       <c r="B16">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="C16" t="s">
         <v>719</v>
@@ -4705,7 +4720,7 @@
         <v>720</v>
       </c>
       <c r="B17">
-        <v>16</v>
+        <v>2.6</v>
       </c>
       <c r="C17" t="s">
         <v>721</v>
@@ -4716,7 +4731,7 @@
         <v>722</v>
       </c>
       <c r="B18">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="C18" t="s">
         <v>723</v>
@@ -4727,7 +4742,7 @@
         <v>724</v>
       </c>
       <c r="B19">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C19" t="s">
         <v>725</v>
@@ -4738,7 +4753,7 @@
         <v>726</v>
       </c>
       <c r="B20">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="C20" t="s">
         <v>727</v>
@@ -4749,7 +4764,7 @@
         <v>728</v>
       </c>
       <c r="B21">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="C21" t="s">
         <v>729</v>
@@ -4760,7 +4775,7 @@
         <v>730</v>
       </c>
       <c r="B22">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="C22" t="s">
         <v>731</v>
@@ -4771,7 +4786,7 @@
         <v>732</v>
       </c>
       <c r="B23">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="C23" t="s">
         <v>733</v>
@@ -4782,7 +4797,7 @@
         <v>734</v>
       </c>
       <c r="B24">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="C24" t="s">
         <v>735</v>
@@ -4793,7 +4808,7 @@
         <v>736</v>
       </c>
       <c r="B25">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="C25" t="s">
         <v>737</v>
@@ -4804,7 +4819,7 @@
         <v>738</v>
       </c>
       <c r="B26">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C26" t="s">
         <v>739</v>
@@ -4815,7 +4830,7 @@
         <v>740</v>
       </c>
       <c r="B27">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="C27" t="s">
         <v>741</v>
@@ -4826,7 +4841,7 @@
         <v>742</v>
       </c>
       <c r="B28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C28" t="s">
         <v>743</v>
@@ -4837,7 +4852,7 @@
         <v>744</v>
       </c>
       <c r="B29">
-        <v>0.16</v>
+        <v>1.1</v>
       </c>
       <c r="C29" t="s">
         <v>745</v>
@@ -4848,7 +4863,7 @@
         <v>746</v>
       </c>
       <c r="B30">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C30" t="s">
         <v>747</v>
@@ -4859,7 +4874,7 @@
         <v>748</v>
       </c>
       <c r="B31">
-        <v>1.3</v>
+        <v>0.16</v>
       </c>
       <c r="C31" t="s">
         <v>749</v>
@@ -4870,7 +4885,7 @@
         <v>750</v>
       </c>
       <c r="B32">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="C32" t="s">
         <v>751</v>
@@ -4881,7 +4896,7 @@
         <v>752</v>
       </c>
       <c r="B33">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="C33" t="s">
         <v>753</v>
@@ -4892,7 +4907,7 @@
         <v>754</v>
       </c>
       <c r="B34">
-        <v>0.5</v>
+        <v>22</v>
       </c>
       <c r="C34" t="s">
         <v>755</v>
@@ -4903,7 +4918,7 @@
         <v>756</v>
       </c>
       <c r="B35">
-        <v>20</v>
+        <v>2.5</v>
       </c>
       <c r="C35" t="s">
         <v>757</v>
@@ -4914,7 +4929,7 @@
         <v>758</v>
       </c>
       <c r="B36">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="C36" t="s">
         <v>759</v>
@@ -4925,7 +4940,7 @@
         <v>760</v>
       </c>
       <c r="B37">
-        <v>2.6</v>
+        <v>20</v>
       </c>
       <c r="C37" t="s">
         <v>761</v>
@@ -4936,7 +4951,7 @@
         <v>762</v>
       </c>
       <c r="B38">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="C38" t="s">
         <v>763</v>
@@ -4947,7 +4962,7 @@
         <v>764</v>
       </c>
       <c r="B39">
-        <v>9</v>
+        <v>2.6</v>
       </c>
       <c r="C39" t="s">
         <v>765</v>
@@ -4958,7 +4973,7 @@
         <v>766</v>
       </c>
       <c r="B40">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C40" t="s">
         <v>767</v>
@@ -4969,7 +4984,7 @@
         <v>768</v>
       </c>
       <c r="B41">
-        <v>0.8</v>
+        <v>9</v>
       </c>
       <c r="C41" t="s">
         <v>769</v>
@@ -4980,7 +4995,7 @@
         <v>770</v>
       </c>
       <c r="B42">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C42" t="s">
         <v>771</v>
@@ -4991,7 +5006,7 @@
         <v>772</v>
       </c>
       <c r="B43">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="C43" t="s">
         <v>773</v>
@@ -5002,7 +5017,7 @@
         <v>774</v>
       </c>
       <c r="B44">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C44" t="s">
         <v>775</v>
@@ -5013,7 +5028,7 @@
         <v>776</v>
       </c>
       <c r="B45">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="C45" t="s">
         <v>777</v>
@@ -5024,7 +5039,7 @@
         <v>778</v>
       </c>
       <c r="B46">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="C46" t="s">
         <v>779</v>
@@ -5035,7 +5050,7 @@
         <v>780</v>
       </c>
       <c r="B47">
-        <v>16</v>
+        <v>0.2</v>
       </c>
       <c r="C47" t="s">
         <v>781</v>
@@ -5046,7 +5061,7 @@
         <v>782</v>
       </c>
       <c r="B48">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="C48" t="s">
         <v>783</v>
@@ -5057,7 +5072,7 @@
         <v>784</v>
       </c>
       <c r="B49">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C49" t="s">
         <v>785</v>
@@ -5068,7 +5083,7 @@
         <v>786</v>
       </c>
       <c r="B50">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="C50" t="s">
         <v>787</v>
@@ -5079,7 +5094,7 @@
         <v>788</v>
       </c>
       <c r="B51">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C51" t="s">
         <v>789</v>
@@ -5090,7 +5105,7 @@
         <v>790</v>
       </c>
       <c r="B52">
-        <v>14</v>
+        <v>2.2</v>
       </c>
       <c r="C52" t="s">
         <v>791</v>
@@ -5101,7 +5116,7 @@
         <v>792</v>
       </c>
       <c r="B53">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C53" t="s">
         <v>793</v>
@@ -5112,7 +5127,7 @@
         <v>794</v>
       </c>
       <c r="B54">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C54" t="s">
         <v>795</v>
@@ -5123,7 +5138,7 @@
         <v>796</v>
       </c>
       <c r="B55">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C55" t="s">
         <v>797</v>
@@ -5134,7 +5149,7 @@
         <v>798</v>
       </c>
       <c r="B56">
-        <v>0.5</v>
+        <v>28</v>
       </c>
       <c r="C56" t="s">
         <v>799</v>
@@ -5145,7 +5160,7 @@
         <v>800</v>
       </c>
       <c r="B57">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="C57" t="s">
         <v>801</v>
@@ -5156,7 +5171,7 @@
         <v>802</v>
       </c>
       <c r="B58">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="C58" t="s">
         <v>803</v>
@@ -5167,7 +5182,7 @@
         <v>804</v>
       </c>
       <c r="B59">
-        <v>0.35</v>
+        <v>45</v>
       </c>
       <c r="C59" t="s">
         <v>805</v>
@@ -5178,7 +5193,7 @@
         <v>806</v>
       </c>
       <c r="B60">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="C60" t="s">
         <v>807</v>
@@ -5189,7 +5204,7 @@
         <v>808</v>
       </c>
       <c r="B61">
-        <v>24</v>
+        <v>0.35</v>
       </c>
       <c r="C61" t="s">
         <v>809</v>
@@ -5200,7 +5215,7 @@
         <v>810</v>
       </c>
       <c r="B62">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="C62" t="s">
         <v>811</v>
@@ -5211,7 +5226,7 @@
         <v>812</v>
       </c>
       <c r="B63">
-        <v>0.6</v>
+        <v>24</v>
       </c>
       <c r="C63" t="s">
         <v>813</v>
@@ -5222,7 +5237,7 @@
         <v>814</v>
       </c>
       <c r="B64">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="C64" t="s">
         <v>815</v>
@@ -5233,7 +5248,7 @@
         <v>816</v>
       </c>
       <c r="B65">
-        <v>17</v>
+        <v>0.6</v>
       </c>
       <c r="C65" t="s">
         <v>817</v>
@@ -5244,7 +5259,7 @@
         <v>818</v>
       </c>
       <c r="B66">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="C66" t="s">
         <v>819</v>
@@ -5255,7 +5270,7 @@
         <v>820</v>
       </c>
       <c r="B67">
-        <v>1.5</v>
+        <v>17</v>
       </c>
       <c r="C67" t="s">
         <v>821</v>
@@ -5266,7 +5281,7 @@
         <v>822</v>
       </c>
       <c r="B68">
-        <v>0.55</v>
+        <v>1.5</v>
       </c>
       <c r="C68" t="s">
         <v>823</v>
@@ -5277,7 +5292,7 @@
         <v>824</v>
       </c>
       <c r="B69">
-        <v>26</v>
+        <v>1.5</v>
       </c>
       <c r="C69" t="s">
         <v>825</v>
@@ -5288,7 +5303,7 @@
         <v>826</v>
       </c>
       <c r="B70">
-        <v>1.2</v>
+        <v>0.55</v>
       </c>
       <c r="C70" t="s">
         <v>827</v>
@@ -5299,7 +5314,7 @@
         <v>828</v>
       </c>
       <c r="B71">
-        <v>1.5</v>
+        <v>26</v>
       </c>
       <c r="C71" t="s">
         <v>829</v>
@@ -5310,7 +5325,7 @@
         <v>830</v>
       </c>
       <c r="B72">
-        <v>10</v>
+        <v>1.2</v>
       </c>
       <c r="C72" t="s">
         <v>831</v>
@@ -5321,7 +5336,7 @@
         <v>832</v>
       </c>
       <c r="B73">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="C73" t="s">
         <v>833</v>
@@ -5332,7 +5347,7 @@
         <v>834</v>
       </c>
       <c r="B74">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="C74" t="s">
         <v>835</v>
@@ -5343,7 +5358,7 @@
         <v>836</v>
       </c>
       <c r="B75">
-        <v>0.35</v>
+        <v>4</v>
       </c>
       <c r="C75" t="s">
         <v>837</v>
@@ -5354,7 +5369,7 @@
         <v>838</v>
       </c>
       <c r="B76">
-        <v>0.25</v>
+        <v>40</v>
       </c>
       <c r="C76" t="s">
         <v>839</v>
@@ -5365,7 +5380,7 @@
         <v>840</v>
       </c>
       <c r="B77">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="C77" t="s">
         <v>841</v>
@@ -5376,7 +5391,7 @@
         <v>842</v>
       </c>
       <c r="B78">
-        <v>25</v>
+        <v>0.25</v>
       </c>
       <c r="C78" t="s">
         <v>843</v>
@@ -5387,7 +5402,7 @@
         <v>844</v>
       </c>
       <c r="B79">
-        <v>3.8</v>
+        <v>0.25</v>
       </c>
       <c r="C79" t="s">
         <v>845</v>
@@ -5398,7 +5413,7 @@
         <v>846</v>
       </c>
       <c r="B80">
-        <v>2.6</v>
+        <v>25</v>
       </c>
       <c r="C80" t="s">
         <v>847</v>
@@ -5409,7 +5424,7 @@
         <v>848</v>
       </c>
       <c r="B81">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="C81" t="s">
         <v>849</v>
@@ -5420,7 +5435,7 @@
         <v>850</v>
       </c>
       <c r="B82">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="C82" t="s">
         <v>851</v>
@@ -5431,7 +5446,7 @@
         <v>852</v>
       </c>
       <c r="B83">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="C83" t="s">
         <v>853</v>
@@ -5442,7 +5457,7 @@
         <v>854</v>
       </c>
       <c r="B84">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="C84" t="s">
         <v>855</v>
@@ -5453,7 +5468,7 @@
         <v>856</v>
       </c>
       <c r="B85">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="C85" t="s">
         <v>857</v>
@@ -5464,32 +5479,32 @@
         <v>858</v>
       </c>
       <c r="B86">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="C86" t="s">
-        <v>847</v>
+        <v>859</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B87">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C87" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B88">
-        <v>26</v>
+        <v>0.75</v>
       </c>
       <c r="C88" t="s">
-        <v>862</v>
+        <v>851</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -5497,7 +5512,7 @@
         <v>863</v>
       </c>
       <c r="B89">
-        <v>2.6</v>
+        <v>30</v>
       </c>
       <c r="C89" t="s">
         <v>864</v>
@@ -5508,7 +5523,7 @@
         <v>865</v>
       </c>
       <c r="B90">
-        <v>0.9</v>
+        <v>26</v>
       </c>
       <c r="C90" t="s">
         <v>866</v>
@@ -5519,10 +5534,32 @@
         <v>867</v>
       </c>
       <c r="B91">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="C91" t="s">
         <v>868</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>869</v>
+      </c>
+      <c r="B92">
+        <v>0.9</v>
+      </c>
+      <c r="C92" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="B93">
+        <v>1.4</v>
+      </c>
+      <c r="C93" t="s">
+        <v>872</v>
       </c>
     </row>
   </sheetData>
@@ -5545,17 +5582,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="B4" s="7">
         <v>0</v>
@@ -5563,7 +5600,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="B5" s="7">
         <v>1</v>
@@ -5571,7 +5608,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>177</v>
@@ -5579,7 +5616,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="B7" s="7">
         <v>12</v>
@@ -5587,7 +5624,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="B8" s="7">
         <v>1</v>
@@ -5595,7 +5632,7 @@
     </row>
     <row r="9" spans="4:29" x14ac:dyDescent="0.25">
       <c r="D9" s="8" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="E9" s="8">
         <f>INDEX(armas!$B$3:$B$500,MATCH(E$10,armas!$A$3:$A$500,0))</f>
@@ -5670,12 +5707,12 @@
         <f>INDEX(armas!$B$3:$B$500,MATCH(AB$10,armas!$A$3:$A$500,0))</f>
       </c>
       <c r="AC9" s="8" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
     </row>
     <row r="10" spans="4:29" x14ac:dyDescent="0.25">
       <c r="D10" s="9" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>105</v>
@@ -5755,7 +5792,7 @@
     </row>
     <row r="11" spans="4:28" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -5841,7 +5878,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>880</v>
+        <v>884</v>
       </c>
       <c r="E12" s="10">
         <f>(INDEX(armas!$D$3:$D$500,MATCH(E$10,armas!$A$3:$A$500,0))+INDEX(armas!$E$3:$E$500,MATCH(E$10,armas!$A$3:$A$500,0))*E$11)*$B$5</f>
@@ -7097,17 +7134,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="B4" s="7">
         <v>0.8</v>
@@ -7124,16 +7161,16 @@
         <v>8</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>9</v>
+        <v>888</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>884</v>
+        <v>889</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>885</v>
+        <v>890</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>886</v>
+        <v>891</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -7147,7 +7184,7 @@
         <f>INDEX(enemigos!$C$3:$C$500,MATCH($A7,enemigos!$A$3:$A$500,0))</f>
       </c>
       <c r="D7">
-        <f>INDEX(enemigos!$D$3:$D$500,MATCH($A7,enemigos!$A$3:$A$500,0))</f>
+        <f>INDEX(enemigos!$D$3:$D$500,MATCH($A7,enemigos!$A$3:$A$500,0))*IF($C7="jefe_final",1+INDEX(ataques!$B$3:$B$500,MATCH("segunda_barra_vida",ataques!$A$3:$A$500,0)),1)</f>
       </c>
       <c r="E7" s="7">
         <v>200</v>
@@ -7170,7 +7207,7 @@
         <f>INDEX(enemigos!$C$3:$C$500,MATCH($A8,enemigos!$A$3:$A$500,0))</f>
       </c>
       <c r="D8">
-        <f>INDEX(enemigos!$D$3:$D$500,MATCH($A8,enemigos!$A$3:$A$500,0))</f>
+        <f>INDEX(enemigos!$D$3:$D$500,MATCH($A8,enemigos!$A$3:$A$500,0))*IF($C8="jefe_final",1+INDEX(ataques!$B$3:$B$500,MATCH("segunda_barra_vida",ataques!$A$3:$A$500,0)),1)</f>
       </c>
       <c r="E8" s="7">
         <v>200</v>
@@ -7193,7 +7230,7 @@
         <f>INDEX(enemigos!$C$3:$C$500,MATCH($A9,enemigos!$A$3:$A$500,0))</f>
       </c>
       <c r="D9">
-        <f>INDEX(enemigos!$D$3:$D$500,MATCH($A9,enemigos!$A$3:$A$500,0))</f>
+        <f>INDEX(enemigos!$D$3:$D$500,MATCH($A9,enemigos!$A$3:$A$500,0))*IF($C9="jefe_final",1+INDEX(ataques!$B$3:$B$500,MATCH("segunda_barra_vida",ataques!$A$3:$A$500,0)),1)</f>
       </c>
       <c r="E9" s="7">
         <v>200</v>
@@ -7216,7 +7253,7 @@
         <f>INDEX(enemigos!$C$3:$C$500,MATCH($A10,enemigos!$A$3:$A$500,0))</f>
       </c>
       <c r="D10">
-        <f>INDEX(enemigos!$D$3:$D$500,MATCH($A10,enemigos!$A$3:$A$500,0))</f>
+        <f>INDEX(enemigos!$D$3:$D$500,MATCH($A10,enemigos!$A$3:$A$500,0))*IF($C10="jefe_final",1+INDEX(ataques!$B$3:$B$500,MATCH("segunda_barra_vida",ataques!$A$3:$A$500,0)),1)</f>
       </c>
       <c r="E10" s="7">
         <v>200</v>
@@ -7239,7 +7276,7 @@
         <f>INDEX(enemigos!$C$3:$C$500,MATCH($A11,enemigos!$A$3:$A$500,0))</f>
       </c>
       <c r="D11">
-        <f>INDEX(enemigos!$D$3:$D$500,MATCH($A11,enemigos!$A$3:$A$500,0))</f>
+        <f>INDEX(enemigos!$D$3:$D$500,MATCH($A11,enemigos!$A$3:$A$500,0))*IF($C11="jefe_final",1+INDEX(ataques!$B$3:$B$500,MATCH("segunda_barra_vida",ataques!$A$3:$A$500,0)),1)</f>
       </c>
       <c r="E11" s="7">
         <v>600</v>
@@ -7262,7 +7299,7 @@
         <f>INDEX(enemigos!$C$3:$C$500,MATCH($A12,enemigos!$A$3:$A$500,0))</f>
       </c>
       <c r="D12">
-        <f>INDEX(enemigos!$D$3:$D$500,MATCH($A12,enemigos!$A$3:$A$500,0))</f>
+        <f>INDEX(enemigos!$D$3:$D$500,MATCH($A12,enemigos!$A$3:$A$500,0))*IF($C12="jefe_final",1+INDEX(ataques!$B$3:$B$500,MATCH("segunda_barra_vida",ataques!$A$3:$A$500,0)),1)</f>
       </c>
       <c r="E12" s="7">
         <v>600</v>
@@ -7285,7 +7322,7 @@
         <f>INDEX(enemigos!$C$3:$C$500,MATCH($A13,enemigos!$A$3:$A$500,0))</f>
       </c>
       <c r="D13">
-        <f>INDEX(enemigos!$D$3:$D$500,MATCH($A13,enemigos!$A$3:$A$500,0))</f>
+        <f>INDEX(enemigos!$D$3:$D$500,MATCH($A13,enemigos!$A$3:$A$500,0))*IF($C13="jefe_final",1+INDEX(ataques!$B$3:$B$500,MATCH("segunda_barra_vida",ataques!$A$3:$A$500,0)),1)</f>
       </c>
       <c r="E13" s="7">
         <v>600</v>
@@ -7315,17 +7352,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>887</v>
+        <v>892</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>888</v>
+        <v>893</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>889</v>
+        <v>894</v>
       </c>
       <c r="B4" s="7">
         <v>100</v>
@@ -7333,7 +7370,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>890</v>
+        <v>895</v>
       </c>
       <c r="B5" s="7">
         <v>420</v>
@@ -7341,7 +7378,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>891</v>
+        <v>896</v>
       </c>
       <c r="B6" s="7">
         <v>600</v>
@@ -7349,7 +7386,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>892</v>
+        <v>897</v>
       </c>
       <c r="B7" s="7">
         <v>1</v>
@@ -7357,7 +7394,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="B8">
         <f>INT((B7*INDEX(ritmo!$B$3:$B$500,MATCH("tornillos_jefe",ritmo!$A$3:$A$500,0))+INT(B5/INDEX(ritmo!$B$3:$B$500,MATCH("tornillos_div_tiempo",ritmo!$A$3:$A$500,0)))+INT(B6*INDEX(ritmo!$B$3:$B$500,MATCH("dureza_xp",ritmo!$A$3:$A$500,0))/INDEX(ritmo!$B$3:$B$500,MATCH("tornillos_div_bajas",ritmo!$A$3:$A$500,0)))))</f>
@@ -7404,7 +7441,7 @@
         <v>233</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>894</v>
+        <v>899</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -8333,7 +8370,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="B32" t="s">
         <v>177</v>
@@ -8350,7 +8387,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="B33" t="s">
         <v>179</v>
@@ -8367,7 +8404,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="B34" t="s">
         <v>181</v>
@@ -8384,7 +8421,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="B35" t="s">
         <v>183</v>
@@ -8401,7 +8438,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="B36" t="s">
         <v>185</v>
@@ -8418,7 +8455,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="B37" t="s">
         <v>186</v>
@@ -8435,7 +8472,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="B38" t="s">
         <v>133</v>
@@ -8452,7 +8489,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="B39" t="s">
         <v>189</v>
@@ -8469,7 +8506,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>896</v>
+        <v>901</v>
       </c>
       <c r="B40" t="s">
         <v>214</v>
@@ -8486,7 +8523,7 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>896</v>
+        <v>901</v>
       </c>
       <c r="B41" t="s">
         <v>216</v>
@@ -8503,7 +8540,7 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>896</v>
+        <v>901</v>
       </c>
       <c r="B42" t="s">
         <v>35</v>
@@ -8520,7 +8557,7 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>896</v>
+        <v>901</v>
       </c>
       <c r="B43" t="s">
         <v>219</v>
@@ -8537,7 +8574,7 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>896</v>
+        <v>901</v>
       </c>
       <c r="B44" t="s">
         <v>221</v>
@@ -8554,7 +8591,7 @@
     </row>
     <row r="46" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C46" s="1" t="s">
-        <v>897</v>
+        <v>902</v>
       </c>
       <c r="N46" s="11">
         <f>SUM(N11:N44)</f>
@@ -8657,7 +8694,7 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E3">
         <v>8</v>
@@ -9007,7 +9044,7 @@
         <v>52</v>
       </c>
       <c r="D13">
-        <v>20000</v>
+        <v>8000</v>
       </c>
       <c r="E13">
         <v>9</v>
@@ -9042,7 +9079,7 @@
         <v>52</v>
       </c>
       <c r="D14">
-        <v>40000</v>
+        <v>7500</v>
       </c>
       <c r="E14">
         <v>7</v>
@@ -9077,7 +9114,7 @@
         <v>52</v>
       </c>
       <c r="D15">
-        <v>30000</v>
+        <v>7000</v>
       </c>
       <c r="E15">
         <v>8</v>

--- a/balance.xlsx
+++ b/balance.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1117" uniqueCount="903">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1117" uniqueCount="904">
   <si>
     <t>Balance de Junked Metal. Esta planilla se genera desde src/balance.json (npm run balance:xlsx) y vuelve al juego con npm run balance:import.</t>
   </si>
@@ -560,43 +560,46 @@
     <t>buggy</t>
   </si>
   <si>
-    <t>Buggy</t>
+    <t>El Divorciado</t>
   </si>
   <si>
     <t>monster</t>
   </si>
   <si>
-    <t>Monster Truck</t>
+    <t>Crisis de los 40</t>
   </si>
   <si>
     <t>formula</t>
   </si>
   <si>
-    <t>Fórmula</t>
+    <t>Multa Pendiente</t>
   </si>
   <si>
     <t>tanque</t>
   </si>
   <si>
-    <t>Tanque de juguete</t>
+    <t>Política Exterior</t>
   </si>
   <si>
     <t>carrera</t>
   </si>
   <si>
+    <t>Sin Seguro</t>
+  </si>
+  <si>
     <t>axel</t>
   </si>
   <si>
-    <t>Axel</t>
-  </si>
-  <si>
-    <t>Camión de helados</t>
+    <t>Axel Sin Licencia</t>
+  </si>
+  <si>
+    <t>Diabetes Tipo Turbo</t>
   </si>
   <si>
     <t>combi</t>
   </si>
   <si>
-    <t>Combi</t>
+    <t>La Combi del Tío Raro</t>
   </si>
   <si>
     <t>dano_mult</t>
@@ -671,28 +674,28 @@
     <t>soldadito</t>
   </si>
   <si>
-    <t>Soldadito de plástico</t>
+    <t>Sargento Sin Pensión</t>
   </si>
   <si>
     <t>muneca</t>
   </si>
   <si>
-    <t>Muñeca de trapo</t>
-  </si>
-  <si>
-    <t>Robot de lata</t>
+    <t>Doña Trapo, Divorciada</t>
+  </si>
+  <si>
+    <t>Robot en Crisis Existencial</t>
   </si>
   <si>
     <t>dino</t>
   </si>
   <si>
-    <t>Dinosaurio</t>
+    <t>Rex, Ya No Tan Temible</t>
   </si>
   <si>
     <t>figura</t>
   </si>
   <si>
-    <t>Figura de acción</t>
+    <t>Mega Macho Sin Articulaciones</t>
   </si>
   <si>
     <t>efecto</t>
@@ -3219,10 +3222,10 @@
         <v>6</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="2" ht="78" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -3230,1297 +3233,1297 @@
         <v>145</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B3">
         <v>0.5</v>
       </c>
       <c r="C3" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B4">
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B5">
         <v>1.3</v>
       </c>
       <c r="C5" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B7">
         <v>200</v>
       </c>
       <c r="C7" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B8">
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B9">
         <v>2.2</v>
       </c>
       <c r="C9" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B10">
         <v>100</v>
       </c>
       <c r="C10" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B11">
         <v>60</v>
       </c>
       <c r="C11" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B13">
         <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B14">
         <v>36</v>
       </c>
       <c r="C14" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B15">
         <v>54</v>
       </c>
       <c r="C15" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B16">
         <v>1.6</v>
       </c>
       <c r="C16" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B17">
         <v>75</v>
       </c>
       <c r="C17" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B18">
         <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B19">
         <v>26</v>
       </c>
       <c r="C19" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B20">
         <v>10</v>
       </c>
       <c r="C20" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B21">
         <v>12</v>
       </c>
       <c r="C21" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B22">
         <v>0.6</v>
       </c>
       <c r="C22" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B23">
         <v>150</v>
       </c>
       <c r="C23" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B24">
         <v>6</v>
       </c>
       <c r="C24" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B25">
         <v>60</v>
       </c>
       <c r="C25" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B26">
         <v>4</v>
       </c>
       <c r="C26" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B27">
         <v>1.2</v>
       </c>
       <c r="C27" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B28">
         <v>90</v>
       </c>
       <c r="C28" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B29">
         <v>0.5</v>
       </c>
       <c r="C29" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B30">
         <v>45</v>
       </c>
       <c r="C30" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B31">
         <v>35</v>
       </c>
       <c r="C31" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B32">
         <v>16</v>
       </c>
       <c r="C32" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B33">
         <v>12</v>
       </c>
       <c r="C33" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B34">
         <v>22</v>
       </c>
       <c r="C34" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B35">
         <v>60</v>
       </c>
       <c r="C35" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B36">
         <v>45</v>
       </c>
       <c r="C36" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B37">
         <v>26</v>
       </c>
       <c r="C37" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B38">
         <v>30</v>
       </c>
       <c r="C38" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B39">
         <v>8</v>
       </c>
       <c r="C39" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B40">
         <v>7</v>
       </c>
       <c r="C40" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B41">
         <v>20</v>
       </c>
       <c r="C41" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B42">
         <v>95</v>
       </c>
       <c r="C42" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B43">
         <v>50</v>
       </c>
       <c r="C43" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B44">
         <v>200</v>
       </c>
       <c r="C44" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B45">
         <v>400</v>
       </c>
       <c r="C45" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B46">
         <v>600</v>
       </c>
       <c r="C46" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B47">
         <v>120</v>
       </c>
       <c r="C47" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B48">
         <v>600</v>
       </c>
       <c r="C48" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B49">
         <v>100</v>
       </c>
       <c r="C49" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B50">
         <v>460</v>
       </c>
       <c r="C50" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B51">
         <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B52">
         <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B53">
         <v>2</v>
       </c>
       <c r="C53" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B54">
         <v>0.6</v>
       </c>
       <c r="C54" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B55">
         <v>3</v>
       </c>
       <c r="C55" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B56">
         <v>5</v>
       </c>
       <c r="C56" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B57">
         <v>350</v>
       </c>
       <c r="C57" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B58">
         <v>40</v>
       </c>
       <c r="C58" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B59">
         <v>8</v>
       </c>
       <c r="C59" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B60">
         <v>0.35</v>
       </c>
       <c r="C60" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B61">
         <v>0.035</v>
       </c>
       <c r="C61" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B62">
         <v>0.006</v>
       </c>
       <c r="C62" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B63">
         <v>30</v>
       </c>
       <c r="C63" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B64">
         <v>40</v>
       </c>
       <c r="C64" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B65">
         <v>5</v>
       </c>
       <c r="C65" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B66">
         <v>4</v>
       </c>
       <c r="C66" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B67">
         <v>2.5</v>
       </c>
       <c r="C67" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B68">
         <v>0.3</v>
       </c>
       <c r="C68" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B69">
         <v>25</v>
       </c>
       <c r="C69" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B70">
         <v>20</v>
       </c>
       <c r="C70" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B71">
         <v>25</v>
       </c>
       <c r="C71" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B72">
         <v>0.3</v>
       </c>
       <c r="C72" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B73">
         <v>1.5</v>
       </c>
       <c r="C73" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B74">
         <v>60</v>
       </c>
       <c r="C74" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B75">
         <v>300</v>
       </c>
       <c r="C75" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B76">
         <v>0.25</v>
       </c>
       <c r="C76" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B77">
         <v>0.5</v>
       </c>
       <c r="C77" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B78">
         <v>0.7</v>
       </c>
       <c r="C78" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B79">
         <v>0.8</v>
       </c>
       <c r="C79" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B80">
         <v>0.4</v>
       </c>
       <c r="C80" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B81">
         <v>60</v>
       </c>
       <c r="C81" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B82">
         <v>20</v>
       </c>
       <c r="C82" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B83">
         <v>1.4</v>
       </c>
       <c r="C83" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B84">
         <v>10</v>
       </c>
       <c r="C84" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B85">
         <v>0.12</v>
       </c>
       <c r="C85" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B86">
         <v>3.5</v>
       </c>
       <c r="C86" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B87">
         <v>30</v>
       </c>
       <c r="C87" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B88">
         <v>25</v>
       </c>
       <c r="C88" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B89">
         <v>3</v>
       </c>
       <c r="C89" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B90">
         <v>0.1</v>
       </c>
       <c r="C90" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B91">
         <v>18</v>
       </c>
       <c r="C91" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B92">
         <v>0.4</v>
       </c>
       <c r="C92" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B93">
         <v>14</v>
       </c>
       <c r="C93" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B94">
         <v>2</v>
       </c>
       <c r="C94" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B95">
         <v>25</v>
       </c>
       <c r="C95" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B96">
         <v>3</v>
       </c>
       <c r="C96" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B97">
         <v>0.4</v>
       </c>
       <c r="C97" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B98">
         <v>40</v>
       </c>
       <c r="C98" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B99">
         <v>1.55</v>
       </c>
       <c r="C99" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B100">
         <v>1.8</v>
       </c>
       <c r="C100" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B101">
         <v>3</v>
       </c>
       <c r="C101" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B102">
         <v>1.3</v>
       </c>
       <c r="C102" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B103">
         <v>1.4</v>
       </c>
       <c r="C103" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B104">
         <v>5</v>
       </c>
       <c r="C104" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B105">
         <v>0.3</v>
       </c>
       <c r="C105" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B106">
         <v>1.3</v>
       </c>
       <c r="C106" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B107">
         <v>1.6</v>
       </c>
       <c r="C107" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B108">
         <v>1.8</v>
       </c>
       <c r="C108" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B109">
         <v>0.4</v>
       </c>
       <c r="C109" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B110">
         <v>0.8</v>
       </c>
       <c r="C110" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B111">
         <v>0.6</v>
       </c>
       <c r="C111" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B112">
         <v>14</v>
       </c>
       <c r="C112" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B113">
         <v>2</v>
       </c>
       <c r="C113" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B114">
         <v>0.2</v>
       </c>
       <c r="C114" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B115">
         <v>0.1</v>
       </c>
       <c r="C115" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B116">
         <v>0.1</v>
       </c>
       <c r="C116" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B117">
         <v>1.5</v>
       </c>
       <c r="C117" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B118">
         <v>8</v>
       </c>
       <c r="C118" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B119">
         <v>0.1</v>
       </c>
       <c r="C119" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
   </sheetData>
@@ -4544,10 +4547,10 @@
         <v>6</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="2" ht="78" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -4555,1011 +4558,1011 @@
         <v>145</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B3">
         <v>0.45</v>
       </c>
       <c r="C3" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B4">
         <v>0.8</v>
       </c>
       <c r="C4" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B5">
         <v>0.5</v>
       </c>
       <c r="C5" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B6">
         <v>0.5</v>
       </c>
       <c r="C6" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B7">
         <v>1.5</v>
       </c>
       <c r="C7" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B8">
         <v>1.2</v>
       </c>
       <c r="C8" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B9">
         <v>1.7</v>
       </c>
       <c r="C9" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B10">
         <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B11">
         <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B12">
         <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B13">
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B14">
         <v>10</v>
       </c>
       <c r="C14" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B15">
         <v>1.2</v>
       </c>
       <c r="C15" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B17">
         <v>2.6</v>
       </c>
       <c r="C17" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B18">
         <v>1.4</v>
       </c>
       <c r="C18" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B19">
         <v>16</v>
       </c>
       <c r="C19" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B20">
         <v>2.6</v>
       </c>
       <c r="C20" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B21">
         <v>4</v>
       </c>
       <c r="C21" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B22">
         <v>3</v>
       </c>
       <c r="C22" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B23">
         <v>1.5</v>
       </c>
       <c r="C23" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B24">
         <v>1.7</v>
       </c>
       <c r="C24" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B25">
         <v>0.7</v>
       </c>
       <c r="C25" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B26">
         <v>3</v>
       </c>
       <c r="C26" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B27">
         <v>3</v>
       </c>
       <c r="C27" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B28">
         <v>5</v>
       </c>
       <c r="C28" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B29">
         <v>1.1</v>
       </c>
       <c r="C29" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B30">
         <v>6</v>
       </c>
       <c r="C30" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B31">
         <v>0.16</v>
       </c>
       <c r="C31" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B32">
         <v>3</v>
       </c>
       <c r="C32" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B33">
         <v>1.3</v>
       </c>
       <c r="C33" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B34">
         <v>22</v>
       </c>
       <c r="C34" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B35">
         <v>2.5</v>
       </c>
       <c r="C35" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B36">
         <v>0.5</v>
       </c>
       <c r="C36" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B37">
         <v>20</v>
       </c>
       <c r="C37" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B38">
         <v>1.4</v>
       </c>
       <c r="C38" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B39">
         <v>2.6</v>
       </c>
       <c r="C39" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B40">
         <v>2</v>
       </c>
       <c r="C40" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B41">
         <v>9</v>
       </c>
       <c r="C41" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B42">
         <v>12</v>
       </c>
       <c r="C42" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B43">
         <v>0.8</v>
       </c>
       <c r="C43" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B44">
         <v>3</v>
       </c>
       <c r="C44" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B45">
         <v>0.3</v>
       </c>
       <c r="C45" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B46">
         <v>7</v>
       </c>
       <c r="C46" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B47">
         <v>0.2</v>
       </c>
       <c r="C47" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B48">
         <v>3.5</v>
       </c>
       <c r="C48" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B49">
         <v>16</v>
       </c>
       <c r="C49" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B50">
         <v>1</v>
       </c>
       <c r="C50" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B51">
         <v>10</v>
       </c>
       <c r="C51" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B52">
         <v>2.2</v>
       </c>
       <c r="C52" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B53">
         <v>4</v>
       </c>
       <c r="C53" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B54">
         <v>14</v>
       </c>
       <c r="C54" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B55">
         <v>8</v>
       </c>
       <c r="C55" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B56">
         <v>28</v>
       </c>
       <c r="C56" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B57">
         <v>6</v>
       </c>
       <c r="C57" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B58">
         <v>0.5</v>
       </c>
       <c r="C58" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B59">
         <v>45</v>
       </c>
       <c r="C59" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B60">
         <v>0.4</v>
       </c>
       <c r="C60" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B61">
         <v>0.35</v>
       </c>
       <c r="C61" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B62">
         <v>1</v>
       </c>
       <c r="C62" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B63">
         <v>24</v>
       </c>
       <c r="C63" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B64">
         <v>1.2</v>
       </c>
       <c r="C64" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B65">
         <v>0.6</v>
       </c>
       <c r="C65" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B66">
         <v>1.8</v>
       </c>
       <c r="C66" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B67">
         <v>17</v>
       </c>
       <c r="C67" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B68">
         <v>1.5</v>
       </c>
       <c r="C68" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B69">
         <v>1.5</v>
       </c>
       <c r="C69" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B70">
         <v>0.55</v>
       </c>
       <c r="C70" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B71">
         <v>26</v>
       </c>
       <c r="C71" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B72">
         <v>1.2</v>
       </c>
       <c r="C72" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B73">
         <v>1.5</v>
       </c>
       <c r="C73" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B74">
         <v>10</v>
       </c>
       <c r="C74" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B75">
         <v>4</v>
       </c>
       <c r="C75" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B76">
         <v>40</v>
       </c>
       <c r="C76" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B77">
         <v>0.35</v>
       </c>
       <c r="C77" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B78">
         <v>0.25</v>
       </c>
       <c r="C78" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B79">
         <v>0.25</v>
       </c>
       <c r="C79" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B80">
         <v>25</v>
       </c>
       <c r="C80" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B81">
         <v>3.8</v>
       </c>
       <c r="C81" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B82">
         <v>2.6</v>
       </c>
       <c r="C82" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B83">
         <v>2.6</v>
       </c>
       <c r="C83" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B84">
         <v>2.1</v>
       </c>
       <c r="C84" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B85">
         <v>1.6</v>
       </c>
       <c r="C85" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B86">
         <v>1.2</v>
       </c>
       <c r="C86" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B87">
         <v>1</v>
       </c>
       <c r="C87" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B88">
         <v>0.75</v>
       </c>
       <c r="C88" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B89">
         <v>30</v>
       </c>
       <c r="C89" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B90">
         <v>26</v>
       </c>
       <c r="C90" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B91">
         <v>2.6</v>
       </c>
       <c r="C91" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B92">
         <v>0.9</v>
       </c>
       <c r="C92" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B93">
         <v>1.4</v>
       </c>
       <c r="C93" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
     </row>
   </sheetData>
@@ -5582,17 +5585,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="B4" s="7">
         <v>0</v>
@@ -5600,7 +5603,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="B5" s="7">
         <v>1</v>
@@ -5608,7 +5611,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>177</v>
@@ -5616,7 +5619,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B7" s="7">
         <v>12</v>
@@ -5624,7 +5627,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B8" s="7">
         <v>1</v>
@@ -5632,7 +5635,7 @@
     </row>
     <row r="9" spans="4:29" x14ac:dyDescent="0.25">
       <c r="D9" s="8" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="E9" s="8">
         <f>INDEX(armas!$B$3:$B$500,MATCH(E$10,armas!$A$3:$A$500,0))</f>
@@ -5707,12 +5710,12 @@
         <f>INDEX(armas!$B$3:$B$500,MATCH(AB$10,armas!$A$3:$A$500,0))</f>
       </c>
       <c r="AC9" s="8" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
     </row>
     <row r="10" spans="4:29" x14ac:dyDescent="0.25">
       <c r="D10" s="9" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>105</v>
@@ -5792,7 +5795,7 @@
     </row>
     <row r="11" spans="4:28" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -5878,7 +5881,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="E12" s="10">
         <f>(INDEX(armas!$D$3:$D$500,MATCH(E$10,armas!$A$3:$A$500,0))+INDEX(armas!$E$3:$E$500,MATCH(E$10,armas!$A$3:$A$500,0))*E$11)*$B$5</f>
@@ -7134,17 +7137,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B4" s="7">
         <v>0.8</v>
@@ -7161,16 +7164,16 @@
         <v>8</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -7352,17 +7355,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B4" s="7">
         <v>100</v>
@@ -7370,7 +7373,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B5" s="7">
         <v>420</v>
@@ -7378,7 +7381,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B6" s="7">
         <v>600</v>
@@ -7386,7 +7389,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B7" s="7">
         <v>1</v>
@@ -7394,7 +7397,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B8">
         <f>INT((B7*INDEX(ritmo!$B$3:$B$500,MATCH("tornillos_jefe",ritmo!$A$3:$A$500,0))+INT(B5/INDEX(ritmo!$B$3:$B$500,MATCH("tornillos_div_tiempo",ritmo!$A$3:$A$500,0)))+INT(B6*INDEX(ritmo!$B$3:$B$500,MATCH("dureza_xp",ritmo!$A$3:$A$500,0))/INDEX(ritmo!$B$3:$B$500,MATCH("tornillos_div_bajas",ritmo!$A$3:$A$500,0)))))</f>
@@ -7411,45 +7414,45 @@
         <v>7</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>248</v>
+      </c>
+      <c r="B11" t="s">
         <v>247</v>
-      </c>
-      <c r="B11" t="s">
-        <v>246</v>
       </c>
       <c r="C11">
         <f>INDEX(precios!$C$3:$C$500,MATCH($B11,precios!$A$3:$A$500,0))</f>
@@ -7490,10 +7493,10 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B12" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C12">
         <f>INDEX(precios!$C$3:$C$500,MATCH($B12,precios!$A$3:$A$500,0))</f>
@@ -7534,10 +7537,10 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B13" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C13">
         <f>INDEX(precios!$C$3:$C$500,MATCH($B13,precios!$A$3:$A$500,0))</f>
@@ -7578,10 +7581,10 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C14">
         <f>INDEX(precios!$C$3:$C$500,MATCH($B14,precios!$A$3:$A$500,0))</f>
@@ -7622,7 +7625,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
@@ -7666,10 +7669,10 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B16" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C16">
         <f>INDEX(precios!$C$3:$C$500,MATCH($B16,precios!$A$3:$A$500,0))</f>
@@ -7710,10 +7713,10 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B17" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C17">
         <f>INDEX(precios!$C$3:$C$500,MATCH($B17,precios!$A$3:$A$500,0))</f>
@@ -7754,10 +7757,10 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B18" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C18">
         <f>INDEX(precios!$C$3:$C$500,MATCH($B18,precios!$A$3:$A$500,0))</f>
@@ -7798,10 +7801,10 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B19" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C19">
         <f>INDEX(precios!$C$3:$C$500,MATCH($B19,precios!$A$3:$A$500,0))</f>
@@ -7842,10 +7845,10 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>266</v>
+      </c>
+      <c r="B20" t="s">
         <v>265</v>
-      </c>
-      <c r="B20" t="s">
-        <v>264</v>
       </c>
       <c r="C20">
         <f>INDEX(precios!$C$3:$C$500,MATCH($B20,precios!$A$3:$A$500,0))</f>
@@ -7886,10 +7889,10 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B21" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C21">
         <f>INDEX(precios!$C$3:$C$500,MATCH($B21,precios!$A$3:$A$500,0))</f>
@@ -7930,10 +7933,10 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>271</v>
+      </c>
+      <c r="B22" t="s">
         <v>270</v>
-      </c>
-      <c r="B22" t="s">
-        <v>269</v>
       </c>
       <c r="C22">
         <f>INDEX(precios!$C$3:$C$500,MATCH($B22,precios!$A$3:$A$500,0))</f>
@@ -7974,10 +7977,10 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B23" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C23">
         <f>INDEX(precios!$C$3:$C$500,MATCH($B23,precios!$A$3:$A$500,0))</f>
@@ -8018,10 +8021,10 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B24" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C24">
         <f>INDEX(precios!$C$3:$C$500,MATCH($B24,precios!$A$3:$A$500,0))</f>
@@ -8062,10 +8065,10 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B25" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C25">
         <f>INDEX(precios!$C$3:$C$500,MATCH($B25,precios!$A$3:$A$500,0))</f>
@@ -8106,10 +8109,10 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B26" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C26">
         <f>INDEX(precios!$C$3:$C$500,MATCH($B26,precios!$A$3:$A$500,0))</f>
@@ -8150,10 +8153,10 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B27" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C27">
         <f>INDEX(precios!$C$3:$C$500,MATCH($B27,precios!$A$3:$A$500,0))</f>
@@ -8194,10 +8197,10 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B28" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C28">
         <f>INDEX(precios!$C$3:$C$500,MATCH($B28,precios!$A$3:$A$500,0))</f>
@@ -8238,10 +8241,10 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B29" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C29">
         <f>INDEX(precios!$C$3:$C$500,MATCH($B29,precios!$A$3:$A$500,0))</f>
@@ -8282,10 +8285,10 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B30" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C30">
         <f>INDEX(precios!$C$3:$C$500,MATCH($B30,precios!$A$3:$A$500,0))</f>
@@ -8326,10 +8329,10 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B31" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C31">
         <f>INDEX(precios!$C$3:$C$500,MATCH($B31,precios!$A$3:$A$500,0))</f>
@@ -8370,7 +8373,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B32" t="s">
         <v>177</v>
@@ -8387,7 +8390,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B33" t="s">
         <v>179</v>
@@ -8404,7 +8407,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B34" t="s">
         <v>181</v>
@@ -8421,7 +8424,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B35" t="s">
         <v>183</v>
@@ -8438,7 +8441,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B36" t="s">
         <v>185</v>
@@ -8455,10 +8458,10 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B37" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C37">
         <f>INDEX(autos!$B$3:$B$500,MATCH($B37,autos!$A$3:$A$500,0))</f>
@@ -8472,7 +8475,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B38" t="s">
         <v>133</v>
@@ -8489,10 +8492,10 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B39" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C39">
         <f>INDEX(autos!$B$3:$B$500,MATCH($B39,autos!$A$3:$A$500,0))</f>
@@ -8506,10 +8509,10 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B40" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C40">
         <f>INDEX(pilotos!$B$3:$B$500,MATCH($B40,pilotos!$A$3:$A$500,0))</f>
@@ -8523,10 +8526,10 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B41" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C41">
         <f>INDEX(pilotos!$B$3:$B$500,MATCH($B41,pilotos!$A$3:$A$500,0))</f>
@@ -8540,7 +8543,7 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B42" t="s">
         <v>35</v>
@@ -8557,10 +8560,10 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B43" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C43">
         <f>INDEX(pilotos!$B$3:$B$500,MATCH($B43,pilotos!$A$3:$A$500,0))</f>
@@ -8574,10 +8577,10 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B44" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C44">
         <f>INDEX(pilotos!$B$3:$B$500,MATCH($B44,pilotos!$A$3:$A$500,0))</f>
@@ -8591,7 +8594,7 @@
     </row>
     <row r="46" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C46" s="1" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="N46" s="11">
         <f>SUM(N11:N44)</f>
@@ -10763,7 +10766,7 @@
         <v>185</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>186</v>
       </c>
       <c r="C7">
         <v>650</v>
@@ -10792,10 +10795,10 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C8">
         <v>700</v>
@@ -10827,7 +10830,7 @@
         <v>133</v>
       </c>
       <c r="B9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C9">
         <v>650</v>
@@ -10856,10 +10859,10 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C10">
         <v>900</v>
@@ -10913,37 +10916,37 @@
         <v>164</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="2" ht="78" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -10954,48 +10957,48 @@
         <v>81</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -11036,10 +11039,10 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C4">
         <v>450</v>
@@ -11083,7 +11086,7 @@
         <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C5">
         <v>650</v>
@@ -11124,10 +11127,10 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -11168,10 +11171,10 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B7" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -11238,37 +11241,37 @@
         <v>7</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2" ht="78" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -11276,54 +11279,54 @@
         <v>145</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>81</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D3">
         <v>10</v>
@@ -11361,13 +11364,13 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D4">
         <v>0.1</v>
@@ -11405,13 +11408,13 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D5">
         <v>0.04</v>
@@ -11449,13 +11452,13 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D6">
         <v>0.1</v>
@@ -11496,10 +11499,10 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D7">
         <v>0.05</v>
@@ -11519,13 +11522,13 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C8" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -11542,13 +11545,13 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -11559,13 +11562,13 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -11579,13 +11582,13 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C11" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -11596,13 +11599,13 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B12" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C12" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -11613,13 +11616,13 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B13" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C13" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -11630,13 +11633,13 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B14" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C14" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -11647,13 +11650,13 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B15" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C15" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -11664,13 +11667,13 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B16" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C16" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -11681,13 +11684,13 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B17" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C17" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -11698,13 +11701,13 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B18" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C18" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -11715,13 +11718,13 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B19" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C19" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -11732,13 +11735,13 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B20" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C20" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -11749,13 +11752,13 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B21" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C21" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -11766,13 +11769,13 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B22" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C22" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -11783,13 +11786,13 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B23" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C23" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -11822,40 +11825,40 @@
         <v>7</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="2" ht="78" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -11866,48 +11869,48 @@
         <v>81</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B3" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C3">
         <v>1.6</v>
@@ -11948,10 +11951,10 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C4">
         <v>0.6</v>
@@ -11992,10 +11995,10 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -12036,10 +12039,10 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -12080,10 +12083,10 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B7" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C7">
         <v>0.8</v>
@@ -12143,10 +12146,10 @@
         <v>6</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="2" ht="78" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -12154,725 +12157,725 @@
         <v>145</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B3">
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B4">
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B5">
         <v>0.8</v>
       </c>
       <c r="C5" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B6">
         <v>0.16</v>
       </c>
       <c r="C6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B7">
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B8">
         <v>0.35</v>
       </c>
       <c r="C8" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B9">
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B10">
         <v>0.09</v>
       </c>
       <c r="C10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B11">
         <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B12">
         <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B13">
         <v>0.7</v>
       </c>
       <c r="C13" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B14">
         <v>0.6</v>
       </c>
       <c r="C14" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B15">
         <v>6</v>
       </c>
       <c r="C15" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B16">
         <v>0.5</v>
       </c>
       <c r="C16" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B17">
         <v>0.3</v>
       </c>
       <c r="C17" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B18">
         <v>0.5</v>
       </c>
       <c r="C18" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B19">
         <v>0.1</v>
       </c>
       <c r="C19" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B20">
         <v>3</v>
       </c>
       <c r="C20" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B21">
         <v>5</v>
       </c>
       <c r="C21" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B22">
         <v>1.2</v>
       </c>
       <c r="C22" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B23">
         <v>2</v>
       </c>
       <c r="C23" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B24">
         <v>1.6</v>
       </c>
       <c r="C24" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B25">
         <v>1.3</v>
       </c>
       <c r="C25" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B26">
         <v>2.5</v>
       </c>
       <c r="C26" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B27">
         <v>4.5</v>
       </c>
       <c r="C27" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B28">
         <v>1.6</v>
       </c>
       <c r="C28" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B29">
         <v>0.3</v>
       </c>
       <c r="C29" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B30">
         <v>0.45</v>
       </c>
       <c r="C30" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B31">
         <v>2</v>
       </c>
       <c r="C31" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B32">
         <v>0.7</v>
       </c>
       <c r="C32" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B33">
         <v>0.5</v>
       </c>
       <c r="C33" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B34">
         <v>0.7</v>
       </c>
       <c r="C34" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B35">
         <v>1.4</v>
       </c>
       <c r="C35" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B36">
         <v>2.5</v>
       </c>
       <c r="C36" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B37">
         <v>0.2</v>
       </c>
       <c r="C37" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B38">
         <v>0.28</v>
       </c>
       <c r="C38" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B39">
         <v>1.6</v>
       </c>
       <c r="C39" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B40">
         <v>0.4</v>
       </c>
       <c r="C40" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B41">
         <v>1</v>
       </c>
       <c r="C41" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B42">
         <v>4.5</v>
       </c>
       <c r="C42" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B43">
         <v>2.5</v>
       </c>
       <c r="C43" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B44">
         <v>1.5</v>
       </c>
       <c r="C44" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B45">
         <v>6</v>
       </c>
       <c r="C45" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B46">
         <v>0.6</v>
       </c>
       <c r="C46" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B47">
         <v>3</v>
       </c>
       <c r="C47" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B48">
         <v>1.5</v>
       </c>
       <c r="C48" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B49">
         <v>26</v>
       </c>
       <c r="C49" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B50">
         <v>0.5</v>
       </c>
       <c r="C50" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B51">
         <v>0.35</v>
       </c>
       <c r="C51" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B52">
         <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B53">
         <v>3</v>
       </c>
       <c r="C53" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B54">
         <v>2</v>
       </c>
       <c r="C54" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B55">
         <v>8</v>
       </c>
       <c r="C55" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B56">
         <v>0.25</v>
       </c>
       <c r="C56" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B57">
         <v>4</v>
       </c>
       <c r="C57" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B58">
         <v>30</v>
       </c>
       <c r="C58" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B59">
         <v>0.25</v>
       </c>
       <c r="C59" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B60">
         <v>4</v>
       </c>
       <c r="C60" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B61">
         <v>0.35</v>
       </c>
       <c r="C61" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B62">
         <v>0.3</v>
       </c>
       <c r="C62" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B63">
         <v>1.1</v>
       </c>
       <c r="C63" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B64">
         <v>1.5</v>
       </c>
       <c r="C64" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B65">
         <v>1.25</v>
       </c>
       <c r="C65" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B66">
         <v>1.3</v>
       </c>
       <c r="C66" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B67">
         <v>0.5</v>
       </c>
       <c r="C67" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
   </sheetData>

--- a/balance.xlsx
+++ b/balance.xlsx
@@ -566,40 +566,40 @@
     <t>monster</t>
   </si>
   <si>
-    <t>Crisis de los 40</t>
+    <t>El Loco Cuarentón</t>
   </si>
   <si>
     <t>formula</t>
   </si>
   <si>
-    <t>Multa Pendiente</t>
+    <t>El Apurado</t>
   </si>
   <si>
     <t>tanque</t>
   </si>
   <si>
-    <t>Política Exterior</t>
+    <t>El Suegro</t>
   </si>
   <si>
     <t>carrera</t>
   </si>
   <si>
-    <t>Sin Seguro</t>
+    <t>El Sin Seguro</t>
   </si>
   <si>
     <t>axel</t>
   </si>
   <si>
-    <t>Axel Sin Licencia</t>
-  </si>
-  <si>
-    <t>Diabetes Tipo Turbo</t>
+    <t>El Sin Licencia</t>
+  </si>
+  <si>
+    <t>El Tío del Helado</t>
   </si>
   <si>
     <t>combi</t>
   </si>
   <si>
-    <t>La Combi del Tío Raro</t>
+    <t>El Tío Raro</t>
   </si>
   <si>
     <t>dano_mult</t>
@@ -674,28 +674,28 @@
     <t>soldadito</t>
   </si>
   <si>
-    <t>Sargento Sin Pensión</t>
+    <t>El Sargento Sin Pensión</t>
   </si>
   <si>
     <t>muneca</t>
   </si>
   <si>
-    <t>Doña Trapo, Divorciada</t>
-  </si>
-  <si>
-    <t>Robot en Crisis Existencial</t>
+    <t>La Divorciada de Trapo</t>
+  </si>
+  <si>
+    <t>El Robot en Crisis</t>
   </si>
   <si>
     <t>dino</t>
   </si>
   <si>
-    <t>Rex, Ya No Tan Temible</t>
+    <t>El Rex Jubilado</t>
   </si>
   <si>
     <t>figura</t>
   </si>
   <si>
-    <t>Mega Macho Sin Articulaciones</t>
+    <t>El Mega Macho</t>
   </si>
   <si>
     <t>efecto</t>

--- a/balance.xlsx
+++ b/balance.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1117" uniqueCount="904">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1283" uniqueCount="968">
   <si>
     <t>Balance de Junked Metal. Esta planilla se genera desde src/balance.json (npm run balance:xlsx) y vuelve al juego con npm run balance:import.</t>
   </si>
@@ -731,10 +731,10 @@
     <t>nivel10</t>
   </si>
   <si>
-    <t>mejora, zona o pieza (referencia)</t>
-  </si>
-  <si>
-    <t>Efecto por nivel de la mejora: Chasis +vida, Piñón +fracción de daño, Motor +fracción de velocidad, Imán +fracción, Contador de tuercas +fracción de XP (0 = fijo)</t>
+    <t>mejora, habilidad, arma, zona o pieza (referencia)</t>
+  </si>
+  <si>
+    <t>Efecto por nivel de la mejora: Chasis +vida, Piñón +fracción de daño, Motor +fracción de velocidad, Imán +fracción, Contador de tuercas +fracción de XP, Placa de lata +fracción de blindaje, Cinta aisladora +vida/s, Nafta de encendedor +fracción de turbo (recarga y duración), Paragolpes de fierro +fracción de daño al embestir, Gatillo engrasado −fracción de recarga de armas (0 = fijo; habilidades: ver ritmo habilidad_cd_nivel y habilidad_efecto_nivel)</t>
   </si>
   <si>
     <t>Precio en tornillos del nivel 1 (vacío = ese nivel no existe)</t>
@@ -794,6 +794,36 @@
     <t>Imán de parlante</t>
   </si>
   <si>
+    <t>arm</t>
+  </si>
+  <si>
+    <t>Placa de lata</t>
+  </si>
+  <si>
+    <t>reg</t>
+  </si>
+  <si>
+    <t>Cinta aisladora</t>
+  </si>
+  <si>
+    <t>tur</t>
+  </si>
+  <si>
+    <t>Nafta de encendedor</t>
+  </si>
+  <si>
+    <t>ram</t>
+  </si>
+  <si>
+    <t>Paragolpes de fierro</t>
+  </si>
+  <si>
+    <t>cdr</t>
+  </si>
+  <si>
+    <t>Gatillo engrasado</t>
+  </si>
+  <si>
     <t>Contador de tuercas</t>
   </si>
   <si>
@@ -899,6 +929,153 @@
     <t>Escape Chimeneas</t>
   </si>
   <si>
+    <t>hab_bombardeo</t>
+  </si>
+  <si>
+    <t>habilidad</t>
+  </si>
+  <si>
+    <t>Bombardeo de petardos</t>
+  </si>
+  <si>
+    <t>hab_escudo</t>
+  </si>
+  <si>
+    <t>Escudo que cura</t>
+  </si>
+  <si>
+    <t>hab_emp</t>
+  </si>
+  <si>
+    <t>Pulso EMP</t>
+  </si>
+  <si>
+    <t>hab_lenta</t>
+  </si>
+  <si>
+    <t>Cámara lenta</t>
+  </si>
+  <si>
+    <t>arma_clips</t>
+  </si>
+  <si>
+    <t>arma</t>
+  </si>
+  <si>
+    <t>Lanzaclips</t>
+  </si>
+  <si>
+    <t>arma_chispero</t>
+  </si>
+  <si>
+    <t>arma_agua</t>
+  </si>
+  <si>
+    <t>arma_yoyo</t>
+  </si>
+  <si>
+    <t>Yoyó</t>
+  </si>
+  <si>
+    <t>arma_bengalas</t>
+  </si>
+  <si>
+    <t>arma_regla</t>
+  </si>
+  <si>
+    <t>Regla</t>
+  </si>
+  <si>
+    <t>arma_petardos</t>
+  </si>
+  <si>
+    <t>arma_helado</t>
+  </si>
+  <si>
+    <t>Helado</t>
+  </si>
+  <si>
+    <t>arma_bocina</t>
+  </si>
+  <si>
+    <t>arma_trompo</t>
+  </si>
+  <si>
+    <t>arma_tesla</t>
+  </si>
+  <si>
+    <t>pieza_bumper_cano</t>
+  </si>
+  <si>
+    <t>Paragolpes de caño</t>
+  </si>
+  <si>
+    <t>pieza_bumper_antivuelco</t>
+  </si>
+  <si>
+    <t>Barra antivuelco</t>
+  </si>
+  <si>
+    <t>pieza_bumper_laterales</t>
+  </si>
+  <si>
+    <t>Defensas laterales</t>
+  </si>
+  <si>
+    <t>pieza_tires_oruga</t>
+  </si>
+  <si>
+    <t>Orugas</t>
+  </si>
+  <si>
+    <t>pieza_tires_todoterreno</t>
+  </si>
+  <si>
+    <t>Todoterreno</t>
+  </si>
+  <si>
+    <t>pieza_tires_lisas</t>
+  </si>
+  <si>
+    <t>Lisas de carrera</t>
+  </si>
+  <si>
+    <t>pieza_tires_rayos</t>
+  </si>
+  <si>
+    <t>Rayos de colores</t>
+  </si>
+  <si>
+    <t>pieza_acc_pelotita</t>
+  </si>
+  <si>
+    <t>Antena con pelotita</t>
+  </si>
+  <si>
+    <t>pieza_acc_bocina</t>
+  </si>
+  <si>
+    <t>Bocina de payaso</t>
+  </si>
+  <si>
+    <t>pieza_acc_matafuego</t>
+  </si>
+  <si>
+    <t>Matafuego</t>
+  </si>
+  <si>
+    <t>pieza_acc_dados</t>
+  </si>
+  <si>
+    <t>Dados de peluche</t>
+  </si>
+  <si>
+    <t>pieza_acc_banderita</t>
+  </si>
+  <si>
+    <t>Banderita</t>
+  </si>
+  <si>
     <t>mult_hormiga</t>
   </si>
   <si>
@@ -1967,6 +2144,18 @@
     <t>Cámara lenta: segundos activa</t>
   </si>
   <si>
+    <t>habilidad_cd_nivel</t>
+  </si>
+  <si>
+    <t>Mejora de habilidad (Taller): fracción de enfriamiento que baja por nivel</t>
+  </si>
+  <si>
+    <t>habilidad_efecto_nivel</t>
+  </si>
+  <si>
+    <t>Mejora de habilidad (Taller): fracción de efecto que sube por nivel (petardos, segundos de escudo, aturdido del EMP y de cámara lenta)</t>
+  </si>
+  <si>
     <t>lenta_mundo</t>
   </si>
   <si>
@@ -2105,6 +2294,12 @@
     <t>Combo de manejo: cuánto baja por segundo</t>
   </si>
   <si>
+    <t>tornillos_partida_tipica</t>
+  </si>
+  <si>
+    <t>Tornillos de una partida típica: el Taller lo usa para decir cuántas partidas faltan para pagar algo</t>
+  </si>
+  <si>
     <t>bicho_lento_mult</t>
   </si>
   <si>
@@ -2669,9 +2864,6 @@
     <t>Multiplicador extra de embestida (turbo 1,3; Lápiz-lanza nivel 5: 2,75)</t>
   </si>
   <si>
-    <t>arma</t>
-  </si>
-  <si>
     <t>Embestida</t>
   </si>
   <si>
@@ -2711,7 +2903,7 @@
     <t>Precio ÷ tornillos promedio por partida, por cada nivel de mejora, auto, piloto, zona y pieza. Se recalcula con las hojas precios, autos, pilotos y ritmo.</t>
   </si>
   <si>
-    <t>Tornillos promedio por partida (editable; el taller se calibró con ≈ 100)</t>
+    <t>Tornillos promedio por partida (sale de ritmo tornillos_partida_tipica; el taller lo usa para decir cuántas partidas faltan)</t>
   </si>
   <si>
     <t>Referencia: tiempo medio sobrevivido (s)</t>
@@ -2807,7 +2999,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2826,6 +3018,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3209,7 +3402,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C119"/>
+  <dimension ref="A1:C122"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" style="1" customWidth="1"/>
@@ -3222,10 +3415,10 @@
         <v>6</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>325</v>
+        <v>384</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>326</v>
+        <v>385</v>
       </c>
     </row>
     <row r="2" ht="78" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -3233,1297 +3426,1330 @@
         <v>145</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>327</v>
+        <v>386</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>328</v>
+        <v>387</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>459</v>
+        <v>518</v>
       </c>
       <c r="B3">
         <v>0.5</v>
       </c>
       <c r="C3" t="s">
-        <v>460</v>
+        <v>519</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>461</v>
+        <v>520</v>
       </c>
       <c r="B4">
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>462</v>
+        <v>521</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>463</v>
+        <v>522</v>
       </c>
       <c r="B5">
         <v>1.3</v>
       </c>
       <c r="C5" t="s">
-        <v>464</v>
+        <v>523</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>465</v>
+        <v>524</v>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>466</v>
+        <v>525</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>467</v>
+        <v>526</v>
       </c>
       <c r="B7">
         <v>200</v>
       </c>
       <c r="C7" t="s">
-        <v>468</v>
+        <v>527</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>469</v>
+        <v>528</v>
       </c>
       <c r="B8">
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>470</v>
+        <v>529</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>471</v>
+        <v>530</v>
       </c>
       <c r="B9">
         <v>2.2</v>
       </c>
       <c r="C9" t="s">
-        <v>472</v>
+        <v>531</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>473</v>
+        <v>532</v>
       </c>
       <c r="B10">
         <v>100</v>
       </c>
       <c r="C10" t="s">
-        <v>474</v>
+        <v>533</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>475</v>
+        <v>534</v>
       </c>
       <c r="B11">
         <v>60</v>
       </c>
       <c r="C11" t="s">
-        <v>476</v>
+        <v>535</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>477</v>
+        <v>536</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>478</v>
+        <v>537</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>479</v>
+        <v>538</v>
       </c>
       <c r="B13">
         <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>480</v>
+        <v>539</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>481</v>
+        <v>540</v>
       </c>
       <c r="B14">
         <v>36</v>
       </c>
       <c r="C14" t="s">
-        <v>482</v>
+        <v>541</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>483</v>
+        <v>542</v>
       </c>
       <c r="B15">
         <v>54</v>
       </c>
       <c r="C15" t="s">
-        <v>484</v>
+        <v>543</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>485</v>
+        <v>544</v>
       </c>
       <c r="B16">
         <v>1.6</v>
       </c>
       <c r="C16" t="s">
-        <v>486</v>
+        <v>545</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>487</v>
+        <v>546</v>
       </c>
       <c r="B17">
         <v>75</v>
       </c>
       <c r="C17" t="s">
-        <v>488</v>
+        <v>547</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>489</v>
+        <v>548</v>
       </c>
       <c r="B18">
         <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>490</v>
+        <v>549</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>491</v>
+        <v>550</v>
       </c>
       <c r="B19">
         <v>26</v>
       </c>
       <c r="C19" t="s">
-        <v>492</v>
+        <v>551</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>493</v>
+        <v>552</v>
       </c>
       <c r="B20">
         <v>10</v>
       </c>
       <c r="C20" t="s">
-        <v>494</v>
+        <v>553</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>495</v>
+        <v>554</v>
       </c>
       <c r="B21">
         <v>12</v>
       </c>
       <c r="C21" t="s">
-        <v>496</v>
+        <v>555</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>497</v>
+        <v>556</v>
       </c>
       <c r="B22">
         <v>0.6</v>
       </c>
       <c r="C22" t="s">
-        <v>498</v>
+        <v>557</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>499</v>
+        <v>558</v>
       </c>
       <c r="B23">
         <v>150</v>
       </c>
       <c r="C23" t="s">
-        <v>500</v>
+        <v>559</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>501</v>
+        <v>560</v>
       </c>
       <c r="B24">
         <v>6</v>
       </c>
       <c r="C24" t="s">
-        <v>502</v>
+        <v>561</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>503</v>
+        <v>562</v>
       </c>
       <c r="B25">
         <v>60</v>
       </c>
       <c r="C25" t="s">
-        <v>504</v>
+        <v>563</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>505</v>
+        <v>564</v>
       </c>
       <c r="B26">
         <v>4</v>
       </c>
       <c r="C26" t="s">
-        <v>506</v>
+        <v>565</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>507</v>
+        <v>566</v>
       </c>
       <c r="B27">
         <v>1.2</v>
       </c>
       <c r="C27" t="s">
-        <v>508</v>
+        <v>567</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>509</v>
+        <v>568</v>
       </c>
       <c r="B28">
         <v>90</v>
       </c>
       <c r="C28" t="s">
-        <v>510</v>
+        <v>569</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>511</v>
+        <v>570</v>
       </c>
       <c r="B29">
         <v>0.5</v>
       </c>
       <c r="C29" t="s">
-        <v>512</v>
+        <v>571</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>513</v>
+        <v>572</v>
       </c>
       <c r="B30">
         <v>45</v>
       </c>
       <c r="C30" t="s">
-        <v>514</v>
+        <v>573</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>515</v>
+        <v>574</v>
       </c>
       <c r="B31">
         <v>35</v>
       </c>
       <c r="C31" t="s">
-        <v>516</v>
+        <v>575</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>517</v>
+        <v>576</v>
       </c>
       <c r="B32">
         <v>16</v>
       </c>
       <c r="C32" t="s">
-        <v>518</v>
+        <v>577</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>519</v>
+        <v>578</v>
       </c>
       <c r="B33">
         <v>12</v>
       </c>
       <c r="C33" t="s">
-        <v>520</v>
+        <v>579</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>521</v>
+        <v>580</v>
       </c>
       <c r="B34">
         <v>22</v>
       </c>
       <c r="C34" t="s">
-        <v>522</v>
+        <v>581</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>523</v>
+        <v>582</v>
       </c>
       <c r="B35">
         <v>60</v>
       </c>
       <c r="C35" t="s">
-        <v>524</v>
+        <v>583</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>525</v>
+        <v>584</v>
       </c>
       <c r="B36">
         <v>45</v>
       </c>
       <c r="C36" t="s">
-        <v>526</v>
+        <v>585</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>527</v>
+        <v>586</v>
       </c>
       <c r="B37">
         <v>26</v>
       </c>
       <c r="C37" t="s">
-        <v>528</v>
+        <v>587</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>529</v>
+        <v>588</v>
       </c>
       <c r="B38">
         <v>30</v>
       </c>
       <c r="C38" t="s">
-        <v>530</v>
+        <v>589</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>531</v>
+        <v>590</v>
       </c>
       <c r="B39">
         <v>8</v>
       </c>
       <c r="C39" t="s">
-        <v>532</v>
+        <v>591</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>533</v>
+        <v>592</v>
       </c>
       <c r="B40">
         <v>7</v>
       </c>
       <c r="C40" t="s">
-        <v>534</v>
+        <v>593</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>535</v>
+        <v>594</v>
       </c>
       <c r="B41">
         <v>20</v>
       </c>
       <c r="C41" t="s">
-        <v>536</v>
+        <v>595</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>537</v>
+        <v>596</v>
       </c>
       <c r="B42">
         <v>95</v>
       </c>
       <c r="C42" t="s">
-        <v>538</v>
+        <v>597</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>539</v>
+        <v>598</v>
       </c>
       <c r="B43">
         <v>50</v>
       </c>
       <c r="C43" t="s">
-        <v>540</v>
+        <v>599</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>541</v>
+        <v>600</v>
       </c>
       <c r="B44">
         <v>200</v>
       </c>
       <c r="C44" t="s">
-        <v>542</v>
+        <v>601</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>543</v>
+        <v>602</v>
       </c>
       <c r="B45">
         <v>400</v>
       </c>
       <c r="C45" t="s">
-        <v>544</v>
+        <v>603</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>545</v>
+        <v>604</v>
       </c>
       <c r="B46">
         <v>600</v>
       </c>
       <c r="C46" t="s">
-        <v>546</v>
+        <v>605</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>547</v>
+        <v>606</v>
       </c>
       <c r="B47">
         <v>120</v>
       </c>
       <c r="C47" t="s">
-        <v>548</v>
+        <v>607</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>549</v>
+        <v>608</v>
       </c>
       <c r="B48">
         <v>600</v>
       </c>
       <c r="C48" t="s">
-        <v>550</v>
+        <v>609</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>551</v>
+        <v>610</v>
       </c>
       <c r="B49">
         <v>100</v>
       </c>
       <c r="C49" t="s">
-        <v>552</v>
+        <v>611</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>553</v>
+        <v>612</v>
       </c>
       <c r="B50">
         <v>460</v>
       </c>
       <c r="C50" t="s">
-        <v>554</v>
+        <v>613</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>555</v>
+        <v>614</v>
       </c>
       <c r="B51">
         <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>556</v>
+        <v>615</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>557</v>
+        <v>616</v>
       </c>
       <c r="B52">
         <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>558</v>
+        <v>617</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>559</v>
+        <v>618</v>
       </c>
       <c r="B53">
         <v>2</v>
       </c>
       <c r="C53" t="s">
-        <v>560</v>
+        <v>619</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>561</v>
+        <v>620</v>
       </c>
       <c r="B54">
         <v>0.6</v>
       </c>
       <c r="C54" t="s">
-        <v>562</v>
+        <v>621</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>563</v>
+        <v>622</v>
       </c>
       <c r="B55">
         <v>3</v>
       </c>
       <c r="C55" t="s">
-        <v>564</v>
+        <v>623</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>565</v>
+        <v>624</v>
       </c>
       <c r="B56">
         <v>5</v>
       </c>
       <c r="C56" t="s">
-        <v>566</v>
+        <v>625</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>567</v>
+        <v>626</v>
       </c>
       <c r="B57">
         <v>350</v>
       </c>
       <c r="C57" t="s">
-        <v>568</v>
+        <v>627</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>569</v>
+        <v>628</v>
       </c>
       <c r="B58">
         <v>40</v>
       </c>
       <c r="C58" t="s">
-        <v>570</v>
+        <v>629</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>571</v>
+        <v>630</v>
       </c>
       <c r="B59">
         <v>8</v>
       </c>
       <c r="C59" t="s">
-        <v>572</v>
+        <v>631</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>573</v>
+        <v>632</v>
       </c>
       <c r="B60">
         <v>0.35</v>
       </c>
       <c r="C60" t="s">
-        <v>574</v>
+        <v>633</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>575</v>
+        <v>634</v>
       </c>
       <c r="B61">
         <v>0.035</v>
       </c>
       <c r="C61" t="s">
-        <v>576</v>
+        <v>635</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>577</v>
+        <v>636</v>
       </c>
       <c r="B62">
         <v>0.006</v>
       </c>
       <c r="C62" t="s">
-        <v>578</v>
+        <v>637</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>579</v>
+        <v>638</v>
       </c>
       <c r="B63">
         <v>30</v>
       </c>
       <c r="C63" t="s">
-        <v>580</v>
+        <v>639</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>581</v>
+        <v>640</v>
       </c>
       <c r="B64">
         <v>40</v>
       </c>
       <c r="C64" t="s">
-        <v>582</v>
+        <v>641</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>583</v>
+        <v>642</v>
       </c>
       <c r="B65">
         <v>5</v>
       </c>
       <c r="C65" t="s">
-        <v>584</v>
+        <v>643</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>585</v>
+        <v>644</v>
       </c>
       <c r="B66">
         <v>4</v>
       </c>
       <c r="C66" t="s">
-        <v>586</v>
+        <v>645</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>587</v>
+        <v>646</v>
       </c>
       <c r="B67">
         <v>2.5</v>
       </c>
       <c r="C67" t="s">
-        <v>588</v>
+        <v>647</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>589</v>
+        <v>648</v>
       </c>
       <c r="B68">
         <v>0.3</v>
       </c>
       <c r="C68" t="s">
-        <v>590</v>
+        <v>649</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>591</v>
+        <v>650</v>
       </c>
       <c r="B69">
         <v>25</v>
       </c>
       <c r="C69" t="s">
-        <v>592</v>
+        <v>651</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>593</v>
+        <v>652</v>
       </c>
       <c r="B70">
         <v>20</v>
       </c>
       <c r="C70" t="s">
-        <v>594</v>
+        <v>653</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>595</v>
+        <v>654</v>
       </c>
       <c r="B71">
         <v>25</v>
       </c>
       <c r="C71" t="s">
-        <v>596</v>
+        <v>655</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>597</v>
+        <v>656</v>
       </c>
       <c r="B72">
         <v>0.3</v>
       </c>
       <c r="C72" t="s">
-        <v>598</v>
+        <v>657</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>599</v>
+        <v>658</v>
       </c>
       <c r="B73">
         <v>1.5</v>
       </c>
       <c r="C73" t="s">
-        <v>600</v>
+        <v>659</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>601</v>
+        <v>660</v>
       </c>
       <c r="B74">
         <v>60</v>
       </c>
       <c r="C74" t="s">
-        <v>602</v>
+        <v>661</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>603</v>
+        <v>662</v>
       </c>
       <c r="B75">
         <v>300</v>
       </c>
       <c r="C75" t="s">
-        <v>604</v>
+        <v>663</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>605</v>
+        <v>664</v>
       </c>
       <c r="B76">
         <v>0.25</v>
       </c>
       <c r="C76" t="s">
-        <v>606</v>
+        <v>665</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>607</v>
+        <v>666</v>
       </c>
       <c r="B77">
         <v>0.5</v>
       </c>
       <c r="C77" t="s">
-        <v>608</v>
+        <v>667</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>609</v>
+        <v>668</v>
       </c>
       <c r="B78">
         <v>0.7</v>
       </c>
       <c r="C78" t="s">
-        <v>610</v>
+        <v>669</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>611</v>
+        <v>670</v>
       </c>
       <c r="B79">
         <v>0.8</v>
       </c>
       <c r="C79" t="s">
-        <v>612</v>
+        <v>671</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>613</v>
+        <v>672</v>
       </c>
       <c r="B80">
         <v>0.4</v>
       </c>
       <c r="C80" t="s">
-        <v>614</v>
+        <v>673</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>615</v>
+        <v>674</v>
       </c>
       <c r="B81">
         <v>60</v>
       </c>
       <c r="C81" t="s">
-        <v>616</v>
+        <v>675</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>617</v>
+        <v>676</v>
       </c>
       <c r="B82">
         <v>20</v>
       </c>
       <c r="C82" t="s">
-        <v>618</v>
+        <v>677</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>619</v>
+        <v>678</v>
       </c>
       <c r="B83">
         <v>1.4</v>
       </c>
       <c r="C83" t="s">
-        <v>620</v>
+        <v>679</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>621</v>
+        <v>680</v>
       </c>
       <c r="B84">
         <v>10</v>
       </c>
       <c r="C84" t="s">
-        <v>622</v>
+        <v>681</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>623</v>
+        <v>682</v>
       </c>
       <c r="B85">
         <v>0.12</v>
       </c>
       <c r="C85" t="s">
-        <v>624</v>
+        <v>683</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>625</v>
+        <v>684</v>
       </c>
       <c r="B86">
         <v>3.5</v>
       </c>
       <c r="C86" t="s">
-        <v>626</v>
+        <v>685</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>627</v>
+        <v>686</v>
       </c>
       <c r="B87">
         <v>30</v>
       </c>
       <c r="C87" t="s">
-        <v>628</v>
+        <v>687</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>629</v>
+        <v>688</v>
       </c>
       <c r="B88">
         <v>25</v>
       </c>
       <c r="C88" t="s">
-        <v>630</v>
+        <v>689</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>631</v>
+        <v>690</v>
       </c>
       <c r="B89">
         <v>3</v>
       </c>
       <c r="C89" t="s">
-        <v>632</v>
+        <v>691</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>633</v>
+        <v>692</v>
       </c>
       <c r="B90">
         <v>0.1</v>
       </c>
       <c r="C90" t="s">
-        <v>634</v>
+        <v>693</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>635</v>
+        <v>694</v>
       </c>
       <c r="B91">
         <v>18</v>
       </c>
       <c r="C91" t="s">
-        <v>636</v>
+        <v>695</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>637</v>
+        <v>696</v>
       </c>
       <c r="B92">
         <v>0.4</v>
       </c>
       <c r="C92" t="s">
-        <v>638</v>
+        <v>697</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>639</v>
+        <v>698</v>
       </c>
       <c r="B93">
         <v>14</v>
       </c>
       <c r="C93" t="s">
-        <v>640</v>
+        <v>699</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>641</v>
+        <v>700</v>
       </c>
       <c r="B94">
         <v>2</v>
       </c>
       <c r="C94" t="s">
-        <v>642</v>
+        <v>701</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>643</v>
+        <v>702</v>
       </c>
       <c r="B95">
         <v>25</v>
       </c>
       <c r="C95" t="s">
-        <v>644</v>
+        <v>703</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>645</v>
+        <v>704</v>
       </c>
       <c r="B96">
         <v>3</v>
       </c>
       <c r="C96" t="s">
-        <v>646</v>
+        <v>705</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>647</v>
+        <v>706</v>
       </c>
       <c r="B97">
-        <v>0.4</v>
+        <v>0.08</v>
       </c>
       <c r="C97" t="s">
-        <v>648</v>
+        <v>707</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>649</v>
+        <v>708</v>
       </c>
       <c r="B98">
-        <v>40</v>
+        <v>0.15</v>
       </c>
       <c r="C98" t="s">
-        <v>650</v>
+        <v>709</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>651</v>
+        <v>710</v>
       </c>
       <c r="B99">
-        <v>1.55</v>
+        <v>0.4</v>
       </c>
       <c r="C99" t="s">
-        <v>652</v>
+        <v>711</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>653</v>
+        <v>712</v>
       </c>
       <c r="B100">
-        <v>1.8</v>
+        <v>40</v>
       </c>
       <c r="C100" t="s">
-        <v>654</v>
+        <v>713</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>655</v>
+        <v>714</v>
       </c>
       <c r="B101">
-        <v>3</v>
+        <v>1.55</v>
       </c>
       <c r="C101" t="s">
-        <v>656</v>
+        <v>715</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>657</v>
+        <v>716</v>
       </c>
       <c r="B102">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="C102" t="s">
-        <v>658</v>
+        <v>717</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>659</v>
+        <v>718</v>
       </c>
       <c r="B103">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="C103" t="s">
-        <v>660</v>
+        <v>719</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>661</v>
+        <v>720</v>
       </c>
       <c r="B104">
-        <v>5</v>
+        <v>1.3</v>
       </c>
       <c r="C104" t="s">
-        <v>662</v>
+        <v>721</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>663</v>
+        <v>722</v>
       </c>
       <c r="B105">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="C105" t="s">
-        <v>664</v>
+        <v>723</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>665</v>
+        <v>724</v>
       </c>
       <c r="B106">
-        <v>1.3</v>
+        <v>5</v>
       </c>
       <c r="C106" t="s">
-        <v>666</v>
+        <v>725</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>667</v>
+        <v>726</v>
       </c>
       <c r="B107">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="C107" t="s">
-        <v>668</v>
+        <v>727</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>669</v>
+        <v>728</v>
       </c>
       <c r="B108">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="C108" t="s">
-        <v>670</v>
+        <v>729</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>671</v>
+        <v>730</v>
       </c>
       <c r="B109">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="C109" t="s">
-        <v>672</v>
+        <v>731</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>673</v>
+        <v>732</v>
       </c>
       <c r="B110">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="C110" t="s">
-        <v>674</v>
+        <v>733</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>675</v>
+        <v>734</v>
       </c>
       <c r="B111">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="C111" t="s">
-        <v>676</v>
+        <v>735</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>677</v>
+        <v>736</v>
       </c>
       <c r="B112">
-        <v>14</v>
+        <v>0.8</v>
       </c>
       <c r="C112" t="s">
-        <v>678</v>
+        <v>737</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>679</v>
+        <v>738</v>
       </c>
       <c r="B113">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="C113" t="s">
-        <v>680</v>
+        <v>739</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>681</v>
+        <v>740</v>
       </c>
       <c r="B114">
-        <v>0.2</v>
+        <v>14</v>
       </c>
       <c r="C114" t="s">
-        <v>682</v>
+        <v>741</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>683</v>
+        <v>742</v>
       </c>
       <c r="B115">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="C115" t="s">
-        <v>684</v>
+        <v>743</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>685</v>
+        <v>744</v>
       </c>
       <c r="B116">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="C116" t="s">
-        <v>686</v>
+        <v>745</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>687</v>
+        <v>746</v>
       </c>
       <c r="B117">
-        <v>1.5</v>
+        <v>0.1</v>
       </c>
       <c r="C117" t="s">
-        <v>688</v>
+        <v>747</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>689</v>
+        <v>748</v>
       </c>
       <c r="B118">
-        <v>8</v>
+        <v>0.1</v>
       </c>
       <c r="C118" t="s">
-        <v>690</v>
+        <v>749</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>691</v>
+        <v>750</v>
       </c>
       <c r="B119">
+        <v>1.5</v>
+      </c>
+      <c r="C119" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="B120">
+        <v>8</v>
+      </c>
+      <c r="C120" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="B121">
         <v>0.1</v>
       </c>
-      <c r="C119" t="s">
-        <v>692</v>
+      <c r="C121" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="B122">
+        <v>100</v>
+      </c>
+      <c r="C122" t="s">
+        <v>757</v>
       </c>
     </row>
   </sheetData>
@@ -4547,10 +4773,10 @@
         <v>6</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>325</v>
+        <v>384</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>326</v>
+        <v>385</v>
       </c>
     </row>
     <row r="2" ht="78" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -4558,1011 +4784,1011 @@
         <v>145</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>327</v>
+        <v>386</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>328</v>
+        <v>387</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>693</v>
+        <v>758</v>
       </c>
       <c r="B3">
         <v>0.45</v>
       </c>
       <c r="C3" t="s">
-        <v>694</v>
+        <v>759</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>695</v>
+        <v>760</v>
       </c>
       <c r="B4">
         <v>0.8</v>
       </c>
       <c r="C4" t="s">
-        <v>696</v>
+        <v>761</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>697</v>
+        <v>762</v>
       </c>
       <c r="B5">
         <v>0.5</v>
       </c>
       <c r="C5" t="s">
-        <v>698</v>
+        <v>763</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>699</v>
+        <v>764</v>
       </c>
       <c r="B6">
         <v>0.5</v>
       </c>
       <c r="C6" t="s">
-        <v>700</v>
+        <v>765</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>701</v>
+        <v>766</v>
       </c>
       <c r="B7">
         <v>1.5</v>
       </c>
       <c r="C7" t="s">
-        <v>702</v>
+        <v>767</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>703</v>
+        <v>768</v>
       </c>
       <c r="B8">
         <v>1.2</v>
       </c>
       <c r="C8" t="s">
-        <v>704</v>
+        <v>769</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>705</v>
+        <v>770</v>
       </c>
       <c r="B9">
         <v>1.7</v>
       </c>
       <c r="C9" t="s">
-        <v>706</v>
+        <v>771</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>707</v>
+        <v>772</v>
       </c>
       <c r="B10">
         <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>708</v>
+        <v>773</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>709</v>
+        <v>774</v>
       </c>
       <c r="B11">
         <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>710</v>
+        <v>775</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>711</v>
+        <v>776</v>
       </c>
       <c r="B12">
         <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>712</v>
+        <v>777</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>713</v>
+        <v>778</v>
       </c>
       <c r="B13">
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>714</v>
+        <v>779</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>715</v>
+        <v>780</v>
       </c>
       <c r="B14">
         <v>10</v>
       </c>
       <c r="C14" t="s">
-        <v>716</v>
+        <v>781</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>717</v>
+        <v>782</v>
       </c>
       <c r="B15">
         <v>1.2</v>
       </c>
       <c r="C15" t="s">
-        <v>718</v>
+        <v>783</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>719</v>
+        <v>784</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>720</v>
+        <v>785</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>721</v>
+        <v>786</v>
       </c>
       <c r="B17">
         <v>2.6</v>
       </c>
       <c r="C17" t="s">
-        <v>722</v>
+        <v>787</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>723</v>
+        <v>788</v>
       </c>
       <c r="B18">
         <v>1.4</v>
       </c>
       <c r="C18" t="s">
-        <v>724</v>
+        <v>789</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>725</v>
+        <v>790</v>
       </c>
       <c r="B19">
         <v>16</v>
       </c>
       <c r="C19" t="s">
-        <v>726</v>
+        <v>791</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>727</v>
+        <v>792</v>
       </c>
       <c r="B20">
         <v>2.6</v>
       </c>
       <c r="C20" t="s">
-        <v>728</v>
+        <v>793</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>729</v>
+        <v>794</v>
       </c>
       <c r="B21">
         <v>4</v>
       </c>
       <c r="C21" t="s">
-        <v>730</v>
+        <v>795</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>731</v>
+        <v>796</v>
       </c>
       <c r="B22">
         <v>3</v>
       </c>
       <c r="C22" t="s">
-        <v>732</v>
+        <v>797</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>733</v>
+        <v>798</v>
       </c>
       <c r="B23">
         <v>1.5</v>
       </c>
       <c r="C23" t="s">
-        <v>734</v>
+        <v>799</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>735</v>
+        <v>800</v>
       </c>
       <c r="B24">
         <v>1.7</v>
       </c>
       <c r="C24" t="s">
-        <v>736</v>
+        <v>801</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>737</v>
+        <v>802</v>
       </c>
       <c r="B25">
         <v>0.7</v>
       </c>
       <c r="C25" t="s">
-        <v>738</v>
+        <v>803</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>739</v>
+        <v>804</v>
       </c>
       <c r="B26">
         <v>3</v>
       </c>
       <c r="C26" t="s">
-        <v>740</v>
+        <v>805</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>741</v>
+        <v>806</v>
       </c>
       <c r="B27">
         <v>3</v>
       </c>
       <c r="C27" t="s">
-        <v>742</v>
+        <v>807</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>743</v>
+        <v>808</v>
       </c>
       <c r="B28">
         <v>5</v>
       </c>
       <c r="C28" t="s">
-        <v>744</v>
+        <v>809</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>745</v>
+        <v>810</v>
       </c>
       <c r="B29">
         <v>1.1</v>
       </c>
       <c r="C29" t="s">
-        <v>746</v>
+        <v>811</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>747</v>
+        <v>812</v>
       </c>
       <c r="B30">
         <v>6</v>
       </c>
       <c r="C30" t="s">
-        <v>748</v>
+        <v>813</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>749</v>
+        <v>814</v>
       </c>
       <c r="B31">
         <v>0.16</v>
       </c>
       <c r="C31" t="s">
-        <v>750</v>
+        <v>815</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>751</v>
+        <v>816</v>
       </c>
       <c r="B32">
         <v>3</v>
       </c>
       <c r="C32" t="s">
-        <v>752</v>
+        <v>817</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>753</v>
+        <v>818</v>
       </c>
       <c r="B33">
         <v>1.3</v>
       </c>
       <c r="C33" t="s">
-        <v>754</v>
+        <v>819</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>755</v>
+        <v>820</v>
       </c>
       <c r="B34">
         <v>22</v>
       </c>
       <c r="C34" t="s">
-        <v>756</v>
+        <v>821</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>757</v>
+        <v>822</v>
       </c>
       <c r="B35">
         <v>2.5</v>
       </c>
       <c r="C35" t="s">
-        <v>758</v>
+        <v>823</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>759</v>
+        <v>824</v>
       </c>
       <c r="B36">
         <v>0.5</v>
       </c>
       <c r="C36" t="s">
-        <v>760</v>
+        <v>825</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>761</v>
+        <v>826</v>
       </c>
       <c r="B37">
         <v>20</v>
       </c>
       <c r="C37" t="s">
-        <v>762</v>
+        <v>827</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>763</v>
+        <v>828</v>
       </c>
       <c r="B38">
         <v>1.4</v>
       </c>
       <c r="C38" t="s">
-        <v>764</v>
+        <v>829</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>765</v>
+        <v>830</v>
       </c>
       <c r="B39">
         <v>2.6</v>
       </c>
       <c r="C39" t="s">
-        <v>766</v>
+        <v>831</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>767</v>
+        <v>832</v>
       </c>
       <c r="B40">
         <v>2</v>
       </c>
       <c r="C40" t="s">
-        <v>768</v>
+        <v>833</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>769</v>
+        <v>834</v>
       </c>
       <c r="B41">
         <v>9</v>
       </c>
       <c r="C41" t="s">
-        <v>770</v>
+        <v>835</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>771</v>
+        <v>836</v>
       </c>
       <c r="B42">
         <v>12</v>
       </c>
       <c r="C42" t="s">
-        <v>772</v>
+        <v>837</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>773</v>
+        <v>838</v>
       </c>
       <c r="B43">
         <v>0.8</v>
       </c>
       <c r="C43" t="s">
-        <v>774</v>
+        <v>839</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>775</v>
+        <v>840</v>
       </c>
       <c r="B44">
         <v>3</v>
       </c>
       <c r="C44" t="s">
-        <v>776</v>
+        <v>841</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>777</v>
+        <v>842</v>
       </c>
       <c r="B45">
         <v>0.3</v>
       </c>
       <c r="C45" t="s">
-        <v>778</v>
+        <v>843</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>779</v>
+        <v>844</v>
       </c>
       <c r="B46">
         <v>7</v>
       </c>
       <c r="C46" t="s">
-        <v>780</v>
+        <v>845</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>781</v>
+        <v>846</v>
       </c>
       <c r="B47">
         <v>0.2</v>
       </c>
       <c r="C47" t="s">
-        <v>782</v>
+        <v>847</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>783</v>
+        <v>848</v>
       </c>
       <c r="B48">
         <v>3.5</v>
       </c>
       <c r="C48" t="s">
-        <v>784</v>
+        <v>849</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>785</v>
+        <v>850</v>
       </c>
       <c r="B49">
         <v>16</v>
       </c>
       <c r="C49" t="s">
-        <v>786</v>
+        <v>851</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>787</v>
+        <v>852</v>
       </c>
       <c r="B50">
         <v>1</v>
       </c>
       <c r="C50" t="s">
-        <v>788</v>
+        <v>853</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>789</v>
+        <v>854</v>
       </c>
       <c r="B51">
         <v>10</v>
       </c>
       <c r="C51" t="s">
-        <v>790</v>
+        <v>855</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>791</v>
+        <v>856</v>
       </c>
       <c r="B52">
         <v>2.2</v>
       </c>
       <c r="C52" t="s">
-        <v>792</v>
+        <v>857</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>793</v>
+        <v>858</v>
       </c>
       <c r="B53">
         <v>4</v>
       </c>
       <c r="C53" t="s">
-        <v>794</v>
+        <v>859</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>795</v>
+        <v>860</v>
       </c>
       <c r="B54">
         <v>14</v>
       </c>
       <c r="C54" t="s">
-        <v>796</v>
+        <v>861</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>797</v>
+        <v>862</v>
       </c>
       <c r="B55">
         <v>8</v>
       </c>
       <c r="C55" t="s">
-        <v>798</v>
+        <v>863</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>799</v>
+        <v>864</v>
       </c>
       <c r="B56">
         <v>28</v>
       </c>
       <c r="C56" t="s">
-        <v>800</v>
+        <v>865</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>801</v>
+        <v>866</v>
       </c>
       <c r="B57">
         <v>6</v>
       </c>
       <c r="C57" t="s">
-        <v>802</v>
+        <v>867</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>803</v>
+        <v>868</v>
       </c>
       <c r="B58">
         <v>0.5</v>
       </c>
       <c r="C58" t="s">
-        <v>804</v>
+        <v>869</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>805</v>
+        <v>870</v>
       </c>
       <c r="B59">
         <v>45</v>
       </c>
       <c r="C59" t="s">
-        <v>806</v>
+        <v>871</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>807</v>
+        <v>872</v>
       </c>
       <c r="B60">
         <v>0.4</v>
       </c>
       <c r="C60" t="s">
-        <v>808</v>
+        <v>873</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>809</v>
+        <v>874</v>
       </c>
       <c r="B61">
         <v>0.35</v>
       </c>
       <c r="C61" t="s">
-        <v>810</v>
+        <v>875</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>811</v>
+        <v>876</v>
       </c>
       <c r="B62">
         <v>1</v>
       </c>
       <c r="C62" t="s">
-        <v>812</v>
+        <v>877</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>813</v>
+        <v>878</v>
       </c>
       <c r="B63">
         <v>24</v>
       </c>
       <c r="C63" t="s">
-        <v>814</v>
+        <v>879</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>815</v>
+        <v>880</v>
       </c>
       <c r="B64">
         <v>1.2</v>
       </c>
       <c r="C64" t="s">
-        <v>816</v>
+        <v>881</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>817</v>
+        <v>882</v>
       </c>
       <c r="B65">
         <v>0.6</v>
       </c>
       <c r="C65" t="s">
-        <v>818</v>
+        <v>883</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>819</v>
+        <v>884</v>
       </c>
       <c r="B66">
         <v>1.8</v>
       </c>
       <c r="C66" t="s">
-        <v>820</v>
+        <v>885</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>821</v>
+        <v>886</v>
       </c>
       <c r="B67">
         <v>17</v>
       </c>
       <c r="C67" t="s">
-        <v>822</v>
+        <v>887</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>823</v>
+        <v>888</v>
       </c>
       <c r="B68">
         <v>1.5</v>
       </c>
       <c r="C68" t="s">
-        <v>824</v>
+        <v>889</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>825</v>
+        <v>890</v>
       </c>
       <c r="B69">
         <v>1.5</v>
       </c>
       <c r="C69" t="s">
-        <v>826</v>
+        <v>891</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>827</v>
+        <v>892</v>
       </c>
       <c r="B70">
         <v>0.55</v>
       </c>
       <c r="C70" t="s">
-        <v>828</v>
+        <v>893</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>829</v>
+        <v>894</v>
       </c>
       <c r="B71">
         <v>26</v>
       </c>
       <c r="C71" t="s">
-        <v>830</v>
+        <v>895</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>831</v>
+        <v>896</v>
       </c>
       <c r="B72">
         <v>1.2</v>
       </c>
       <c r="C72" t="s">
-        <v>832</v>
+        <v>897</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>833</v>
+        <v>898</v>
       </c>
       <c r="B73">
         <v>1.5</v>
       </c>
       <c r="C73" t="s">
-        <v>834</v>
+        <v>899</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>835</v>
+        <v>900</v>
       </c>
       <c r="B74">
         <v>10</v>
       </c>
       <c r="C74" t="s">
-        <v>836</v>
+        <v>901</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>837</v>
+        <v>902</v>
       </c>
       <c r="B75">
         <v>4</v>
       </c>
       <c r="C75" t="s">
-        <v>838</v>
+        <v>903</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>839</v>
+        <v>904</v>
       </c>
       <c r="B76">
         <v>40</v>
       </c>
       <c r="C76" t="s">
-        <v>840</v>
+        <v>905</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>841</v>
+        <v>906</v>
       </c>
       <c r="B77">
         <v>0.35</v>
       </c>
       <c r="C77" t="s">
-        <v>842</v>
+        <v>907</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>843</v>
+        <v>908</v>
       </c>
       <c r="B78">
         <v>0.25</v>
       </c>
       <c r="C78" t="s">
-        <v>844</v>
+        <v>909</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>845</v>
+        <v>910</v>
       </c>
       <c r="B79">
         <v>0.25</v>
       </c>
       <c r="C79" t="s">
-        <v>846</v>
+        <v>911</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>847</v>
+        <v>912</v>
       </c>
       <c r="B80">
         <v>25</v>
       </c>
       <c r="C80" t="s">
-        <v>848</v>
+        <v>913</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>849</v>
+        <v>914</v>
       </c>
       <c r="B81">
         <v>3.8</v>
       </c>
       <c r="C81" t="s">
-        <v>850</v>
+        <v>915</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>851</v>
+        <v>916</v>
       </c>
       <c r="B82">
         <v>2.6</v>
       </c>
       <c r="C82" t="s">
-        <v>852</v>
+        <v>917</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>853</v>
+        <v>918</v>
       </c>
       <c r="B83">
         <v>2.6</v>
       </c>
       <c r="C83" t="s">
-        <v>854</v>
+        <v>919</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>855</v>
+        <v>920</v>
       </c>
       <c r="B84">
         <v>2.1</v>
       </c>
       <c r="C84" t="s">
-        <v>856</v>
+        <v>921</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>857</v>
+        <v>922</v>
       </c>
       <c r="B85">
         <v>1.6</v>
       </c>
       <c r="C85" t="s">
-        <v>858</v>
+        <v>923</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>859</v>
+        <v>924</v>
       </c>
       <c r="B86">
         <v>1.2</v>
       </c>
       <c r="C86" t="s">
-        <v>860</v>
+        <v>925</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>861</v>
+        <v>926</v>
       </c>
       <c r="B87">
         <v>1</v>
       </c>
       <c r="C87" t="s">
-        <v>862</v>
+        <v>927</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>863</v>
+        <v>928</v>
       </c>
       <c r="B88">
         <v>0.75</v>
       </c>
       <c r="C88" t="s">
-        <v>852</v>
+        <v>917</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>864</v>
+        <v>929</v>
       </c>
       <c r="B89">
         <v>30</v>
       </c>
       <c r="C89" t="s">
-        <v>865</v>
+        <v>930</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>866</v>
+        <v>931</v>
       </c>
       <c r="B90">
         <v>26</v>
       </c>
       <c r="C90" t="s">
-        <v>867</v>
+        <v>932</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>868</v>
+        <v>933</v>
       </c>
       <c r="B91">
         <v>2.6</v>
       </c>
       <c r="C91" t="s">
-        <v>869</v>
+        <v>934</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>870</v>
+        <v>935</v>
       </c>
       <c r="B92">
         <v>0.9</v>
       </c>
       <c r="C92" t="s">
-        <v>871</v>
+        <v>936</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>872</v>
+        <v>937</v>
       </c>
       <c r="B93">
         <v>1.4</v>
       </c>
       <c r="C93" t="s">
-        <v>873</v>
+        <v>938</v>
       </c>
     </row>
   </sheetData>
@@ -5585,17 +5811,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>874</v>
+        <v>939</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>875</v>
+        <v>940</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>876</v>
+        <v>941</v>
       </c>
       <c r="B4" s="7">
         <v>0</v>
@@ -5603,7 +5829,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>877</v>
+        <v>942</v>
       </c>
       <c r="B5" s="7">
         <v>1</v>
@@ -5611,7 +5837,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>878</v>
+        <v>943</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>177</v>
@@ -5619,7 +5845,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>879</v>
+        <v>944</v>
       </c>
       <c r="B7" s="7">
         <v>12</v>
@@ -5627,7 +5853,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>880</v>
+        <v>945</v>
       </c>
       <c r="B8" s="7">
         <v>1</v>
@@ -5635,7 +5861,7 @@
     </row>
     <row r="9" spans="4:29" x14ac:dyDescent="0.25">
       <c r="D9" s="8" t="s">
-        <v>881</v>
+        <v>311</v>
       </c>
       <c r="E9" s="8">
         <f>INDEX(armas!$B$3:$B$500,MATCH(E$10,armas!$A$3:$A$500,0))</f>
@@ -5710,12 +5936,12 @@
         <f>INDEX(armas!$B$3:$B$500,MATCH(AB$10,armas!$A$3:$A$500,0))</f>
       </c>
       <c r="AC9" s="8" t="s">
-        <v>882</v>
+        <v>946</v>
       </c>
     </row>
     <row r="10" spans="4:29" x14ac:dyDescent="0.25">
       <c r="D10" s="9" t="s">
-        <v>883</v>
+        <v>947</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>105</v>
@@ -5795,7 +6021,7 @@
     </row>
     <row r="11" spans="4:28" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>884</v>
+        <v>948</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -5881,7 +6107,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>885</v>
+        <v>949</v>
       </c>
       <c r="E12" s="10">
         <f>(INDEX(armas!$D$3:$D$500,MATCH(E$10,armas!$A$3:$A$500,0))+INDEX(armas!$E$3:$E$500,MATCH(E$10,armas!$A$3:$A$500,0))*E$11)*$B$5</f>
@@ -7137,17 +7363,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>886</v>
+        <v>950</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>887</v>
+        <v>951</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>888</v>
+        <v>952</v>
       </c>
       <c r="B4" s="7">
         <v>0.8</v>
@@ -7164,16 +7390,16 @@
         <v>8</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>889</v>
+        <v>953</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>890</v>
+        <v>954</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>891</v>
+        <v>955</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>892</v>
+        <v>956</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -7345,7 +7571,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N46"/>
+  <dimension ref="A1:N78"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="70" customWidth="1"/>
@@ -7355,25 +7581,25 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>893</v>
+        <v>957</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>894</v>
+        <v>958</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>895</v>
-      </c>
-      <c r="B4" s="7">
-        <v>100</v>
+        <v>959</v>
+      </c>
+      <c r="B4" s="12">
+        <f>INDEX(ritmo!$B$3:$B$500,MATCH("tornillos_partida_tipica",ritmo!$A$3:$A$500,0))</f>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>896</v>
+        <v>960</v>
       </c>
       <c r="B5" s="7">
         <v>420</v>
@@ -7381,7 +7607,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>897</v>
+        <v>961</v>
       </c>
       <c r="B6" s="7">
         <v>600</v>
@@ -7389,7 +7615,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>898</v>
+        <v>962</v>
       </c>
       <c r="B7" s="7">
         <v>1</v>
@@ -7397,7 +7623,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>899</v>
+        <v>963</v>
       </c>
       <c r="B8">
         <f>INT((B7*INDEX(ritmo!$B$3:$B$500,MATCH("tornillos_jefe",ritmo!$A$3:$A$500,0))+INT(B5/INDEX(ritmo!$B$3:$B$500,MATCH("tornillos_div_tiempo",ritmo!$A$3:$A$500,0)))+INT(B6*INDEX(ritmo!$B$3:$B$500,MATCH("dureza_xp",ritmo!$A$3:$A$500,0))/INDEX(ritmo!$B$3:$B$500,MATCH("tornillos_div_bajas",ritmo!$A$3:$A$500,0)))))</f>
@@ -7444,7 +7670,7 @@
         <v>234</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>900</v>
+        <v>964</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -7628,7 +7854,7 @@
         <v>248</v>
       </c>
       <c r="B15" t="s">
-        <v>13</v>
+        <v>256</v>
       </c>
       <c r="C15">
         <f>INDEX(precios!$C$3:$C$500,MATCH($B15,precios!$A$3:$A$500,0))</f>
@@ -7672,7 +7898,7 @@
         <v>248</v>
       </c>
       <c r="B16" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C16">
         <f>INDEX(precios!$C$3:$C$500,MATCH($B16,precios!$A$3:$A$500,0))</f>
@@ -7716,7 +7942,7 @@
         <v>248</v>
       </c>
       <c r="B17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C17">
         <f>INDEX(precios!$C$3:$C$500,MATCH($B17,precios!$A$3:$A$500,0))</f>
@@ -7760,7 +7986,7 @@
         <v>248</v>
       </c>
       <c r="B18" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C18">
         <f>INDEX(precios!$C$3:$C$500,MATCH($B18,precios!$A$3:$A$500,0))</f>
@@ -7804,7 +8030,7 @@
         <v>248</v>
       </c>
       <c r="B19" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C19">
         <f>INDEX(precios!$C$3:$C$500,MATCH($B19,precios!$A$3:$A$500,0))</f>
@@ -7845,10 +8071,10 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>266</v>
+        <v>248</v>
       </c>
       <c r="B20" t="s">
-        <v>265</v>
+        <v>13</v>
       </c>
       <c r="C20">
         <f>INDEX(precios!$C$3:$C$500,MATCH($B20,precios!$A$3:$A$500,0))</f>
@@ -7889,10 +8115,10 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>266</v>
+        <v>248</v>
       </c>
       <c r="B21" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C21">
         <f>INDEX(precios!$C$3:$C$500,MATCH($B21,precios!$A$3:$A$500,0))</f>
@@ -7933,10 +8159,10 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>271</v>
+        <v>248</v>
       </c>
       <c r="B22" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C22">
         <f>INDEX(precios!$C$3:$C$500,MATCH($B22,precios!$A$3:$A$500,0))</f>
@@ -7977,10 +8203,10 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>248</v>
+      </c>
+      <c r="B23" t="s">
         <v>271</v>
-      </c>
-      <c r="B23" t="s">
-        <v>273</v>
       </c>
       <c r="C23">
         <f>INDEX(precios!$C$3:$C$500,MATCH($B23,precios!$A$3:$A$500,0))</f>
@@ -8021,10 +8247,10 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>271</v>
+        <v>248</v>
       </c>
       <c r="B24" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C24">
         <f>INDEX(precios!$C$3:$C$500,MATCH($B24,precios!$A$3:$A$500,0))</f>
@@ -8065,10 +8291,10 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B25" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C25">
         <f>INDEX(precios!$C$3:$C$500,MATCH($B25,precios!$A$3:$A$500,0))</f>
@@ -8109,10 +8335,10 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B26" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C26">
         <f>INDEX(precios!$C$3:$C$500,MATCH($B26,precios!$A$3:$A$500,0))</f>
@@ -8153,10 +8379,10 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="B27" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C27">
         <f>INDEX(precios!$C$3:$C$500,MATCH($B27,precios!$A$3:$A$500,0))</f>
@@ -8197,7 +8423,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="B28" t="s">
         <v>283</v>
@@ -8241,7 +8467,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="B29" t="s">
         <v>285</v>
@@ -8285,7 +8511,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="B30" t="s">
         <v>287</v>
@@ -8329,7 +8555,7 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="B31" t="s">
         <v>289</v>
@@ -8373,16 +8599,43 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>901</v>
+        <v>281</v>
       </c>
       <c r="B32" t="s">
-        <v>177</v>
+        <v>291</v>
       </c>
       <c r="C32">
-        <f>INDEX(autos!$B$3:$B$500,MATCH($B32,autos!$A$3:$A$500,0))</f>
+        <f>INDEX(precios!$C$3:$C$500,MATCH($B32,precios!$A$3:$A$500,0))</f>
       </c>
       <c r="D32" s="11">
-        <f>IF(INDEX(autos!$C$3:$C$500,MATCH($B32,autos!$A$3:$A$500,0))&gt;0,INDEX(autos!$C$3:$C$500,MATCH($B32,autos!$A$3:$A$500,0))/$B$4,"")</f>
+        <f>IF(INDEX(precios!$E$3:$E$500,MATCH($B32,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$E$3:$E$500,MATCH($B32,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="E32" s="11">
+        <f>IF(INDEX(precios!$F$3:$F$500,MATCH($B32,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$F$3:$F$500,MATCH($B32,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="F32" s="11">
+        <f>IF(INDEX(precios!$G$3:$G$500,MATCH($B32,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$G$3:$G$500,MATCH($B32,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="G32" s="11">
+        <f>IF(INDEX(precios!$H$3:$H$500,MATCH($B32,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$H$3:$H$500,MATCH($B32,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="H32" s="11">
+        <f>IF(INDEX(precios!$I$3:$I$500,MATCH($B32,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$I$3:$I$500,MATCH($B32,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="I32" s="11">
+        <f>IF(INDEX(precios!$J$3:$J$500,MATCH($B32,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$J$3:$J$500,MATCH($B32,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="J32" s="11">
+        <f>IF(INDEX(precios!$K$3:$K$500,MATCH($B32,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$K$3:$K$500,MATCH($B32,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="K32" s="11">
+        <f>IF(INDEX(precios!$L$3:$L$500,MATCH($B32,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$L$3:$L$500,MATCH($B32,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="L32" s="11">
+        <f>IF(INDEX(precios!$M$3:$M$500,MATCH($B32,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$M$3:$M$500,MATCH($B32,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="M32" s="11">
+        <f>IF(INDEX(precios!$N$3:$N$500,MATCH($B32,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$N$3:$N$500,MATCH($B32,precios!$A$3:$A$500,0))/$B$4,"")</f>
       </c>
       <c r="N32" s="11">
         <f>SUM(D32:M32)</f>
@@ -8390,16 +8643,43 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>901</v>
+        <v>281</v>
       </c>
       <c r="B33" t="s">
-        <v>179</v>
+        <v>293</v>
       </c>
       <c r="C33">
-        <f>INDEX(autos!$B$3:$B$500,MATCH($B33,autos!$A$3:$A$500,0))</f>
+        <f>INDEX(precios!$C$3:$C$500,MATCH($B33,precios!$A$3:$A$500,0))</f>
       </c>
       <c r="D33" s="11">
-        <f>IF(INDEX(autos!$C$3:$C$500,MATCH($B33,autos!$A$3:$A$500,0))&gt;0,INDEX(autos!$C$3:$C$500,MATCH($B33,autos!$A$3:$A$500,0))/$B$4,"")</f>
+        <f>IF(INDEX(precios!$E$3:$E$500,MATCH($B33,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$E$3:$E$500,MATCH($B33,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="E33" s="11">
+        <f>IF(INDEX(precios!$F$3:$F$500,MATCH($B33,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$F$3:$F$500,MATCH($B33,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="F33" s="11">
+        <f>IF(INDEX(precios!$G$3:$G$500,MATCH($B33,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$G$3:$G$500,MATCH($B33,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="G33" s="11">
+        <f>IF(INDEX(precios!$H$3:$H$500,MATCH($B33,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$H$3:$H$500,MATCH($B33,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="H33" s="11">
+        <f>IF(INDEX(precios!$I$3:$I$500,MATCH($B33,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$I$3:$I$500,MATCH($B33,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="I33" s="11">
+        <f>IF(INDEX(precios!$J$3:$J$500,MATCH($B33,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$J$3:$J$500,MATCH($B33,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="J33" s="11">
+        <f>IF(INDEX(precios!$K$3:$K$500,MATCH($B33,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$K$3:$K$500,MATCH($B33,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="K33" s="11">
+        <f>IF(INDEX(precios!$L$3:$L$500,MATCH($B33,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$L$3:$L$500,MATCH($B33,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="L33" s="11">
+        <f>IF(INDEX(precios!$M$3:$M$500,MATCH($B33,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$M$3:$M$500,MATCH($B33,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="M33" s="11">
+        <f>IF(INDEX(precios!$N$3:$N$500,MATCH($B33,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$N$3:$N$500,MATCH($B33,precios!$A$3:$A$500,0))/$B$4,"")</f>
       </c>
       <c r="N33" s="11">
         <f>SUM(D33:M33)</f>
@@ -8407,16 +8687,43 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>901</v>
+        <v>281</v>
       </c>
       <c r="B34" t="s">
-        <v>181</v>
+        <v>295</v>
       </c>
       <c r="C34">
-        <f>INDEX(autos!$B$3:$B$500,MATCH($B34,autos!$A$3:$A$500,0))</f>
+        <f>INDEX(precios!$C$3:$C$500,MATCH($B34,precios!$A$3:$A$500,0))</f>
       </c>
       <c r="D34" s="11">
-        <f>IF(INDEX(autos!$C$3:$C$500,MATCH($B34,autos!$A$3:$A$500,0))&gt;0,INDEX(autos!$C$3:$C$500,MATCH($B34,autos!$A$3:$A$500,0))/$B$4,"")</f>
+        <f>IF(INDEX(precios!$E$3:$E$500,MATCH($B34,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$E$3:$E$500,MATCH($B34,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="E34" s="11">
+        <f>IF(INDEX(precios!$F$3:$F$500,MATCH($B34,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$F$3:$F$500,MATCH($B34,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="F34" s="11">
+        <f>IF(INDEX(precios!$G$3:$G$500,MATCH($B34,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$G$3:$G$500,MATCH($B34,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="G34" s="11">
+        <f>IF(INDEX(precios!$H$3:$H$500,MATCH($B34,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$H$3:$H$500,MATCH($B34,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="H34" s="11">
+        <f>IF(INDEX(precios!$I$3:$I$500,MATCH($B34,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$I$3:$I$500,MATCH($B34,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="I34" s="11">
+        <f>IF(INDEX(precios!$J$3:$J$500,MATCH($B34,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$J$3:$J$500,MATCH($B34,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="J34" s="11">
+        <f>IF(INDEX(precios!$K$3:$K$500,MATCH($B34,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$K$3:$K$500,MATCH($B34,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="K34" s="11">
+        <f>IF(INDEX(precios!$L$3:$L$500,MATCH($B34,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$L$3:$L$500,MATCH($B34,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="L34" s="11">
+        <f>IF(INDEX(precios!$M$3:$M$500,MATCH($B34,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$M$3:$M$500,MATCH($B34,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="M34" s="11">
+        <f>IF(INDEX(precios!$N$3:$N$500,MATCH($B34,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$N$3:$N$500,MATCH($B34,precios!$A$3:$A$500,0))/$B$4,"")</f>
       </c>
       <c r="N34" s="11">
         <f>SUM(D34:M34)</f>
@@ -8424,16 +8731,43 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>901</v>
+        <v>281</v>
       </c>
       <c r="B35" t="s">
-        <v>183</v>
+        <v>297</v>
       </c>
       <c r="C35">
-        <f>INDEX(autos!$B$3:$B$500,MATCH($B35,autos!$A$3:$A$500,0))</f>
+        <f>INDEX(precios!$C$3:$C$500,MATCH($B35,precios!$A$3:$A$500,0))</f>
       </c>
       <c r="D35" s="11">
-        <f>IF(INDEX(autos!$C$3:$C$500,MATCH($B35,autos!$A$3:$A$500,0))&gt;0,INDEX(autos!$C$3:$C$500,MATCH($B35,autos!$A$3:$A$500,0))/$B$4,"")</f>
+        <f>IF(INDEX(precios!$E$3:$E$500,MATCH($B35,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$E$3:$E$500,MATCH($B35,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="E35" s="11">
+        <f>IF(INDEX(precios!$F$3:$F$500,MATCH($B35,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$F$3:$F$500,MATCH($B35,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="F35" s="11">
+        <f>IF(INDEX(precios!$G$3:$G$500,MATCH($B35,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$G$3:$G$500,MATCH($B35,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="G35" s="11">
+        <f>IF(INDEX(precios!$H$3:$H$500,MATCH($B35,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$H$3:$H$500,MATCH($B35,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="H35" s="11">
+        <f>IF(INDEX(precios!$I$3:$I$500,MATCH($B35,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$I$3:$I$500,MATCH($B35,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="I35" s="11">
+        <f>IF(INDEX(precios!$J$3:$J$500,MATCH($B35,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$J$3:$J$500,MATCH($B35,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="J35" s="11">
+        <f>IF(INDEX(precios!$K$3:$K$500,MATCH($B35,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$K$3:$K$500,MATCH($B35,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="K35" s="11">
+        <f>IF(INDEX(precios!$L$3:$L$500,MATCH($B35,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$L$3:$L$500,MATCH($B35,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="L35" s="11">
+        <f>IF(INDEX(precios!$M$3:$M$500,MATCH($B35,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$M$3:$M$500,MATCH($B35,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="M35" s="11">
+        <f>IF(INDEX(precios!$N$3:$N$500,MATCH($B35,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$N$3:$N$500,MATCH($B35,precios!$A$3:$A$500,0))/$B$4,"")</f>
       </c>
       <c r="N35" s="11">
         <f>SUM(D35:M35)</f>
@@ -8441,16 +8775,43 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>901</v>
+        <v>281</v>
       </c>
       <c r="B36" t="s">
-        <v>185</v>
+        <v>299</v>
       </c>
       <c r="C36">
-        <f>INDEX(autos!$B$3:$B$500,MATCH($B36,autos!$A$3:$A$500,0))</f>
+        <f>INDEX(precios!$C$3:$C$500,MATCH($B36,precios!$A$3:$A$500,0))</f>
       </c>
       <c r="D36" s="11">
-        <f>IF(INDEX(autos!$C$3:$C$500,MATCH($B36,autos!$A$3:$A$500,0))&gt;0,INDEX(autos!$C$3:$C$500,MATCH($B36,autos!$A$3:$A$500,0))/$B$4,"")</f>
+        <f>IF(INDEX(precios!$E$3:$E$500,MATCH($B36,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$E$3:$E$500,MATCH($B36,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="E36" s="11">
+        <f>IF(INDEX(precios!$F$3:$F$500,MATCH($B36,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$F$3:$F$500,MATCH($B36,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="F36" s="11">
+        <f>IF(INDEX(precios!$G$3:$G$500,MATCH($B36,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$G$3:$G$500,MATCH($B36,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="G36" s="11">
+        <f>IF(INDEX(precios!$H$3:$H$500,MATCH($B36,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$H$3:$H$500,MATCH($B36,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="H36" s="11">
+        <f>IF(INDEX(precios!$I$3:$I$500,MATCH($B36,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$I$3:$I$500,MATCH($B36,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="I36" s="11">
+        <f>IF(INDEX(precios!$J$3:$J$500,MATCH($B36,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$J$3:$J$500,MATCH($B36,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="J36" s="11">
+        <f>IF(INDEX(precios!$K$3:$K$500,MATCH($B36,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$K$3:$K$500,MATCH($B36,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="K36" s="11">
+        <f>IF(INDEX(precios!$L$3:$L$500,MATCH($B36,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$L$3:$L$500,MATCH($B36,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="L36" s="11">
+        <f>IF(INDEX(precios!$M$3:$M$500,MATCH($B36,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$M$3:$M$500,MATCH($B36,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="M36" s="11">
+        <f>IF(INDEX(precios!$N$3:$N$500,MATCH($B36,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$N$3:$N$500,MATCH($B36,precios!$A$3:$A$500,0))/$B$4,"")</f>
       </c>
       <c r="N36" s="11">
         <f>SUM(D36:M36)</f>
@@ -8458,16 +8819,43 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>901</v>
+        <v>302</v>
       </c>
       <c r="B37" t="s">
-        <v>187</v>
+        <v>301</v>
       </c>
       <c r="C37">
-        <f>INDEX(autos!$B$3:$B$500,MATCH($B37,autos!$A$3:$A$500,0))</f>
+        <f>INDEX(precios!$C$3:$C$500,MATCH($B37,precios!$A$3:$A$500,0))</f>
       </c>
       <c r="D37" s="11">
-        <f>IF(INDEX(autos!$C$3:$C$500,MATCH($B37,autos!$A$3:$A$500,0))&gt;0,INDEX(autos!$C$3:$C$500,MATCH($B37,autos!$A$3:$A$500,0))/$B$4,"")</f>
+        <f>IF(INDEX(precios!$E$3:$E$500,MATCH($B37,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$E$3:$E$500,MATCH($B37,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="E37" s="11">
+        <f>IF(INDEX(precios!$F$3:$F$500,MATCH($B37,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$F$3:$F$500,MATCH($B37,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="F37" s="11">
+        <f>IF(INDEX(precios!$G$3:$G$500,MATCH($B37,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$G$3:$G$500,MATCH($B37,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="G37" s="11">
+        <f>IF(INDEX(precios!$H$3:$H$500,MATCH($B37,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$H$3:$H$500,MATCH($B37,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="H37" s="11">
+        <f>IF(INDEX(precios!$I$3:$I$500,MATCH($B37,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$I$3:$I$500,MATCH($B37,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="I37" s="11">
+        <f>IF(INDEX(precios!$J$3:$J$500,MATCH($B37,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$J$3:$J$500,MATCH($B37,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="J37" s="11">
+        <f>IF(INDEX(precios!$K$3:$K$500,MATCH($B37,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$K$3:$K$500,MATCH($B37,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="K37" s="11">
+        <f>IF(INDEX(precios!$L$3:$L$500,MATCH($B37,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$L$3:$L$500,MATCH($B37,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="L37" s="11">
+        <f>IF(INDEX(precios!$M$3:$M$500,MATCH($B37,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$M$3:$M$500,MATCH($B37,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="M37" s="11">
+        <f>IF(INDEX(precios!$N$3:$N$500,MATCH($B37,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$N$3:$N$500,MATCH($B37,precios!$A$3:$A$500,0))/$B$4,"")</f>
       </c>
       <c r="N37" s="11">
         <f>SUM(D37:M37)</f>
@@ -8475,16 +8863,43 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>901</v>
+        <v>302</v>
       </c>
       <c r="B38" t="s">
-        <v>133</v>
+        <v>304</v>
       </c>
       <c r="C38">
-        <f>INDEX(autos!$B$3:$B$500,MATCH($B38,autos!$A$3:$A$500,0))</f>
+        <f>INDEX(precios!$C$3:$C$500,MATCH($B38,precios!$A$3:$A$500,0))</f>
       </c>
       <c r="D38" s="11">
-        <f>IF(INDEX(autos!$C$3:$C$500,MATCH($B38,autos!$A$3:$A$500,0))&gt;0,INDEX(autos!$C$3:$C$500,MATCH($B38,autos!$A$3:$A$500,0))/$B$4,"")</f>
+        <f>IF(INDEX(precios!$E$3:$E$500,MATCH($B38,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$E$3:$E$500,MATCH($B38,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="E38" s="11">
+        <f>IF(INDEX(precios!$F$3:$F$500,MATCH($B38,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$F$3:$F$500,MATCH($B38,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="F38" s="11">
+        <f>IF(INDEX(precios!$G$3:$G$500,MATCH($B38,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$G$3:$G$500,MATCH($B38,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="G38" s="11">
+        <f>IF(INDEX(precios!$H$3:$H$500,MATCH($B38,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$H$3:$H$500,MATCH($B38,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="H38" s="11">
+        <f>IF(INDEX(precios!$I$3:$I$500,MATCH($B38,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$I$3:$I$500,MATCH($B38,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="I38" s="11">
+        <f>IF(INDEX(precios!$J$3:$J$500,MATCH($B38,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$J$3:$J$500,MATCH($B38,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="J38" s="11">
+        <f>IF(INDEX(precios!$K$3:$K$500,MATCH($B38,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$K$3:$K$500,MATCH($B38,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="K38" s="11">
+        <f>IF(INDEX(precios!$L$3:$L$500,MATCH($B38,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$L$3:$L$500,MATCH($B38,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="L38" s="11">
+        <f>IF(INDEX(precios!$M$3:$M$500,MATCH($B38,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$M$3:$M$500,MATCH($B38,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="M38" s="11">
+        <f>IF(INDEX(precios!$N$3:$N$500,MATCH($B38,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$N$3:$N$500,MATCH($B38,precios!$A$3:$A$500,0))/$B$4,"")</f>
       </c>
       <c r="N38" s="11">
         <f>SUM(D38:M38)</f>
@@ -8492,16 +8907,43 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>901</v>
+        <v>302</v>
       </c>
       <c r="B39" t="s">
-        <v>190</v>
+        <v>306</v>
       </c>
       <c r="C39">
-        <f>INDEX(autos!$B$3:$B$500,MATCH($B39,autos!$A$3:$A$500,0))</f>
+        <f>INDEX(precios!$C$3:$C$500,MATCH($B39,precios!$A$3:$A$500,0))</f>
       </c>
       <c r="D39" s="11">
-        <f>IF(INDEX(autos!$C$3:$C$500,MATCH($B39,autos!$A$3:$A$500,0))&gt;0,INDEX(autos!$C$3:$C$500,MATCH($B39,autos!$A$3:$A$500,0))/$B$4,"")</f>
+        <f>IF(INDEX(precios!$E$3:$E$500,MATCH($B39,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$E$3:$E$500,MATCH($B39,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="E39" s="11">
+        <f>IF(INDEX(precios!$F$3:$F$500,MATCH($B39,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$F$3:$F$500,MATCH($B39,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="F39" s="11">
+        <f>IF(INDEX(precios!$G$3:$G$500,MATCH($B39,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$G$3:$G$500,MATCH($B39,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="G39" s="11">
+        <f>IF(INDEX(precios!$H$3:$H$500,MATCH($B39,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$H$3:$H$500,MATCH($B39,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="H39" s="11">
+        <f>IF(INDEX(precios!$I$3:$I$500,MATCH($B39,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$I$3:$I$500,MATCH($B39,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="I39" s="11">
+        <f>IF(INDEX(precios!$J$3:$J$500,MATCH($B39,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$J$3:$J$500,MATCH($B39,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="J39" s="11">
+        <f>IF(INDEX(precios!$K$3:$K$500,MATCH($B39,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$K$3:$K$500,MATCH($B39,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="K39" s="11">
+        <f>IF(INDEX(precios!$L$3:$L$500,MATCH($B39,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$L$3:$L$500,MATCH($B39,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="L39" s="11">
+        <f>IF(INDEX(precios!$M$3:$M$500,MATCH($B39,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$M$3:$M$500,MATCH($B39,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="M39" s="11">
+        <f>IF(INDEX(precios!$N$3:$N$500,MATCH($B39,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$N$3:$N$500,MATCH($B39,precios!$A$3:$A$500,0))/$B$4,"")</f>
       </c>
       <c r="N39" s="11">
         <f>SUM(D39:M39)</f>
@@ -8509,16 +8951,43 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>902</v>
+        <v>302</v>
       </c>
       <c r="B40" t="s">
-        <v>215</v>
+        <v>308</v>
       </c>
       <c r="C40">
-        <f>INDEX(pilotos!$B$3:$B$500,MATCH($B40,pilotos!$A$3:$A$500,0))</f>
+        <f>INDEX(precios!$C$3:$C$500,MATCH($B40,precios!$A$3:$A$500,0))</f>
       </c>
       <c r="D40" s="11">
-        <f>IF(INDEX(pilotos!$C$3:$C$500,MATCH($B40,pilotos!$A$3:$A$500,0))&gt;0,INDEX(pilotos!$C$3:$C$500,MATCH($B40,pilotos!$A$3:$A$500,0))/$B$4,"")</f>
+        <f>IF(INDEX(precios!$E$3:$E$500,MATCH($B40,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$E$3:$E$500,MATCH($B40,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="E40" s="11">
+        <f>IF(INDEX(precios!$F$3:$F$500,MATCH($B40,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$F$3:$F$500,MATCH($B40,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="F40" s="11">
+        <f>IF(INDEX(precios!$G$3:$G$500,MATCH($B40,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$G$3:$G$500,MATCH($B40,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="G40" s="11">
+        <f>IF(INDEX(precios!$H$3:$H$500,MATCH($B40,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$H$3:$H$500,MATCH($B40,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="H40" s="11">
+        <f>IF(INDEX(precios!$I$3:$I$500,MATCH($B40,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$I$3:$I$500,MATCH($B40,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="I40" s="11">
+        <f>IF(INDEX(precios!$J$3:$J$500,MATCH($B40,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$J$3:$J$500,MATCH($B40,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="J40" s="11">
+        <f>IF(INDEX(precios!$K$3:$K$500,MATCH($B40,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$K$3:$K$500,MATCH($B40,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="K40" s="11">
+        <f>IF(INDEX(precios!$L$3:$L$500,MATCH($B40,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$L$3:$L$500,MATCH($B40,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="L40" s="11">
+        <f>IF(INDEX(precios!$M$3:$M$500,MATCH($B40,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$M$3:$M$500,MATCH($B40,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="M40" s="11">
+        <f>IF(INDEX(precios!$N$3:$N$500,MATCH($B40,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$N$3:$N$500,MATCH($B40,precios!$A$3:$A$500,0))/$B$4,"")</f>
       </c>
       <c r="N40" s="11">
         <f>SUM(D40:M40)</f>
@@ -8526,16 +8995,43 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>902</v>
+        <v>311</v>
       </c>
       <c r="B41" t="s">
-        <v>217</v>
+        <v>310</v>
       </c>
       <c r="C41">
-        <f>INDEX(pilotos!$B$3:$B$500,MATCH($B41,pilotos!$A$3:$A$500,0))</f>
+        <f>INDEX(precios!$C$3:$C$500,MATCH($B41,precios!$A$3:$A$500,0))</f>
       </c>
       <c r="D41" s="11">
-        <f>IF(INDEX(pilotos!$C$3:$C$500,MATCH($B41,pilotos!$A$3:$A$500,0))&gt;0,INDEX(pilotos!$C$3:$C$500,MATCH($B41,pilotos!$A$3:$A$500,0))/$B$4,"")</f>
+        <f>IF(INDEX(precios!$E$3:$E$500,MATCH($B41,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$E$3:$E$500,MATCH($B41,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="E41" s="11">
+        <f>IF(INDEX(precios!$F$3:$F$500,MATCH($B41,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$F$3:$F$500,MATCH($B41,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="F41" s="11">
+        <f>IF(INDEX(precios!$G$3:$G$500,MATCH($B41,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$G$3:$G$500,MATCH($B41,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="G41" s="11">
+        <f>IF(INDEX(precios!$H$3:$H$500,MATCH($B41,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$H$3:$H$500,MATCH($B41,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="H41" s="11">
+        <f>IF(INDEX(precios!$I$3:$I$500,MATCH($B41,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$I$3:$I$500,MATCH($B41,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="I41" s="11">
+        <f>IF(INDEX(precios!$J$3:$J$500,MATCH($B41,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$J$3:$J$500,MATCH($B41,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="J41" s="11">
+        <f>IF(INDEX(precios!$K$3:$K$500,MATCH($B41,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$K$3:$K$500,MATCH($B41,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="K41" s="11">
+        <f>IF(INDEX(precios!$L$3:$L$500,MATCH($B41,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$L$3:$L$500,MATCH($B41,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="L41" s="11">
+        <f>IF(INDEX(precios!$M$3:$M$500,MATCH($B41,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$M$3:$M$500,MATCH($B41,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="M41" s="11">
+        <f>IF(INDEX(precios!$N$3:$N$500,MATCH($B41,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$N$3:$N$500,MATCH($B41,precios!$A$3:$A$500,0))/$B$4,"")</f>
       </c>
       <c r="N41" s="11">
         <f>SUM(D41:M41)</f>
@@ -8543,16 +9039,43 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>902</v>
+        <v>311</v>
       </c>
       <c r="B42" t="s">
-        <v>35</v>
+        <v>313</v>
       </c>
       <c r="C42">
-        <f>INDEX(pilotos!$B$3:$B$500,MATCH($B42,pilotos!$A$3:$A$500,0))</f>
+        <f>INDEX(precios!$C$3:$C$500,MATCH($B42,precios!$A$3:$A$500,0))</f>
       </c>
       <c r="D42" s="11">
-        <f>IF(INDEX(pilotos!$C$3:$C$500,MATCH($B42,pilotos!$A$3:$A$500,0))&gt;0,INDEX(pilotos!$C$3:$C$500,MATCH($B42,pilotos!$A$3:$A$500,0))/$B$4,"")</f>
+        <f>IF(INDEX(precios!$E$3:$E$500,MATCH($B42,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$E$3:$E$500,MATCH($B42,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="E42" s="11">
+        <f>IF(INDEX(precios!$F$3:$F$500,MATCH($B42,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$F$3:$F$500,MATCH($B42,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="F42" s="11">
+        <f>IF(INDEX(precios!$G$3:$G$500,MATCH($B42,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$G$3:$G$500,MATCH($B42,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="G42" s="11">
+        <f>IF(INDEX(precios!$H$3:$H$500,MATCH($B42,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$H$3:$H$500,MATCH($B42,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="H42" s="11">
+        <f>IF(INDEX(precios!$I$3:$I$500,MATCH($B42,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$I$3:$I$500,MATCH($B42,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="I42" s="11">
+        <f>IF(INDEX(precios!$J$3:$J$500,MATCH($B42,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$J$3:$J$500,MATCH($B42,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="J42" s="11">
+        <f>IF(INDEX(precios!$K$3:$K$500,MATCH($B42,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$K$3:$K$500,MATCH($B42,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="K42" s="11">
+        <f>IF(INDEX(precios!$L$3:$L$500,MATCH($B42,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$L$3:$L$500,MATCH($B42,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="L42" s="11">
+        <f>IF(INDEX(precios!$M$3:$M$500,MATCH($B42,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$M$3:$M$500,MATCH($B42,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="M42" s="11">
+        <f>IF(INDEX(precios!$N$3:$N$500,MATCH($B42,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$N$3:$N$500,MATCH($B42,precios!$A$3:$A$500,0))/$B$4,"")</f>
       </c>
       <c r="N42" s="11">
         <f>SUM(D42:M42)</f>
@@ -8560,16 +9083,43 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>902</v>
+        <v>311</v>
       </c>
       <c r="B43" t="s">
-        <v>220</v>
+        <v>314</v>
       </c>
       <c r="C43">
-        <f>INDEX(pilotos!$B$3:$B$500,MATCH($B43,pilotos!$A$3:$A$500,0))</f>
+        <f>INDEX(precios!$C$3:$C$500,MATCH($B43,precios!$A$3:$A$500,0))</f>
       </c>
       <c r="D43" s="11">
-        <f>IF(INDEX(pilotos!$C$3:$C$500,MATCH($B43,pilotos!$A$3:$A$500,0))&gt;0,INDEX(pilotos!$C$3:$C$500,MATCH($B43,pilotos!$A$3:$A$500,0))/$B$4,"")</f>
+        <f>IF(INDEX(precios!$E$3:$E$500,MATCH($B43,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$E$3:$E$500,MATCH($B43,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="E43" s="11">
+        <f>IF(INDEX(precios!$F$3:$F$500,MATCH($B43,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$F$3:$F$500,MATCH($B43,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="F43" s="11">
+        <f>IF(INDEX(precios!$G$3:$G$500,MATCH($B43,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$G$3:$G$500,MATCH($B43,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="G43" s="11">
+        <f>IF(INDEX(precios!$H$3:$H$500,MATCH($B43,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$H$3:$H$500,MATCH($B43,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="H43" s="11">
+        <f>IF(INDEX(precios!$I$3:$I$500,MATCH($B43,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$I$3:$I$500,MATCH($B43,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="I43" s="11">
+        <f>IF(INDEX(precios!$J$3:$J$500,MATCH($B43,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$J$3:$J$500,MATCH($B43,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="J43" s="11">
+        <f>IF(INDEX(precios!$K$3:$K$500,MATCH($B43,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$K$3:$K$500,MATCH($B43,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="K43" s="11">
+        <f>IF(INDEX(precios!$L$3:$L$500,MATCH($B43,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$L$3:$L$500,MATCH($B43,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="L43" s="11">
+        <f>IF(INDEX(precios!$M$3:$M$500,MATCH($B43,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$M$3:$M$500,MATCH($B43,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="M43" s="11">
+        <f>IF(INDEX(precios!$N$3:$N$500,MATCH($B43,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$N$3:$N$500,MATCH($B43,precios!$A$3:$A$500,0))/$B$4,"")</f>
       </c>
       <c r="N43" s="11">
         <f>SUM(D43:M43)</f>
@@ -8577,27 +9127,1111 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>902</v>
+        <v>311</v>
       </c>
       <c r="B44" t="s">
-        <v>222</v>
+        <v>315</v>
       </c>
       <c r="C44">
-        <f>INDEX(pilotos!$B$3:$B$500,MATCH($B44,pilotos!$A$3:$A$500,0))</f>
+        <f>INDEX(precios!$C$3:$C$500,MATCH($B44,precios!$A$3:$A$500,0))</f>
       </c>
       <c r="D44" s="11">
-        <f>IF(INDEX(pilotos!$C$3:$C$500,MATCH($B44,pilotos!$A$3:$A$500,0))&gt;0,INDEX(pilotos!$C$3:$C$500,MATCH($B44,pilotos!$A$3:$A$500,0))/$B$4,"")</f>
+        <f>IF(INDEX(precios!$E$3:$E$500,MATCH($B44,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$E$3:$E$500,MATCH($B44,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="E44" s="11">
+        <f>IF(INDEX(precios!$F$3:$F$500,MATCH($B44,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$F$3:$F$500,MATCH($B44,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="F44" s="11">
+        <f>IF(INDEX(precios!$G$3:$G$500,MATCH($B44,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$G$3:$G$500,MATCH($B44,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="G44" s="11">
+        <f>IF(INDEX(precios!$H$3:$H$500,MATCH($B44,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$H$3:$H$500,MATCH($B44,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="H44" s="11">
+        <f>IF(INDEX(precios!$I$3:$I$500,MATCH($B44,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$I$3:$I$500,MATCH($B44,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="I44" s="11">
+        <f>IF(INDEX(precios!$J$3:$J$500,MATCH($B44,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$J$3:$J$500,MATCH($B44,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="J44" s="11">
+        <f>IF(INDEX(precios!$K$3:$K$500,MATCH($B44,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$K$3:$K$500,MATCH($B44,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="K44" s="11">
+        <f>IF(INDEX(precios!$L$3:$L$500,MATCH($B44,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$L$3:$L$500,MATCH($B44,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="L44" s="11">
+        <f>IF(INDEX(precios!$M$3:$M$500,MATCH($B44,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$M$3:$M$500,MATCH($B44,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="M44" s="11">
+        <f>IF(INDEX(precios!$N$3:$N$500,MATCH($B44,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$N$3:$N$500,MATCH($B44,precios!$A$3:$A$500,0))/$B$4,"")</f>
       </c>
       <c r="N44" s="11">
         <f>SUM(D44:M44)</f>
       </c>
     </row>
-    <row r="46" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C46" s="1" t="s">
-        <v>903</v>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>311</v>
+      </c>
+      <c r="B45" t="s">
+        <v>317</v>
+      </c>
+      <c r="C45">
+        <f>INDEX(precios!$C$3:$C$500,MATCH($B45,precios!$A$3:$A$500,0))</f>
+      </c>
+      <c r="D45" s="11">
+        <f>IF(INDEX(precios!$E$3:$E$500,MATCH($B45,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$E$3:$E$500,MATCH($B45,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="E45" s="11">
+        <f>IF(INDEX(precios!$F$3:$F$500,MATCH($B45,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$F$3:$F$500,MATCH($B45,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="F45" s="11">
+        <f>IF(INDEX(precios!$G$3:$G$500,MATCH($B45,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$G$3:$G$500,MATCH($B45,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="G45" s="11">
+        <f>IF(INDEX(precios!$H$3:$H$500,MATCH($B45,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$H$3:$H$500,MATCH($B45,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="H45" s="11">
+        <f>IF(INDEX(precios!$I$3:$I$500,MATCH($B45,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$I$3:$I$500,MATCH($B45,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="I45" s="11">
+        <f>IF(INDEX(precios!$J$3:$J$500,MATCH($B45,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$J$3:$J$500,MATCH($B45,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="J45" s="11">
+        <f>IF(INDEX(precios!$K$3:$K$500,MATCH($B45,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$K$3:$K$500,MATCH($B45,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="K45" s="11">
+        <f>IF(INDEX(precios!$L$3:$L$500,MATCH($B45,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$L$3:$L$500,MATCH($B45,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="L45" s="11">
+        <f>IF(INDEX(precios!$M$3:$M$500,MATCH($B45,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$M$3:$M$500,MATCH($B45,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="M45" s="11">
+        <f>IF(INDEX(precios!$N$3:$N$500,MATCH($B45,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$N$3:$N$500,MATCH($B45,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="N45" s="11">
+        <f>SUM(D45:M45)</f>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>311</v>
+      </c>
+      <c r="B46" t="s">
+        <v>318</v>
+      </c>
+      <c r="C46">
+        <f>INDEX(precios!$C$3:$C$500,MATCH($B46,precios!$A$3:$A$500,0))</f>
+      </c>
+      <c r="D46" s="11">
+        <f>IF(INDEX(precios!$E$3:$E$500,MATCH($B46,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$E$3:$E$500,MATCH($B46,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="E46" s="11">
+        <f>IF(INDEX(precios!$F$3:$F$500,MATCH($B46,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$F$3:$F$500,MATCH($B46,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="F46" s="11">
+        <f>IF(INDEX(precios!$G$3:$G$500,MATCH($B46,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$G$3:$G$500,MATCH($B46,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="G46" s="11">
+        <f>IF(INDEX(precios!$H$3:$H$500,MATCH($B46,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$H$3:$H$500,MATCH($B46,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="H46" s="11">
+        <f>IF(INDEX(precios!$I$3:$I$500,MATCH($B46,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$I$3:$I$500,MATCH($B46,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="I46" s="11">
+        <f>IF(INDEX(precios!$J$3:$J$500,MATCH($B46,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$J$3:$J$500,MATCH($B46,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="J46" s="11">
+        <f>IF(INDEX(precios!$K$3:$K$500,MATCH($B46,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$K$3:$K$500,MATCH($B46,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="K46" s="11">
+        <f>IF(INDEX(precios!$L$3:$L$500,MATCH($B46,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$L$3:$L$500,MATCH($B46,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="L46" s="11">
+        <f>IF(INDEX(precios!$M$3:$M$500,MATCH($B46,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$M$3:$M$500,MATCH($B46,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="M46" s="11">
+        <f>IF(INDEX(precios!$N$3:$N$500,MATCH($B46,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$N$3:$N$500,MATCH($B46,precios!$A$3:$A$500,0))/$B$4,"")</f>
       </c>
       <c r="N46" s="11">
-        <f>SUM(N11:N44)</f>
+        <f>SUM(D46:M46)</f>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>311</v>
+      </c>
+      <c r="B47" t="s">
+        <v>320</v>
+      </c>
+      <c r="C47">
+        <f>INDEX(precios!$C$3:$C$500,MATCH($B47,precios!$A$3:$A$500,0))</f>
+      </c>
+      <c r="D47" s="11">
+        <f>IF(INDEX(precios!$E$3:$E$500,MATCH($B47,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$E$3:$E$500,MATCH($B47,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="E47" s="11">
+        <f>IF(INDEX(precios!$F$3:$F$500,MATCH($B47,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$F$3:$F$500,MATCH($B47,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="F47" s="11">
+        <f>IF(INDEX(precios!$G$3:$G$500,MATCH($B47,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$G$3:$G$500,MATCH($B47,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="G47" s="11">
+        <f>IF(INDEX(precios!$H$3:$H$500,MATCH($B47,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$H$3:$H$500,MATCH($B47,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="H47" s="11">
+        <f>IF(INDEX(precios!$I$3:$I$500,MATCH($B47,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$I$3:$I$500,MATCH($B47,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="I47" s="11">
+        <f>IF(INDEX(precios!$J$3:$J$500,MATCH($B47,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$J$3:$J$500,MATCH($B47,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="J47" s="11">
+        <f>IF(INDEX(precios!$K$3:$K$500,MATCH($B47,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$K$3:$K$500,MATCH($B47,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="K47" s="11">
+        <f>IF(INDEX(precios!$L$3:$L$500,MATCH($B47,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$L$3:$L$500,MATCH($B47,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="L47" s="11">
+        <f>IF(INDEX(precios!$M$3:$M$500,MATCH($B47,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$M$3:$M$500,MATCH($B47,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="M47" s="11">
+        <f>IF(INDEX(precios!$N$3:$N$500,MATCH($B47,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$N$3:$N$500,MATCH($B47,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="N47" s="11">
+        <f>SUM(D47:M47)</f>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>311</v>
+      </c>
+      <c r="B48" t="s">
+        <v>321</v>
+      </c>
+      <c r="C48">
+        <f>INDEX(precios!$C$3:$C$500,MATCH($B48,precios!$A$3:$A$500,0))</f>
+      </c>
+      <c r="D48" s="11">
+        <f>IF(INDEX(precios!$E$3:$E$500,MATCH($B48,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$E$3:$E$500,MATCH($B48,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="E48" s="11">
+        <f>IF(INDEX(precios!$F$3:$F$500,MATCH($B48,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$F$3:$F$500,MATCH($B48,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="F48" s="11">
+        <f>IF(INDEX(precios!$G$3:$G$500,MATCH($B48,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$G$3:$G$500,MATCH($B48,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="G48" s="11">
+        <f>IF(INDEX(precios!$H$3:$H$500,MATCH($B48,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$H$3:$H$500,MATCH($B48,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="H48" s="11">
+        <f>IF(INDEX(precios!$I$3:$I$500,MATCH($B48,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$I$3:$I$500,MATCH($B48,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="I48" s="11">
+        <f>IF(INDEX(precios!$J$3:$J$500,MATCH($B48,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$J$3:$J$500,MATCH($B48,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="J48" s="11">
+        <f>IF(INDEX(precios!$K$3:$K$500,MATCH($B48,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$K$3:$K$500,MATCH($B48,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="K48" s="11">
+        <f>IF(INDEX(precios!$L$3:$L$500,MATCH($B48,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$L$3:$L$500,MATCH($B48,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="L48" s="11">
+        <f>IF(INDEX(precios!$M$3:$M$500,MATCH($B48,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$M$3:$M$500,MATCH($B48,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="M48" s="11">
+        <f>IF(INDEX(precios!$N$3:$N$500,MATCH($B48,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$N$3:$N$500,MATCH($B48,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="N48" s="11">
+        <f>SUM(D48:M48)</f>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>311</v>
+      </c>
+      <c r="B49" t="s">
+        <v>323</v>
+      </c>
+      <c r="C49">
+        <f>INDEX(precios!$C$3:$C$500,MATCH($B49,precios!$A$3:$A$500,0))</f>
+      </c>
+      <c r="D49" s="11">
+        <f>IF(INDEX(precios!$E$3:$E$500,MATCH($B49,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$E$3:$E$500,MATCH($B49,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="E49" s="11">
+        <f>IF(INDEX(precios!$F$3:$F$500,MATCH($B49,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$F$3:$F$500,MATCH($B49,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="F49" s="11">
+        <f>IF(INDEX(precios!$G$3:$G$500,MATCH($B49,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$G$3:$G$500,MATCH($B49,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="G49" s="11">
+        <f>IF(INDEX(precios!$H$3:$H$500,MATCH($B49,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$H$3:$H$500,MATCH($B49,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="H49" s="11">
+        <f>IF(INDEX(precios!$I$3:$I$500,MATCH($B49,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$I$3:$I$500,MATCH($B49,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="I49" s="11">
+        <f>IF(INDEX(precios!$J$3:$J$500,MATCH($B49,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$J$3:$J$500,MATCH($B49,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="J49" s="11">
+        <f>IF(INDEX(precios!$K$3:$K$500,MATCH($B49,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$K$3:$K$500,MATCH($B49,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="K49" s="11">
+        <f>IF(INDEX(precios!$L$3:$L$500,MATCH($B49,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$L$3:$L$500,MATCH($B49,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="L49" s="11">
+        <f>IF(INDEX(precios!$M$3:$M$500,MATCH($B49,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$M$3:$M$500,MATCH($B49,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="M49" s="11">
+        <f>IF(INDEX(precios!$N$3:$N$500,MATCH($B49,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$N$3:$N$500,MATCH($B49,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="N49" s="11">
+        <f>SUM(D49:M49)</f>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>311</v>
+      </c>
+      <c r="B50" t="s">
+        <v>324</v>
+      </c>
+      <c r="C50">
+        <f>INDEX(precios!$C$3:$C$500,MATCH($B50,precios!$A$3:$A$500,0))</f>
+      </c>
+      <c r="D50" s="11">
+        <f>IF(INDEX(precios!$E$3:$E$500,MATCH($B50,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$E$3:$E$500,MATCH($B50,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="E50" s="11">
+        <f>IF(INDEX(precios!$F$3:$F$500,MATCH($B50,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$F$3:$F$500,MATCH($B50,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="F50" s="11">
+        <f>IF(INDEX(precios!$G$3:$G$500,MATCH($B50,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$G$3:$G$500,MATCH($B50,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="G50" s="11">
+        <f>IF(INDEX(precios!$H$3:$H$500,MATCH($B50,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$H$3:$H$500,MATCH($B50,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="H50" s="11">
+        <f>IF(INDEX(precios!$I$3:$I$500,MATCH($B50,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$I$3:$I$500,MATCH($B50,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="I50" s="11">
+        <f>IF(INDEX(precios!$J$3:$J$500,MATCH($B50,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$J$3:$J$500,MATCH($B50,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="J50" s="11">
+        <f>IF(INDEX(precios!$K$3:$K$500,MATCH($B50,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$K$3:$K$500,MATCH($B50,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="K50" s="11">
+        <f>IF(INDEX(precios!$L$3:$L$500,MATCH($B50,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$L$3:$L$500,MATCH($B50,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="L50" s="11">
+        <f>IF(INDEX(precios!$M$3:$M$500,MATCH($B50,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$M$3:$M$500,MATCH($B50,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="M50" s="11">
+        <f>IF(INDEX(precios!$N$3:$N$500,MATCH($B50,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$N$3:$N$500,MATCH($B50,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="N50" s="11">
+        <f>SUM(D50:M50)</f>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>311</v>
+      </c>
+      <c r="B51" t="s">
+        <v>325</v>
+      </c>
+      <c r="C51">
+        <f>INDEX(precios!$C$3:$C$500,MATCH($B51,precios!$A$3:$A$500,0))</f>
+      </c>
+      <c r="D51" s="11">
+        <f>IF(INDEX(precios!$E$3:$E$500,MATCH($B51,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$E$3:$E$500,MATCH($B51,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="E51" s="11">
+        <f>IF(INDEX(precios!$F$3:$F$500,MATCH($B51,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$F$3:$F$500,MATCH($B51,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="F51" s="11">
+        <f>IF(INDEX(precios!$G$3:$G$500,MATCH($B51,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$G$3:$G$500,MATCH($B51,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="G51" s="11">
+        <f>IF(INDEX(precios!$H$3:$H$500,MATCH($B51,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$H$3:$H$500,MATCH($B51,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="H51" s="11">
+        <f>IF(INDEX(precios!$I$3:$I$500,MATCH($B51,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$I$3:$I$500,MATCH($B51,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="I51" s="11">
+        <f>IF(INDEX(precios!$J$3:$J$500,MATCH($B51,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$J$3:$J$500,MATCH($B51,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="J51" s="11">
+        <f>IF(INDEX(precios!$K$3:$K$500,MATCH($B51,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$K$3:$K$500,MATCH($B51,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="K51" s="11">
+        <f>IF(INDEX(precios!$L$3:$L$500,MATCH($B51,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$L$3:$L$500,MATCH($B51,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="L51" s="11">
+        <f>IF(INDEX(precios!$M$3:$M$500,MATCH($B51,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$M$3:$M$500,MATCH($B51,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="M51" s="11">
+        <f>IF(INDEX(precios!$N$3:$N$500,MATCH($B51,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$N$3:$N$500,MATCH($B51,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="N51" s="11">
+        <f>SUM(D51:M51)</f>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>281</v>
+      </c>
+      <c r="B52" t="s">
+        <v>326</v>
+      </c>
+      <c r="C52">
+        <f>INDEX(precios!$C$3:$C$500,MATCH($B52,precios!$A$3:$A$500,0))</f>
+      </c>
+      <c r="D52" s="11">
+        <f>IF(INDEX(precios!$E$3:$E$500,MATCH($B52,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$E$3:$E$500,MATCH($B52,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="E52" s="11">
+        <f>IF(INDEX(precios!$F$3:$F$500,MATCH($B52,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$F$3:$F$500,MATCH($B52,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="F52" s="11">
+        <f>IF(INDEX(precios!$G$3:$G$500,MATCH($B52,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$G$3:$G$500,MATCH($B52,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="G52" s="11">
+        <f>IF(INDEX(precios!$H$3:$H$500,MATCH($B52,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$H$3:$H$500,MATCH($B52,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="H52" s="11">
+        <f>IF(INDEX(precios!$I$3:$I$500,MATCH($B52,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$I$3:$I$500,MATCH($B52,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="I52" s="11">
+        <f>IF(INDEX(precios!$J$3:$J$500,MATCH($B52,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$J$3:$J$500,MATCH($B52,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="J52" s="11">
+        <f>IF(INDEX(precios!$K$3:$K$500,MATCH($B52,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$K$3:$K$500,MATCH($B52,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="K52" s="11">
+        <f>IF(INDEX(precios!$L$3:$L$500,MATCH($B52,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$L$3:$L$500,MATCH($B52,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="L52" s="11">
+        <f>IF(INDEX(precios!$M$3:$M$500,MATCH($B52,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$M$3:$M$500,MATCH($B52,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="M52" s="11">
+        <f>IF(INDEX(precios!$N$3:$N$500,MATCH($B52,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$N$3:$N$500,MATCH($B52,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="N52" s="11">
+        <f>SUM(D52:M52)</f>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>281</v>
+      </c>
+      <c r="B53" t="s">
+        <v>328</v>
+      </c>
+      <c r="C53">
+        <f>INDEX(precios!$C$3:$C$500,MATCH($B53,precios!$A$3:$A$500,0))</f>
+      </c>
+      <c r="D53" s="11">
+        <f>IF(INDEX(precios!$E$3:$E$500,MATCH($B53,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$E$3:$E$500,MATCH($B53,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="E53" s="11">
+        <f>IF(INDEX(precios!$F$3:$F$500,MATCH($B53,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$F$3:$F$500,MATCH($B53,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="F53" s="11">
+        <f>IF(INDEX(precios!$G$3:$G$500,MATCH($B53,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$G$3:$G$500,MATCH($B53,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="G53" s="11">
+        <f>IF(INDEX(precios!$H$3:$H$500,MATCH($B53,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$H$3:$H$500,MATCH($B53,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="H53" s="11">
+        <f>IF(INDEX(precios!$I$3:$I$500,MATCH($B53,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$I$3:$I$500,MATCH($B53,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="I53" s="11">
+        <f>IF(INDEX(precios!$J$3:$J$500,MATCH($B53,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$J$3:$J$500,MATCH($B53,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="J53" s="11">
+        <f>IF(INDEX(precios!$K$3:$K$500,MATCH($B53,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$K$3:$K$500,MATCH($B53,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="K53" s="11">
+        <f>IF(INDEX(precios!$L$3:$L$500,MATCH($B53,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$L$3:$L$500,MATCH($B53,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="L53" s="11">
+        <f>IF(INDEX(precios!$M$3:$M$500,MATCH($B53,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$M$3:$M$500,MATCH($B53,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="M53" s="11">
+        <f>IF(INDEX(precios!$N$3:$N$500,MATCH($B53,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$N$3:$N$500,MATCH($B53,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="N53" s="11">
+        <f>SUM(D53:M53)</f>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>281</v>
+      </c>
+      <c r="B54" t="s">
+        <v>330</v>
+      </c>
+      <c r="C54">
+        <f>INDEX(precios!$C$3:$C$500,MATCH($B54,precios!$A$3:$A$500,0))</f>
+      </c>
+      <c r="D54" s="11">
+        <f>IF(INDEX(precios!$E$3:$E$500,MATCH($B54,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$E$3:$E$500,MATCH($B54,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="E54" s="11">
+        <f>IF(INDEX(precios!$F$3:$F$500,MATCH($B54,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$F$3:$F$500,MATCH($B54,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="F54" s="11">
+        <f>IF(INDEX(precios!$G$3:$G$500,MATCH($B54,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$G$3:$G$500,MATCH($B54,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="G54" s="11">
+        <f>IF(INDEX(precios!$H$3:$H$500,MATCH($B54,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$H$3:$H$500,MATCH($B54,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="H54" s="11">
+        <f>IF(INDEX(precios!$I$3:$I$500,MATCH($B54,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$I$3:$I$500,MATCH($B54,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="I54" s="11">
+        <f>IF(INDEX(precios!$J$3:$J$500,MATCH($B54,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$J$3:$J$500,MATCH($B54,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="J54" s="11">
+        <f>IF(INDEX(precios!$K$3:$K$500,MATCH($B54,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$K$3:$K$500,MATCH($B54,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="K54" s="11">
+        <f>IF(INDEX(precios!$L$3:$L$500,MATCH($B54,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$L$3:$L$500,MATCH($B54,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="L54" s="11">
+        <f>IF(INDEX(precios!$M$3:$M$500,MATCH($B54,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$M$3:$M$500,MATCH($B54,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="M54" s="11">
+        <f>IF(INDEX(precios!$N$3:$N$500,MATCH($B54,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$N$3:$N$500,MATCH($B54,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="N54" s="11">
+        <f>SUM(D54:M54)</f>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>281</v>
+      </c>
+      <c r="B55" t="s">
+        <v>332</v>
+      </c>
+      <c r="C55">
+        <f>INDEX(precios!$C$3:$C$500,MATCH($B55,precios!$A$3:$A$500,0))</f>
+      </c>
+      <c r="D55" s="11">
+        <f>IF(INDEX(precios!$E$3:$E$500,MATCH($B55,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$E$3:$E$500,MATCH($B55,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="E55" s="11">
+        <f>IF(INDEX(precios!$F$3:$F$500,MATCH($B55,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$F$3:$F$500,MATCH($B55,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="F55" s="11">
+        <f>IF(INDEX(precios!$G$3:$G$500,MATCH($B55,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$G$3:$G$500,MATCH($B55,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="G55" s="11">
+        <f>IF(INDEX(precios!$H$3:$H$500,MATCH($B55,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$H$3:$H$500,MATCH($B55,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="H55" s="11">
+        <f>IF(INDEX(precios!$I$3:$I$500,MATCH($B55,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$I$3:$I$500,MATCH($B55,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="I55" s="11">
+        <f>IF(INDEX(precios!$J$3:$J$500,MATCH($B55,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$J$3:$J$500,MATCH($B55,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="J55" s="11">
+        <f>IF(INDEX(precios!$K$3:$K$500,MATCH($B55,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$K$3:$K$500,MATCH($B55,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="K55" s="11">
+        <f>IF(INDEX(precios!$L$3:$L$500,MATCH($B55,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$L$3:$L$500,MATCH($B55,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="L55" s="11">
+        <f>IF(INDEX(precios!$M$3:$M$500,MATCH($B55,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$M$3:$M$500,MATCH($B55,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="M55" s="11">
+        <f>IF(INDEX(precios!$N$3:$N$500,MATCH($B55,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$N$3:$N$500,MATCH($B55,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="N55" s="11">
+        <f>SUM(D55:M55)</f>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>281</v>
+      </c>
+      <c r="B56" t="s">
+        <v>334</v>
+      </c>
+      <c r="C56">
+        <f>INDEX(precios!$C$3:$C$500,MATCH($B56,precios!$A$3:$A$500,0))</f>
+      </c>
+      <c r="D56" s="11">
+        <f>IF(INDEX(precios!$E$3:$E$500,MATCH($B56,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$E$3:$E$500,MATCH($B56,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="E56" s="11">
+        <f>IF(INDEX(precios!$F$3:$F$500,MATCH($B56,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$F$3:$F$500,MATCH($B56,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="F56" s="11">
+        <f>IF(INDEX(precios!$G$3:$G$500,MATCH($B56,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$G$3:$G$500,MATCH($B56,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="G56" s="11">
+        <f>IF(INDEX(precios!$H$3:$H$500,MATCH($B56,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$H$3:$H$500,MATCH($B56,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="H56" s="11">
+        <f>IF(INDEX(precios!$I$3:$I$500,MATCH($B56,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$I$3:$I$500,MATCH($B56,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="I56" s="11">
+        <f>IF(INDEX(precios!$J$3:$J$500,MATCH($B56,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$J$3:$J$500,MATCH($B56,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="J56" s="11">
+        <f>IF(INDEX(precios!$K$3:$K$500,MATCH($B56,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$K$3:$K$500,MATCH($B56,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="K56" s="11">
+        <f>IF(INDEX(precios!$L$3:$L$500,MATCH($B56,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$L$3:$L$500,MATCH($B56,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="L56" s="11">
+        <f>IF(INDEX(precios!$M$3:$M$500,MATCH($B56,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$M$3:$M$500,MATCH($B56,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="M56" s="11">
+        <f>IF(INDEX(precios!$N$3:$N$500,MATCH($B56,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$N$3:$N$500,MATCH($B56,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="N56" s="11">
+        <f>SUM(D56:M56)</f>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>281</v>
+      </c>
+      <c r="B57" t="s">
+        <v>336</v>
+      </c>
+      <c r="C57">
+        <f>INDEX(precios!$C$3:$C$500,MATCH($B57,precios!$A$3:$A$500,0))</f>
+      </c>
+      <c r="D57" s="11">
+        <f>IF(INDEX(precios!$E$3:$E$500,MATCH($B57,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$E$3:$E$500,MATCH($B57,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="E57" s="11">
+        <f>IF(INDEX(precios!$F$3:$F$500,MATCH($B57,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$F$3:$F$500,MATCH($B57,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="F57" s="11">
+        <f>IF(INDEX(precios!$G$3:$G$500,MATCH($B57,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$G$3:$G$500,MATCH($B57,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="G57" s="11">
+        <f>IF(INDEX(precios!$H$3:$H$500,MATCH($B57,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$H$3:$H$500,MATCH($B57,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="H57" s="11">
+        <f>IF(INDEX(precios!$I$3:$I$500,MATCH($B57,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$I$3:$I$500,MATCH($B57,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="I57" s="11">
+        <f>IF(INDEX(precios!$J$3:$J$500,MATCH($B57,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$J$3:$J$500,MATCH($B57,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="J57" s="11">
+        <f>IF(INDEX(precios!$K$3:$K$500,MATCH($B57,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$K$3:$K$500,MATCH($B57,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="K57" s="11">
+        <f>IF(INDEX(precios!$L$3:$L$500,MATCH($B57,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$L$3:$L$500,MATCH($B57,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="L57" s="11">
+        <f>IF(INDEX(precios!$M$3:$M$500,MATCH($B57,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$M$3:$M$500,MATCH($B57,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="M57" s="11">
+        <f>IF(INDEX(precios!$N$3:$N$500,MATCH($B57,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$N$3:$N$500,MATCH($B57,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="N57" s="11">
+        <f>SUM(D57:M57)</f>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>281</v>
+      </c>
+      <c r="B58" t="s">
+        <v>338</v>
+      </c>
+      <c r="C58">
+        <f>INDEX(precios!$C$3:$C$500,MATCH($B58,precios!$A$3:$A$500,0))</f>
+      </c>
+      <c r="D58" s="11">
+        <f>IF(INDEX(precios!$E$3:$E$500,MATCH($B58,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$E$3:$E$500,MATCH($B58,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="E58" s="11">
+        <f>IF(INDEX(precios!$F$3:$F$500,MATCH($B58,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$F$3:$F$500,MATCH($B58,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="F58" s="11">
+        <f>IF(INDEX(precios!$G$3:$G$500,MATCH($B58,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$G$3:$G$500,MATCH($B58,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="G58" s="11">
+        <f>IF(INDEX(precios!$H$3:$H$500,MATCH($B58,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$H$3:$H$500,MATCH($B58,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="H58" s="11">
+        <f>IF(INDEX(precios!$I$3:$I$500,MATCH($B58,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$I$3:$I$500,MATCH($B58,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="I58" s="11">
+        <f>IF(INDEX(precios!$J$3:$J$500,MATCH($B58,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$J$3:$J$500,MATCH($B58,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="J58" s="11">
+        <f>IF(INDEX(precios!$K$3:$K$500,MATCH($B58,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$K$3:$K$500,MATCH($B58,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="K58" s="11">
+        <f>IF(INDEX(precios!$L$3:$L$500,MATCH($B58,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$L$3:$L$500,MATCH($B58,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="L58" s="11">
+        <f>IF(INDEX(precios!$M$3:$M$500,MATCH($B58,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$M$3:$M$500,MATCH($B58,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="M58" s="11">
+        <f>IF(INDEX(precios!$N$3:$N$500,MATCH($B58,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$N$3:$N$500,MATCH($B58,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="N58" s="11">
+        <f>SUM(D58:M58)</f>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>281</v>
+      </c>
+      <c r="B59" t="s">
+        <v>340</v>
+      </c>
+      <c r="C59">
+        <f>INDEX(precios!$C$3:$C$500,MATCH($B59,precios!$A$3:$A$500,0))</f>
+      </c>
+      <c r="D59" s="11">
+        <f>IF(INDEX(precios!$E$3:$E$500,MATCH($B59,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$E$3:$E$500,MATCH($B59,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="E59" s="11">
+        <f>IF(INDEX(precios!$F$3:$F$500,MATCH($B59,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$F$3:$F$500,MATCH($B59,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="F59" s="11">
+        <f>IF(INDEX(precios!$G$3:$G$500,MATCH($B59,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$G$3:$G$500,MATCH($B59,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="G59" s="11">
+        <f>IF(INDEX(precios!$H$3:$H$500,MATCH($B59,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$H$3:$H$500,MATCH($B59,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="H59" s="11">
+        <f>IF(INDEX(precios!$I$3:$I$500,MATCH($B59,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$I$3:$I$500,MATCH($B59,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="I59" s="11">
+        <f>IF(INDEX(precios!$J$3:$J$500,MATCH($B59,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$J$3:$J$500,MATCH($B59,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="J59" s="11">
+        <f>IF(INDEX(precios!$K$3:$K$500,MATCH($B59,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$K$3:$K$500,MATCH($B59,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="K59" s="11">
+        <f>IF(INDEX(precios!$L$3:$L$500,MATCH($B59,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$L$3:$L$500,MATCH($B59,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="L59" s="11">
+        <f>IF(INDEX(precios!$M$3:$M$500,MATCH($B59,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$M$3:$M$500,MATCH($B59,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="M59" s="11">
+        <f>IF(INDEX(precios!$N$3:$N$500,MATCH($B59,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$N$3:$N$500,MATCH($B59,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="N59" s="11">
+        <f>SUM(D59:M59)</f>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>281</v>
+      </c>
+      <c r="B60" t="s">
+        <v>342</v>
+      </c>
+      <c r="C60">
+        <f>INDEX(precios!$C$3:$C$500,MATCH($B60,precios!$A$3:$A$500,0))</f>
+      </c>
+      <c r="D60" s="11">
+        <f>IF(INDEX(precios!$E$3:$E$500,MATCH($B60,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$E$3:$E$500,MATCH($B60,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="E60" s="11">
+        <f>IF(INDEX(precios!$F$3:$F$500,MATCH($B60,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$F$3:$F$500,MATCH($B60,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="F60" s="11">
+        <f>IF(INDEX(precios!$G$3:$G$500,MATCH($B60,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$G$3:$G$500,MATCH($B60,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="G60" s="11">
+        <f>IF(INDEX(precios!$H$3:$H$500,MATCH($B60,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$H$3:$H$500,MATCH($B60,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="H60" s="11">
+        <f>IF(INDEX(precios!$I$3:$I$500,MATCH($B60,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$I$3:$I$500,MATCH($B60,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="I60" s="11">
+        <f>IF(INDEX(precios!$J$3:$J$500,MATCH($B60,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$J$3:$J$500,MATCH($B60,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="J60" s="11">
+        <f>IF(INDEX(precios!$K$3:$K$500,MATCH($B60,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$K$3:$K$500,MATCH($B60,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="K60" s="11">
+        <f>IF(INDEX(precios!$L$3:$L$500,MATCH($B60,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$L$3:$L$500,MATCH($B60,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="L60" s="11">
+        <f>IF(INDEX(precios!$M$3:$M$500,MATCH($B60,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$M$3:$M$500,MATCH($B60,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="M60" s="11">
+        <f>IF(INDEX(precios!$N$3:$N$500,MATCH($B60,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$N$3:$N$500,MATCH($B60,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="N60" s="11">
+        <f>SUM(D60:M60)</f>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>281</v>
+      </c>
+      <c r="B61" t="s">
+        <v>344</v>
+      </c>
+      <c r="C61">
+        <f>INDEX(precios!$C$3:$C$500,MATCH($B61,precios!$A$3:$A$500,0))</f>
+      </c>
+      <c r="D61" s="11">
+        <f>IF(INDEX(precios!$E$3:$E$500,MATCH($B61,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$E$3:$E$500,MATCH($B61,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="E61" s="11">
+        <f>IF(INDEX(precios!$F$3:$F$500,MATCH($B61,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$F$3:$F$500,MATCH($B61,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="F61" s="11">
+        <f>IF(INDEX(precios!$G$3:$G$500,MATCH($B61,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$G$3:$G$500,MATCH($B61,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="G61" s="11">
+        <f>IF(INDEX(precios!$H$3:$H$500,MATCH($B61,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$H$3:$H$500,MATCH($B61,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="H61" s="11">
+        <f>IF(INDEX(precios!$I$3:$I$500,MATCH($B61,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$I$3:$I$500,MATCH($B61,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="I61" s="11">
+        <f>IF(INDEX(precios!$J$3:$J$500,MATCH($B61,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$J$3:$J$500,MATCH($B61,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="J61" s="11">
+        <f>IF(INDEX(precios!$K$3:$K$500,MATCH($B61,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$K$3:$K$500,MATCH($B61,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="K61" s="11">
+        <f>IF(INDEX(precios!$L$3:$L$500,MATCH($B61,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$L$3:$L$500,MATCH($B61,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="L61" s="11">
+        <f>IF(INDEX(precios!$M$3:$M$500,MATCH($B61,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$M$3:$M$500,MATCH($B61,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="M61" s="11">
+        <f>IF(INDEX(precios!$N$3:$N$500,MATCH($B61,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$N$3:$N$500,MATCH($B61,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="N61" s="11">
+        <f>SUM(D61:M61)</f>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>281</v>
+      </c>
+      <c r="B62" t="s">
+        <v>346</v>
+      </c>
+      <c r="C62">
+        <f>INDEX(precios!$C$3:$C$500,MATCH($B62,precios!$A$3:$A$500,0))</f>
+      </c>
+      <c r="D62" s="11">
+        <f>IF(INDEX(precios!$E$3:$E$500,MATCH($B62,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$E$3:$E$500,MATCH($B62,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="E62" s="11">
+        <f>IF(INDEX(precios!$F$3:$F$500,MATCH($B62,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$F$3:$F$500,MATCH($B62,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="F62" s="11">
+        <f>IF(INDEX(precios!$G$3:$G$500,MATCH($B62,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$G$3:$G$500,MATCH($B62,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="G62" s="11">
+        <f>IF(INDEX(precios!$H$3:$H$500,MATCH($B62,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$H$3:$H$500,MATCH($B62,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="H62" s="11">
+        <f>IF(INDEX(precios!$I$3:$I$500,MATCH($B62,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$I$3:$I$500,MATCH($B62,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="I62" s="11">
+        <f>IF(INDEX(precios!$J$3:$J$500,MATCH($B62,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$J$3:$J$500,MATCH($B62,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="J62" s="11">
+        <f>IF(INDEX(precios!$K$3:$K$500,MATCH($B62,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$K$3:$K$500,MATCH($B62,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="K62" s="11">
+        <f>IF(INDEX(precios!$L$3:$L$500,MATCH($B62,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$L$3:$L$500,MATCH($B62,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="L62" s="11">
+        <f>IF(INDEX(precios!$M$3:$M$500,MATCH($B62,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$M$3:$M$500,MATCH($B62,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="M62" s="11">
+        <f>IF(INDEX(precios!$N$3:$N$500,MATCH($B62,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$N$3:$N$500,MATCH($B62,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="N62" s="11">
+        <f>SUM(D62:M62)</f>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>281</v>
+      </c>
+      <c r="B63" t="s">
+        <v>348</v>
+      </c>
+      <c r="C63">
+        <f>INDEX(precios!$C$3:$C$500,MATCH($B63,precios!$A$3:$A$500,0))</f>
+      </c>
+      <c r="D63" s="11">
+        <f>IF(INDEX(precios!$E$3:$E$500,MATCH($B63,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$E$3:$E$500,MATCH($B63,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="E63" s="11">
+        <f>IF(INDEX(precios!$F$3:$F$500,MATCH($B63,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$F$3:$F$500,MATCH($B63,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="F63" s="11">
+        <f>IF(INDEX(precios!$G$3:$G$500,MATCH($B63,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$G$3:$G$500,MATCH($B63,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="G63" s="11">
+        <f>IF(INDEX(precios!$H$3:$H$500,MATCH($B63,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$H$3:$H$500,MATCH($B63,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="H63" s="11">
+        <f>IF(INDEX(precios!$I$3:$I$500,MATCH($B63,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$I$3:$I$500,MATCH($B63,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="I63" s="11">
+        <f>IF(INDEX(precios!$J$3:$J$500,MATCH($B63,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$J$3:$J$500,MATCH($B63,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="J63" s="11">
+        <f>IF(INDEX(precios!$K$3:$K$500,MATCH($B63,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$K$3:$K$500,MATCH($B63,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="K63" s="11">
+        <f>IF(INDEX(precios!$L$3:$L$500,MATCH($B63,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$L$3:$L$500,MATCH($B63,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="L63" s="11">
+        <f>IF(INDEX(precios!$M$3:$M$500,MATCH($B63,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$M$3:$M$500,MATCH($B63,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="M63" s="11">
+        <f>IF(INDEX(precios!$N$3:$N$500,MATCH($B63,precios!$A$3:$A$500,0))&gt;0,INDEX(precios!$N$3:$N$500,MATCH($B63,precios!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="N63" s="11">
+        <f>SUM(D63:M63)</f>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>965</v>
+      </c>
+      <c r="B64" t="s">
+        <v>177</v>
+      </c>
+      <c r="C64">
+        <f>INDEX(autos!$B$3:$B$500,MATCH($B64,autos!$A$3:$A$500,0))</f>
+      </c>
+      <c r="D64" s="11">
+        <f>IF(INDEX(autos!$C$3:$C$500,MATCH($B64,autos!$A$3:$A$500,0))&gt;0,INDEX(autos!$C$3:$C$500,MATCH($B64,autos!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="N64" s="11">
+        <f>SUM(D64:M64)</f>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>965</v>
+      </c>
+      <c r="B65" t="s">
+        <v>179</v>
+      </c>
+      <c r="C65">
+        <f>INDEX(autos!$B$3:$B$500,MATCH($B65,autos!$A$3:$A$500,0))</f>
+      </c>
+      <c r="D65" s="11">
+        <f>IF(INDEX(autos!$C$3:$C$500,MATCH($B65,autos!$A$3:$A$500,0))&gt;0,INDEX(autos!$C$3:$C$500,MATCH($B65,autos!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="N65" s="11">
+        <f>SUM(D65:M65)</f>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>965</v>
+      </c>
+      <c r="B66" t="s">
+        <v>181</v>
+      </c>
+      <c r="C66">
+        <f>INDEX(autos!$B$3:$B$500,MATCH($B66,autos!$A$3:$A$500,0))</f>
+      </c>
+      <c r="D66" s="11">
+        <f>IF(INDEX(autos!$C$3:$C$500,MATCH($B66,autos!$A$3:$A$500,0))&gt;0,INDEX(autos!$C$3:$C$500,MATCH($B66,autos!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="N66" s="11">
+        <f>SUM(D66:M66)</f>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>965</v>
+      </c>
+      <c r="B67" t="s">
+        <v>183</v>
+      </c>
+      <c r="C67">
+        <f>INDEX(autos!$B$3:$B$500,MATCH($B67,autos!$A$3:$A$500,0))</f>
+      </c>
+      <c r="D67" s="11">
+        <f>IF(INDEX(autos!$C$3:$C$500,MATCH($B67,autos!$A$3:$A$500,0))&gt;0,INDEX(autos!$C$3:$C$500,MATCH($B67,autos!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="N67" s="11">
+        <f>SUM(D67:M67)</f>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>965</v>
+      </c>
+      <c r="B68" t="s">
+        <v>185</v>
+      </c>
+      <c r="C68">
+        <f>INDEX(autos!$B$3:$B$500,MATCH($B68,autos!$A$3:$A$500,0))</f>
+      </c>
+      <c r="D68" s="11">
+        <f>IF(INDEX(autos!$C$3:$C$500,MATCH($B68,autos!$A$3:$A$500,0))&gt;0,INDEX(autos!$C$3:$C$500,MATCH($B68,autos!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="N68" s="11">
+        <f>SUM(D68:M68)</f>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>965</v>
+      </c>
+      <c r="B69" t="s">
+        <v>187</v>
+      </c>
+      <c r="C69">
+        <f>INDEX(autos!$B$3:$B$500,MATCH($B69,autos!$A$3:$A$500,0))</f>
+      </c>
+      <c r="D69" s="11">
+        <f>IF(INDEX(autos!$C$3:$C$500,MATCH($B69,autos!$A$3:$A$500,0))&gt;0,INDEX(autos!$C$3:$C$500,MATCH($B69,autos!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="N69" s="11">
+        <f>SUM(D69:M69)</f>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>965</v>
+      </c>
+      <c r="B70" t="s">
+        <v>133</v>
+      </c>
+      <c r="C70">
+        <f>INDEX(autos!$B$3:$B$500,MATCH($B70,autos!$A$3:$A$500,0))</f>
+      </c>
+      <c r="D70" s="11">
+        <f>IF(INDEX(autos!$C$3:$C$500,MATCH($B70,autos!$A$3:$A$500,0))&gt;0,INDEX(autos!$C$3:$C$500,MATCH($B70,autos!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="N70" s="11">
+        <f>SUM(D70:M70)</f>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>965</v>
+      </c>
+      <c r="B71" t="s">
+        <v>190</v>
+      </c>
+      <c r="C71">
+        <f>INDEX(autos!$B$3:$B$500,MATCH($B71,autos!$A$3:$A$500,0))</f>
+      </c>
+      <c r="D71" s="11">
+        <f>IF(INDEX(autos!$C$3:$C$500,MATCH($B71,autos!$A$3:$A$500,0))&gt;0,INDEX(autos!$C$3:$C$500,MATCH($B71,autos!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="N71" s="11">
+        <f>SUM(D71:M71)</f>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>966</v>
+      </c>
+      <c r="B72" t="s">
+        <v>215</v>
+      </c>
+      <c r="C72">
+        <f>INDEX(pilotos!$B$3:$B$500,MATCH($B72,pilotos!$A$3:$A$500,0))</f>
+      </c>
+      <c r="D72" s="11">
+        <f>IF(INDEX(pilotos!$C$3:$C$500,MATCH($B72,pilotos!$A$3:$A$500,0))&gt;0,INDEX(pilotos!$C$3:$C$500,MATCH($B72,pilotos!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="N72" s="11">
+        <f>SUM(D72:M72)</f>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>966</v>
+      </c>
+      <c r="B73" t="s">
+        <v>217</v>
+      </c>
+      <c r="C73">
+        <f>INDEX(pilotos!$B$3:$B$500,MATCH($B73,pilotos!$A$3:$A$500,0))</f>
+      </c>
+      <c r="D73" s="11">
+        <f>IF(INDEX(pilotos!$C$3:$C$500,MATCH($B73,pilotos!$A$3:$A$500,0))&gt;0,INDEX(pilotos!$C$3:$C$500,MATCH($B73,pilotos!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="N73" s="11">
+        <f>SUM(D73:M73)</f>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>966</v>
+      </c>
+      <c r="B74" t="s">
+        <v>35</v>
+      </c>
+      <c r="C74">
+        <f>INDEX(pilotos!$B$3:$B$500,MATCH($B74,pilotos!$A$3:$A$500,0))</f>
+      </c>
+      <c r="D74" s="11">
+        <f>IF(INDEX(pilotos!$C$3:$C$500,MATCH($B74,pilotos!$A$3:$A$500,0))&gt;0,INDEX(pilotos!$C$3:$C$500,MATCH($B74,pilotos!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="N74" s="11">
+        <f>SUM(D74:M74)</f>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>966</v>
+      </c>
+      <c r="B75" t="s">
+        <v>220</v>
+      </c>
+      <c r="C75">
+        <f>INDEX(pilotos!$B$3:$B$500,MATCH($B75,pilotos!$A$3:$A$500,0))</f>
+      </c>
+      <c r="D75" s="11">
+        <f>IF(INDEX(pilotos!$C$3:$C$500,MATCH($B75,pilotos!$A$3:$A$500,0))&gt;0,INDEX(pilotos!$C$3:$C$500,MATCH($B75,pilotos!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="N75" s="11">
+        <f>SUM(D75:M75)</f>
+      </c>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>966</v>
+      </c>
+      <c r="B76" t="s">
+        <v>222</v>
+      </c>
+      <c r="C76">
+        <f>INDEX(pilotos!$B$3:$B$500,MATCH($B76,pilotos!$A$3:$A$500,0))</f>
+      </c>
+      <c r="D76" s="11">
+        <f>IF(INDEX(pilotos!$C$3:$C$500,MATCH($B76,pilotos!$A$3:$A$500,0))&gt;0,INDEX(pilotos!$C$3:$C$500,MATCH($B76,pilotos!$A$3:$A$500,0))/$B$4,"")</f>
+      </c>
+      <c r="N76" s="11">
+        <f>SUM(D76:M76)</f>
+      </c>
+    </row>
+    <row r="78" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C78" s="1" t="s">
+        <v>967</v>
+      </c>
+      <c r="N78" s="11">
+        <f>SUM(N11:N76)</f>
       </c>
     </row>
   </sheetData>
@@ -11221,7 +12855,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:N55"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" style="1" customWidth="1"/>
@@ -11496,232 +13130,367 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>256</v>
       </c>
       <c r="B7" t="s">
         <v>248</v>
       </c>
       <c r="C7" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D7">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="E7">
+        <v>20</v>
+      </c>
+      <c r="F7">
+        <v>40</v>
+      </c>
+      <c r="G7">
+        <v>60</v>
+      </c>
+      <c r="H7">
         <v>80</v>
       </c>
-      <c r="F7">
+      <c r="I7">
+        <v>100</v>
+      </c>
+      <c r="J7">
         <v>180</v>
       </c>
-      <c r="G7">
-        <v>320</v>
-      </c>
-      <c r="H7">
-        <v>500</v>
+      <c r="K7">
+        <v>275</v>
+      </c>
+      <c r="L7">
+        <v>385</v>
+      </c>
+      <c r="M7">
+        <v>515</v>
+      </c>
+      <c r="N7">
+        <v>660</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B8" t="s">
         <v>248</v>
       </c>
       <c r="C8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E8">
+        <v>20</v>
+      </c>
+      <c r="F8">
+        <v>40</v>
+      </c>
+      <c r="G8">
+        <v>60</v>
+      </c>
+      <c r="H8">
+        <v>80</v>
+      </c>
+      <c r="I8">
         <v>100</v>
       </c>
-      <c r="F8">
-        <v>250</v>
-      </c>
-      <c r="G8">
-        <v>450</v>
+      <c r="J8">
+        <v>180</v>
+      </c>
+      <c r="K8">
+        <v>275</v>
+      </c>
+      <c r="L8">
+        <v>385</v>
+      </c>
+      <c r="M8">
+        <v>515</v>
+      </c>
+      <c r="N8">
+        <v>660</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B9" t="s">
         <v>248</v>
       </c>
       <c r="C9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="E9">
-        <v>500</v>
+        <v>20</v>
+      </c>
+      <c r="F9">
+        <v>40</v>
+      </c>
+      <c r="G9">
+        <v>60</v>
+      </c>
+      <c r="H9">
+        <v>80</v>
+      </c>
+      <c r="I9">
+        <v>100</v>
+      </c>
+      <c r="J9">
+        <v>180</v>
+      </c>
+      <c r="K9">
+        <v>275</v>
+      </c>
+      <c r="L9">
+        <v>385</v>
+      </c>
+      <c r="M9">
+        <v>515</v>
+      </c>
+      <c r="N9">
+        <v>660</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B10" t="s">
         <v>248</v>
       </c>
       <c r="C10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="E10">
-        <v>600</v>
+        <v>20</v>
       </c>
       <c r="F10">
-        <v>1800</v>
+        <v>40</v>
+      </c>
+      <c r="G10">
+        <v>60</v>
+      </c>
+      <c r="H10">
+        <v>80</v>
+      </c>
+      <c r="I10">
+        <v>100</v>
+      </c>
+      <c r="J10">
+        <v>180</v>
+      </c>
+      <c r="K10">
+        <v>275</v>
+      </c>
+      <c r="L10">
+        <v>385</v>
+      </c>
+      <c r="M10">
+        <v>515</v>
+      </c>
+      <c r="N10">
+        <v>660</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B11" t="s">
         <v>248</v>
       </c>
       <c r="C11" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E11">
-        <v>2200</v>
+        <v>25</v>
+      </c>
+      <c r="F11">
+        <v>50</v>
+      </c>
+      <c r="G11">
+        <v>75</v>
+      </c>
+      <c r="H11">
+        <v>100</v>
+      </c>
+      <c r="I11">
+        <v>125</v>
+      </c>
+      <c r="J11">
+        <v>225</v>
+      </c>
+      <c r="K11">
+        <v>345</v>
+      </c>
+      <c r="L11">
+        <v>480</v>
+      </c>
+      <c r="M11">
+        <v>645</v>
+      </c>
+      <c r="N11">
+        <v>825</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>265</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
+        <v>248</v>
+      </c>
+      <c r="C12" t="s">
         <v>266</v>
       </c>
-      <c r="C12" t="s">
-        <v>267</v>
-      </c>
       <c r="D12">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="E12">
-        <v>700</v>
+        <v>80</v>
+      </c>
+      <c r="F12">
+        <v>180</v>
+      </c>
+      <c r="G12">
+        <v>320</v>
+      </c>
+      <c r="H12">
+        <v>500</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B13" t="s">
+        <v>248</v>
+      </c>
+      <c r="C13" t="s">
         <v>268</v>
       </c>
-      <c r="B13" t="s">
-        <v>266</v>
-      </c>
-      <c r="C13" t="s">
-        <v>269</v>
-      </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13">
-        <v>1000</v>
+        <v>100</v>
+      </c>
+      <c r="F13">
+        <v>250</v>
+      </c>
+      <c r="G13">
+        <v>450</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B14" t="s">
+        <v>248</v>
+      </c>
+      <c r="C14" t="s">
         <v>270</v>
       </c>
-      <c r="B14" t="s">
-        <v>271</v>
-      </c>
-      <c r="C14" t="s">
-        <v>272</v>
-      </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>60</v>
+        <v>500</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B15" t="s">
-        <v>271</v>
+        <v>248</v>
       </c>
       <c r="C15" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
       <c r="E15">
-        <v>110</v>
+        <v>600</v>
+      </c>
+      <c r="F15">
+        <v>1800</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B16" t="s">
-        <v>271</v>
+        <v>248</v>
       </c>
       <c r="C16" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D16">
         <v>0</v>
       </c>
       <c r="E16">
-        <v>40</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B17" t="s">
+        <v>276</v>
+      </c>
+      <c r="C17" t="s">
         <v>277</v>
       </c>
-      <c r="B17" t="s">
-        <v>271</v>
-      </c>
-      <c r="C17" t="s">
-        <v>278</v>
-      </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>60</v>
+        <v>700</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B18" t="s">
+        <v>276</v>
+      </c>
+      <c r="C18" t="s">
         <v>279</v>
       </c>
-      <c r="B18" t="s">
-        <v>271</v>
-      </c>
-      <c r="C18" t="s">
-        <v>280</v>
-      </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18">
-        <v>90</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B19" t="s">
         <v>281</v>
-      </c>
-      <c r="B19" t="s">
-        <v>271</v>
       </c>
       <c r="C19" t="s">
         <v>282</v>
@@ -11730,7 +13499,7 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
@@ -11738,7 +13507,7 @@
         <v>283</v>
       </c>
       <c r="B20" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="C20" t="s">
         <v>284</v>
@@ -11747,7 +13516,7 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>80</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
@@ -11755,7 +13524,7 @@
         <v>285</v>
       </c>
       <c r="B21" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="C21" t="s">
         <v>286</v>
@@ -11764,7 +13533,7 @@
         <v>0</v>
       </c>
       <c r="E21">
-        <v>120</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
@@ -11772,7 +13541,7 @@
         <v>287</v>
       </c>
       <c r="B22" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="C22" t="s">
         <v>288</v>
@@ -11789,7 +13558,7 @@
         <v>289</v>
       </c>
       <c r="B23" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="C23" t="s">
         <v>290</v>
@@ -11798,7 +13567,587 @@
         <v>0</v>
       </c>
       <c r="E23">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B24" t="s">
+        <v>281</v>
+      </c>
+      <c r="C24" t="s">
+        <v>292</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B25" t="s">
+        <v>281</v>
+      </c>
+      <c r="C25" t="s">
+        <v>294</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B26" t="s">
+        <v>281</v>
+      </c>
+      <c r="C26" t="s">
+        <v>296</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B27" t="s">
+        <v>281</v>
+      </c>
+      <c r="C27" t="s">
+        <v>298</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B28" t="s">
+        <v>281</v>
+      </c>
+      <c r="C28" t="s">
+        <v>300</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
         <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B29" t="s">
+        <v>302</v>
+      </c>
+      <c r="C29" t="s">
+        <v>303</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>60</v>
+      </c>
+      <c r="F29">
+        <v>150</v>
+      </c>
+      <c r="G29">
+        <v>300</v>
+      </c>
+      <c r="H29">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B30" t="s">
+        <v>302</v>
+      </c>
+      <c r="C30" t="s">
+        <v>305</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>60</v>
+      </c>
+      <c r="F30">
+        <v>150</v>
+      </c>
+      <c r="G30">
+        <v>300</v>
+      </c>
+      <c r="H30">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B31" t="s">
+        <v>302</v>
+      </c>
+      <c r="C31" t="s">
+        <v>307</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>60</v>
+      </c>
+      <c r="F31">
+        <v>150</v>
+      </c>
+      <c r="G31">
+        <v>300</v>
+      </c>
+      <c r="H31">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B32" t="s">
+        <v>302</v>
+      </c>
+      <c r="C32" t="s">
+        <v>309</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>60</v>
+      </c>
+      <c r="F32">
+        <v>150</v>
+      </c>
+      <c r="G32">
+        <v>300</v>
+      </c>
+      <c r="H32">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B33" t="s">
+        <v>311</v>
+      </c>
+      <c r="C33" t="s">
+        <v>312</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B34" t="s">
+        <v>311</v>
+      </c>
+      <c r="C34" t="s">
+        <v>112</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B35" t="s">
+        <v>311</v>
+      </c>
+      <c r="C35" t="s">
+        <v>124</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B36" t="s">
+        <v>311</v>
+      </c>
+      <c r="C36" t="s">
+        <v>316</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B37" t="s">
+        <v>311</v>
+      </c>
+      <c r="C37" t="s">
+        <v>129</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B38" t="s">
+        <v>311</v>
+      </c>
+      <c r="C38" t="s">
+        <v>319</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B39" t="s">
+        <v>311</v>
+      </c>
+      <c r="C39" t="s">
+        <v>115</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+      <c r="E39">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B40" t="s">
+        <v>311</v>
+      </c>
+      <c r="C40" t="s">
+        <v>322</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
+      </c>
+      <c r="E40">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B41" t="s">
+        <v>311</v>
+      </c>
+      <c r="C41" t="s">
+        <v>136</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="E41">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B42" t="s">
+        <v>311</v>
+      </c>
+      <c r="C42" t="s">
+        <v>139</v>
+      </c>
+      <c r="D42">
+        <v>0</v>
+      </c>
+      <c r="E42">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B43" t="s">
+        <v>311</v>
+      </c>
+      <c r="C43" t="s">
+        <v>118</v>
+      </c>
+      <c r="D43">
+        <v>0</v>
+      </c>
+      <c r="E43">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B44" t="s">
+        <v>281</v>
+      </c>
+      <c r="C44" t="s">
+        <v>327</v>
+      </c>
+      <c r="D44">
+        <v>0</v>
+      </c>
+      <c r="E44">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B45" t="s">
+        <v>281</v>
+      </c>
+      <c r="C45" t="s">
+        <v>329</v>
+      </c>
+      <c r="D45">
+        <v>0</v>
+      </c>
+      <c r="E45">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B46" t="s">
+        <v>281</v>
+      </c>
+      <c r="C46" t="s">
+        <v>331</v>
+      </c>
+      <c r="D46">
+        <v>0</v>
+      </c>
+      <c r="E46">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B47" t="s">
+        <v>281</v>
+      </c>
+      <c r="C47" t="s">
+        <v>333</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="E47">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B48" t="s">
+        <v>281</v>
+      </c>
+      <c r="C48" t="s">
+        <v>335</v>
+      </c>
+      <c r="D48">
+        <v>0</v>
+      </c>
+      <c r="E48">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B49" t="s">
+        <v>281</v>
+      </c>
+      <c r="C49" t="s">
+        <v>337</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+      <c r="E49">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B50" t="s">
+        <v>281</v>
+      </c>
+      <c r="C50" t="s">
+        <v>339</v>
+      </c>
+      <c r="D50">
+        <v>0</v>
+      </c>
+      <c r="E50">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B51" t="s">
+        <v>281</v>
+      </c>
+      <c r="C51" t="s">
+        <v>341</v>
+      </c>
+      <c r="D51">
+        <v>0</v>
+      </c>
+      <c r="E51">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B52" t="s">
+        <v>281</v>
+      </c>
+      <c r="C52" t="s">
+        <v>343</v>
+      </c>
+      <c r="D52">
+        <v>0</v>
+      </c>
+      <c r="E52">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B53" t="s">
+        <v>281</v>
+      </c>
+      <c r="C53" t="s">
+        <v>345</v>
+      </c>
+      <c r="D53">
+        <v>0</v>
+      </c>
+      <c r="E53">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B54" t="s">
+        <v>281</v>
+      </c>
+      <c r="C54" t="s">
+        <v>347</v>
+      </c>
+      <c r="D54">
+        <v>0</v>
+      </c>
+      <c r="E54">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B55" t="s">
+        <v>281</v>
+      </c>
+      <c r="C55" t="s">
+        <v>349</v>
+      </c>
+      <c r="D55">
+        <v>0</v>
+      </c>
+      <c r="E55">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -11825,40 +14174,40 @@
         <v>7</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>291</v>
+        <v>350</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>292</v>
+        <v>351</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>293</v>
+        <v>352</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>294</v>
+        <v>353</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>295</v>
+        <v>354</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>296</v>
+        <v>355</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>297</v>
+        <v>356</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>298</v>
+        <v>357</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>299</v>
+        <v>358</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>300</v>
+        <v>359</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>301</v>
+        <v>360</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>302</v>
+        <v>361</v>
       </c>
     </row>
     <row r="2" ht="78" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -11869,48 +14218,48 @@
         <v>81</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>303</v>
+        <v>362</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>304</v>
+        <v>363</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>305</v>
+        <v>364</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>306</v>
+        <v>365</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>307</v>
+        <v>366</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>308</v>
+        <v>367</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>309</v>
+        <v>368</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>310</v>
+        <v>369</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>311</v>
+        <v>370</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>312</v>
+        <v>371</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>313</v>
+        <v>372</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>314</v>
+        <v>373</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="B3" t="s">
-        <v>316</v>
+        <v>375</v>
       </c>
       <c r="C3">
         <v>1.6</v>
@@ -11951,10 +14300,10 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>317</v>
+        <v>376</v>
       </c>
       <c r="B4" t="s">
-        <v>318</v>
+        <v>377</v>
       </c>
       <c r="C4">
         <v>0.6</v>
@@ -11995,10 +14344,10 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>319</v>
+        <v>378</v>
       </c>
       <c r="B5" t="s">
-        <v>320</v>
+        <v>379</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -12039,10 +14388,10 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>321</v>
+        <v>380</v>
       </c>
       <c r="B6" t="s">
-        <v>322</v>
+        <v>381</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -12083,10 +14432,10 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>323</v>
+        <v>382</v>
       </c>
       <c r="B7" t="s">
-        <v>324</v>
+        <v>383</v>
       </c>
       <c r="C7">
         <v>0.8</v>
@@ -12146,10 +14495,10 @@
         <v>6</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>325</v>
+        <v>384</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>326</v>
+        <v>385</v>
       </c>
     </row>
     <row r="2" ht="78" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -12157,725 +14506,725 @@
         <v>145</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>327</v>
+        <v>386</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>328</v>
+        <v>387</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>329</v>
+        <v>388</v>
       </c>
       <c r="B3">
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>330</v>
+        <v>389</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>331</v>
+        <v>390</v>
       </c>
       <c r="B4">
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>332</v>
+        <v>391</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>333</v>
+        <v>392</v>
       </c>
       <c r="B5">
         <v>0.8</v>
       </c>
       <c r="C5" t="s">
-        <v>334</v>
+        <v>393</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>335</v>
+        <v>394</v>
       </c>
       <c r="B6">
         <v>0.16</v>
       </c>
       <c r="C6" t="s">
-        <v>336</v>
+        <v>395</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>337</v>
+        <v>396</v>
       </c>
       <c r="B7">
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>338</v>
+        <v>397</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>339</v>
+        <v>398</v>
       </c>
       <c r="B8">
         <v>0.35</v>
       </c>
       <c r="C8" t="s">
-        <v>340</v>
+        <v>399</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>341</v>
+        <v>400</v>
       </c>
       <c r="B9">
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>342</v>
+        <v>401</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>343</v>
+        <v>402</v>
       </c>
       <c r="B10">
         <v>0.09</v>
       </c>
       <c r="C10" t="s">
-        <v>344</v>
+        <v>403</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>345</v>
+        <v>404</v>
       </c>
       <c r="B11">
         <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>346</v>
+        <v>405</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>347</v>
+        <v>406</v>
       </c>
       <c r="B12">
         <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>348</v>
+        <v>407</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>349</v>
+        <v>408</v>
       </c>
       <c r="B13">
         <v>0.7</v>
       </c>
       <c r="C13" t="s">
-        <v>350</v>
+        <v>409</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>351</v>
+        <v>410</v>
       </c>
       <c r="B14">
         <v>0.6</v>
       </c>
       <c r="C14" t="s">
-        <v>352</v>
+        <v>411</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>353</v>
+        <v>412</v>
       </c>
       <c r="B15">
         <v>6</v>
       </c>
       <c r="C15" t="s">
-        <v>354</v>
+        <v>413</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>355</v>
+        <v>414</v>
       </c>
       <c r="B16">
         <v>0.5</v>
       </c>
       <c r="C16" t="s">
-        <v>356</v>
+        <v>415</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>357</v>
+        <v>416</v>
       </c>
       <c r="B17">
         <v>0.3</v>
       </c>
       <c r="C17" t="s">
-        <v>358</v>
+        <v>417</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>359</v>
+        <v>418</v>
       </c>
       <c r="B18">
         <v>0.5</v>
       </c>
       <c r="C18" t="s">
-        <v>360</v>
+        <v>419</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>361</v>
+        <v>420</v>
       </c>
       <c r="B19">
         <v>0.1</v>
       </c>
       <c r="C19" t="s">
-        <v>362</v>
+        <v>421</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>363</v>
+        <v>422</v>
       </c>
       <c r="B20">
         <v>3</v>
       </c>
       <c r="C20" t="s">
-        <v>364</v>
+        <v>423</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>365</v>
+        <v>424</v>
       </c>
       <c r="B21">
         <v>5</v>
       </c>
       <c r="C21" t="s">
-        <v>366</v>
+        <v>425</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>367</v>
+        <v>426</v>
       </c>
       <c r="B22">
         <v>1.2</v>
       </c>
       <c r="C22" t="s">
-        <v>368</v>
+        <v>427</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>369</v>
+        <v>428</v>
       </c>
       <c r="B23">
         <v>2</v>
       </c>
       <c r="C23" t="s">
-        <v>370</v>
+        <v>429</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>371</v>
+        <v>430</v>
       </c>
       <c r="B24">
         <v>1.6</v>
       </c>
       <c r="C24" t="s">
-        <v>372</v>
+        <v>431</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>373</v>
+        <v>432</v>
       </c>
       <c r="B25">
         <v>1.3</v>
       </c>
       <c r="C25" t="s">
-        <v>374</v>
+        <v>433</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>375</v>
+        <v>434</v>
       </c>
       <c r="B26">
         <v>2.5</v>
       </c>
       <c r="C26" t="s">
-        <v>376</v>
+        <v>435</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>377</v>
+        <v>436</v>
       </c>
       <c r="B27">
         <v>4.5</v>
       </c>
       <c r="C27" t="s">
-        <v>378</v>
+        <v>437</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>379</v>
+        <v>438</v>
       </c>
       <c r="B28">
         <v>1.6</v>
       </c>
       <c r="C28" t="s">
-        <v>380</v>
+        <v>439</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>381</v>
+        <v>440</v>
       </c>
       <c r="B29">
         <v>0.3</v>
       </c>
       <c r="C29" t="s">
-        <v>382</v>
+        <v>441</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>383</v>
+        <v>442</v>
       </c>
       <c r="B30">
         <v>0.45</v>
       </c>
       <c r="C30" t="s">
-        <v>384</v>
+        <v>443</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>385</v>
+        <v>444</v>
       </c>
       <c r="B31">
         <v>2</v>
       </c>
       <c r="C31" t="s">
-        <v>386</v>
+        <v>445</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>387</v>
+        <v>446</v>
       </c>
       <c r="B32">
         <v>0.7</v>
       </c>
       <c r="C32" t="s">
-        <v>388</v>
+        <v>447</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>389</v>
+        <v>448</v>
       </c>
       <c r="B33">
         <v>0.5</v>
       </c>
       <c r="C33" t="s">
-        <v>390</v>
+        <v>449</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>391</v>
+        <v>450</v>
       </c>
       <c r="B34">
         <v>0.7</v>
       </c>
       <c r="C34" t="s">
-        <v>392</v>
+        <v>451</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>393</v>
+        <v>452</v>
       </c>
       <c r="B35">
         <v>1.4</v>
       </c>
       <c r="C35" t="s">
-        <v>394</v>
+        <v>453</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>395</v>
+        <v>454</v>
       </c>
       <c r="B36">
         <v>2.5</v>
       </c>
       <c r="C36" t="s">
-        <v>396</v>
+        <v>455</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>397</v>
+        <v>456</v>
       </c>
       <c r="B37">
         <v>0.2</v>
       </c>
       <c r="C37" t="s">
-        <v>398</v>
+        <v>457</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>399</v>
+        <v>458</v>
       </c>
       <c r="B38">
         <v>0.28</v>
       </c>
       <c r="C38" t="s">
-        <v>400</v>
+        <v>459</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>401</v>
+        <v>460</v>
       </c>
       <c r="B39">
         <v>1.6</v>
       </c>
       <c r="C39" t="s">
-        <v>402</v>
+        <v>461</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>403</v>
+        <v>462</v>
       </c>
       <c r="B40">
         <v>0.4</v>
       </c>
       <c r="C40" t="s">
-        <v>404</v>
+        <v>463</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>405</v>
+        <v>464</v>
       </c>
       <c r="B41">
         <v>1</v>
       </c>
       <c r="C41" t="s">
-        <v>406</v>
+        <v>465</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>407</v>
+        <v>466</v>
       </c>
       <c r="B42">
         <v>4.5</v>
       </c>
       <c r="C42" t="s">
-        <v>408</v>
+        <v>467</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>409</v>
+        <v>468</v>
       </c>
       <c r="B43">
         <v>2.5</v>
       </c>
       <c r="C43" t="s">
-        <v>410</v>
+        <v>469</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>411</v>
+        <v>470</v>
       </c>
       <c r="B44">
         <v>1.5</v>
       </c>
       <c r="C44" t="s">
-        <v>412</v>
+        <v>471</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>413</v>
+        <v>472</v>
       </c>
       <c r="B45">
         <v>6</v>
       </c>
       <c r="C45" t="s">
-        <v>414</v>
+        <v>473</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>415</v>
+        <v>474</v>
       </c>
       <c r="B46">
         <v>0.6</v>
       </c>
       <c r="C46" t="s">
-        <v>416</v>
+        <v>475</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>417</v>
+        <v>476</v>
       </c>
       <c r="B47">
         <v>3</v>
       </c>
       <c r="C47" t="s">
-        <v>418</v>
+        <v>477</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>419</v>
+        <v>478</v>
       </c>
       <c r="B48">
         <v>1.5</v>
       </c>
       <c r="C48" t="s">
-        <v>420</v>
+        <v>479</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>421</v>
+        <v>480</v>
       </c>
       <c r="B49">
         <v>26</v>
       </c>
       <c r="C49" t="s">
-        <v>422</v>
+        <v>481</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>423</v>
+        <v>482</v>
       </c>
       <c r="B50">
         <v>0.5</v>
       </c>
       <c r="C50" t="s">
-        <v>424</v>
+        <v>483</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>425</v>
+        <v>484</v>
       </c>
       <c r="B51">
         <v>0.35</v>
       </c>
       <c r="C51" t="s">
-        <v>426</v>
+        <v>485</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>427</v>
+        <v>486</v>
       </c>
       <c r="B52">
         <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>428</v>
+        <v>487</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>429</v>
+        <v>488</v>
       </c>
       <c r="B53">
         <v>3</v>
       </c>
       <c r="C53" t="s">
-        <v>430</v>
+        <v>489</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>431</v>
+        <v>490</v>
       </c>
       <c r="B54">
         <v>2</v>
       </c>
       <c r="C54" t="s">
-        <v>432</v>
+        <v>491</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>433</v>
+        <v>492</v>
       </c>
       <c r="B55">
         <v>8</v>
       </c>
       <c r="C55" t="s">
-        <v>434</v>
+        <v>493</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>435</v>
+        <v>494</v>
       </c>
       <c r="B56">
         <v>0.25</v>
       </c>
       <c r="C56" t="s">
-        <v>436</v>
+        <v>495</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>437</v>
+        <v>496</v>
       </c>
       <c r="B57">
         <v>4</v>
       </c>
       <c r="C57" t="s">
-        <v>438</v>
+        <v>497</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>439</v>
+        <v>498</v>
       </c>
       <c r="B58">
         <v>30</v>
       </c>
       <c r="C58" t="s">
-        <v>440</v>
+        <v>499</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>441</v>
+        <v>500</v>
       </c>
       <c r="B59">
         <v>0.25</v>
       </c>
       <c r="C59" t="s">
-        <v>442</v>
+        <v>501</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>443</v>
+        <v>502</v>
       </c>
       <c r="B60">
         <v>4</v>
       </c>
       <c r="C60" t="s">
-        <v>444</v>
+        <v>503</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>445</v>
+        <v>504</v>
       </c>
       <c r="B61">
         <v>0.35</v>
       </c>
       <c r="C61" t="s">
-        <v>446</v>
+        <v>505</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>447</v>
+        <v>506</v>
       </c>
       <c r="B62">
         <v>0.3</v>
       </c>
       <c r="C62" t="s">
-        <v>448</v>
+        <v>507</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>449</v>
+        <v>508</v>
       </c>
       <c r="B63">
         <v>1.1</v>
       </c>
       <c r="C63" t="s">
-        <v>450</v>
+        <v>509</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>451</v>
+        <v>510</v>
       </c>
       <c r="B64">
         <v>1.5</v>
       </c>
       <c r="C64" t="s">
-        <v>452</v>
+        <v>511</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>453</v>
+        <v>512</v>
       </c>
       <c r="B65">
         <v>1.25</v>
       </c>
       <c r="C65" t="s">
-        <v>454</v>
+        <v>513</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>455</v>
+        <v>514</v>
       </c>
       <c r="B66">
         <v>1.3</v>
       </c>
       <c r="C66" t="s">
-        <v>456</v>
+        <v>515</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>457</v>
+        <v>516</v>
       </c>
       <c r="B67">
         <v>0.5</v>
       </c>
       <c r="C67" t="s">
-        <v>458</v>
+        <v>517</v>
       </c>
     </row>
   </sheetData>
